--- a/social/Content-Ideen-DEGWAW.xlsx
+++ b/social/Content-Ideen-DEGWAW.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Content-Ideen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Content-Ideen'!$A$1:$N$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Content-Ideen'!$A$1:$O$303</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N303"/>
+  <dimension ref="A1:O303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -473,9 +473,10 @@
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -536,15 +537,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Drehskript (fertig)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Geplant für</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notizen</t>
         </is>
@@ -604,9 +610,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Von hinten gefilmt, wie jemand mit Koffer aus der Metro-Rolltreppe nach oben in die Stadt blickt · Text: "Neu in Warschau?"
+3–8s — Bild: Schwenk über eine belebte Warschauer Straße, viele fremde Gesichter · Sprich (ruhig, warm): "Eine neue Stadt kann sich groß und ziemlich einsam anfühlen."
+8–14s — Bild: Schnitt auf eine offene Kirchentür, freundliche Gesichter, jemand winkt · Sprich: "Das kennen wir gut. Und deshalb gibt es einen Ort, an dem Deutsch gesprochen wird — und an dem du einfach dazugehörst."
+14–17s — Bild: Halbnah, jemand reicht einladend die Hand · Sprich: "Komm einfach vorbei. Ganz ohne Anmeldung."
+17–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent (Klavier/Streicher, leise) · 💡 Tipp: Sprich den Off-Text erst getrennt aufs Handy-Diktiergerät ein — dann klingt die Stimme näher als die Kamera-Tonspur der Straße.</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -662,9 +679,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~25s
+0–4s — Bild: POV, Handy auf Brusthöhe, Start am belebten Krakowskie Przedmieście · Text: "Komm einfach mit."
+4–12s — Bild: Durchgehender Gang durch die Altstadt, Fassaden und Passanten ziehen vorbei · Sprich (leise, freundlich): "Manchmal ist der schwerste Schritt der erste vor die Tür. Also gehen wir ihn einmal zusammen."
+12–18s — Bild: Einbiegen in die ruhige Miodowa, die Straße wird stiller · Text: "Bis zu unserer Tür"
+18–22s — Bild: Eine Hand öffnet die Tür Miodowa 21 · Sprich: "Und hier sind wir schon."
+22–25s — Bild: Letzter Blick in den warmen Synodalsaal, dann Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, ein gleichmäßiger Puls, der zum Gehen passt · 💡 Tipp: In einem Rutsch laufen und filmen, nicht stückeln — kleine Wackler wirken authentisch, ruck-Schnitte reißen den POV-Fluss auseinander.</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -720,9 +748,19 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1 (Hook, Aubergine-Hintergrund, weiße Schrift): "3 Dinge, die dir in Warschau keiner sagt" — klein darunter: "aus eigener Erfahrung"
+Slide 2 (Foto Bäckerei/Brot): "1. Wo es richtiges deutsches Brot gibt — such nach Bäckereien mit Roggen- und Sauerteig, es gibt sie öfter als du denkst."
+Slide 3 (Foto Ticketautomat/ÖPNV-App): "2. Wie die Öffi-Tickets gehen — lad dir die App am besten am ersten Tag, entwerten musst du nur beim Papierticket."
+Slide 4 (Foto belebter Treffpunkt/Café): "3. Wo du Deutsch hörst — es gibt mehr deutschsprachige Ecken in Warschau, als in keinem Reiseführer steht."
+Slide 5 (Abschluss, warm): "Und sonntags gibt's uns. 09:30 · Miodowa 21 — Link in Bio zur WhatsApp-Gruppe."
+💡 Tipp: Alle Slides im gleichen Layout halten (gleiche Schrift, gleiche Textposition) — dann wirkt das Carousel wie aus einem Guss und lädt zum Weiterwischen ein.</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -778,9 +816,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s (kein gesprochener Text, nur On-Screen)
+0–4s — Bild: Nahaufnahme einer Kaffeetasse am Fenster, Regentropfen an der Scheibe · Text: "Der erste Sonntag allein"
+4–8s — Bild: Person schaut still nach draußen, Rücken oder Profil · Text: "ist der schwerste."
+8–13s — Bild: Harter Schnitt auf eine offene Kirchentür von innen, warmes Licht fällt herein · Text: "Er muss nicht allein bleiben."
+13–15s — Bild: Freundliche Gesichter, jemand reicht die Hand ins Bild · (kein Text)
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, leise anschwellend — beim Schnitt zur Kirchentür darf es wärmer/heller werden · 💡 Tipp: Den harten Schnitt genau auf einen Musik-Akzent legen (kalt → warm), das trägt die ganze Emotion des Clips.</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -836,9 +885,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–4s — Bild: Langsame Kamerafahrt in den leeren Synodalsaal hinein · Sprich (ruhig): "Zum ersten Mal in eine fremde Kirche zu gehen, kostet Überwindung. Das verstehen wir."
+4–10s — Bild: Detail-Schwenk über Gesangbuch, Stühle, Altar · Sprich: "Deshalb zeigen wir dir kurz, was dich erwartet. Es dauert etwa eine Stunde — Lieder, ein paar Worte, ein Segen."
+10–16s — Bild: Weiter durch den Raum, warmes Licht · Sprich: "Kein Dresscode. Keine Anmeldung. Und keine Erwartung an dich."
+16–19s — Bild: Schwenk auf die offene Tür · Sprich: "Du darfst einfach kommen — und wieder gehen."
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, dezent, unaufdringlich (leises Klavier) · 💡 Tipp: Für die weiche Kamerafahrt das Handy langsam vor dem Körper hertragen und dabei bewusst gleichmäßig gehen — lieber zu langsam als zu schnell.</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -894,9 +954,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–5s — Bild: Schnelle Schnittfolge polnischer Straßenschilder und Schaufenster, viele fremde Wörter · Text: "Den ganzen Tag eine fremde Sprache"
+5–9s — Bild: Menschen in der Metro, Originalton der U-Bahn-Ansage auf Polnisch · Text: "überall um dich herum"
+9–11s — Bild: Kurze Stille, ruhige Kirchentür von außen · (kein Text, Ton fällt weg)
+11–15s — Bild: Die Tür geht auf, eine freundliche Person sagt herzlich · Sprich (warm, direkt in die Kamera): "Guten Morgen! Schön, dass du da bist."
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: erst dichtes, leicht unruhiges Stadt-Ambiente, dann bei der Stille kurz weg — der O-Ton "Guten Morgen" steht allein · 💡 Tipp: Die zwei Sekunden Stille vor dem "Guten Morgen" sind der wichtigste Moment — nicht wegschneiden, die Pause macht den Kontrast.</t>
+        </is>
+      </c>
       <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -952,9 +1023,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Die Fassade Miodowa 21 frontal, die richtige Eingangstür klar im Bild · Bildaufbau/Licht: Bei Tageslicht fotografieren (vormittags, weiches Licht), gerade und auf Augenhöhe stehen, sodass die Tür mittig sitzt; in der Nachbearbeitung einen deutlichen Pfeil (Aubergine oder Weiß) direkt auf die richtige Tür zeichnen · Text im Bild: "Hier ist der Eingang — Miodowa 21. Durch diese Tür, dann geradeaus. So 09:30."
+💡 Tipp: Lieber einen Schritt zurücktreten und die Hausnummer mit aufs Bild nehmen — dann findet man den Eingang auch, wenn die Straße voller geparkter Autos ist.</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1010,9 +1087,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~40s (frei erzählt — die folgenden Sätze sind Leitplanken, keine Auswendig-Vorlage)
+0–4s — Bild: Person sitzt entspannt im Gemeinderaum oder Café, Handy auf Augenhöhe · Sprich: "Vor einem Jahr bin ich hier gelandet und kannte in Warschau keinen einzigen Menschen."
+4–16s — Bild: Weiter im Interview, ruhig · Sprich: "Die ersten Wochen waren hart — viel allein, viel fremde Sprache. Ich hab lange gebraucht, bis ich mich das erste Mal hierher getraut hab."
+16–28s — Bild: Zwischenschnitte Kirchenkaffee, Gruppe im Gespräch, Lachen · Sprich: "Und dann hat mich einfach jemand angesprochen und gefragt, ob ich neu bin. Ab da war ich nicht mehr allein."
+28–36s — Bild: Zurück zur Person, warmes Lächeln · Sprich: "Heute gehör ich fest dazu. Wenn du gerade neu bist: Trau dich, komm einfach mal vorbei."
+36–40s — Endcard: Lutherrose + "So 09:30 · Miodowa 21 · Link in Bio"
+🎵 Musik: sehr leise, warm, im Hintergrund — die Stimme muss klar vorne stehen · 💡 Tipp: Person nah ans Handy setzen und in eine ruhige Ecke — O-Ton-Interviews leben von verständlicher Sprache, nicht von Hall.</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1068,9 +1156,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1 (Hook, Aubergine-Hintergrund): "Wo trifft man in Warschau eigentlich Deutschsprachige?"
+Slide 2 (Foto zwei Menschen im Gespräch): "Sprachtandems &amp; Meetups — such online nach Deutsch-Polnisch-Tandems, oft kostenlos und unkompliziert."
+Slide 3 (Foto Café): "Cafés &amp; Treffpunkte — es gibt Ecken, in denen du regelmäßig Deutsch hörst. Einfach mal hinsetzen und die Ohren aufmachen."
+Slide 4 (Foto Gebäude/Institut): "Vereine &amp; Institute — deutschsprachige Kultur- und Bildungsorte veranstalten oft offene Abende."
+Slide 5 (Foto Kirchenkaffee): "Und sonntags: wir. Eine kleine Gemeinde, in der Deutsch gesprochen, gesungen und Kaffee getrunken wird."
+Slide 6 (Abschluss, sanft): "Such dir aus, was zu dir passt. Und wenn du mal durchatmen willst — unsere Tür ist offen. Link in Bio."
+💡 Tipp: Keine reine Werbung — dass wir uns bewusst als "eine von mehreren" Optionen zeigen, macht den Post glaubwürdig und teilbar. Diesen Ton in den Slide-Texten halten.</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1126,9 +1225,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Person steht vor der Tür Miodowa 21, zögert, atmet einmal tief durch · Sprich (ruhig, ermutigend): "Du musst nicht wissen, wann man aufsteht oder welches Lied kommt."
+4–8s — Bild: Nahaufnahme der Hand, die zur Klinke greift · Text: "Keine Anmeldung · Kein Vorwissen · Kein Kirchen-Abo"
+8–14s — Bild: Sie öffnet die Tür, geht rein, wird freundlich empfangen · Sprich: "Du musst gar nichts können — außer durch diese Tür kommen. Den Rest machen wir gemeinsam."
+14–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, ermutigend, leicht heller werdend beim Eintreten · 💡 Tipp: Das tiefe Durchatmen vor der Tür wirklich zeigen (kurze Nahaufnahme der Schulter/Brust) — dieser winzige Moment macht die ganze Schwellenangst greifbar.</t>
+        </is>
+      </c>
       <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1184,9 +1293,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Statisches Standbild der Türfassade Miodowa 21, ruhig halten · Text: "Diese Tür sieht unscheinbar aus."
+3–8s — Bild: Langsamer Push-in (Schritt für Schritt näher) auf die Tür, sie öffnet sich · Sprich (neugierig-warm): "Von außen ist es nur eine Tür. Aber dahinter …"
+8–13s — Bild: Der warme Raum: Licht, Stühle, Menschen, ein Lachen · Sprich: "… wartet ein warmer Raum, in dem sonntags Deutsch gesprochen, gesungen und gelacht wird."
+13–16s — Endcard: Lutherrose + "Miodowa 21 · So 09:30"
+🎵 Musik: neugierig-ruhig, beim Öffnen der Tür wärmer werdend · 💡 Tipp: Den Kontrast außen (nüchtern, grau) zu innen (warm, hell) im Bild bewusst betonen — draußen kühler Weißabgleich, drinnen warmes Licht suchen.</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1242,9 +1361,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Reine Textkarte auf gedecktem Aubergine-Hintergrund (#480048), keine Ablenkung · Bildaufbau/Licht: Zuspruch-Satz groß und mittig in warmer, gut lesbarer Schrift (weiß/creme); viel Raum drumherum lassen, unten klein die Einladung; als Bildmotiv reicht der Farbverlauf, kein Foto nötig · Text im Bild: groß "Heimweh ist okay." — darunter mittelgroß "Es zeigt nur, dass du irgendwo geliebt wirst." — unten klein "So 09:30 · Miodowa 21"
+💡 Tipp: Nicht überladen — ein Satz, viel Ruhe. Bei ernsten Gefühlsthemen wirkt reduziert und still glaubwürdiger als bunt und laut.</t>
+        </is>
+      </c>
       <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1300,9 +1425,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s (Stimmungs-Reel, überwiegend On-Screen-Text + Originalton)
+0–4s — Bild: Nahaufnahme, wie Kaffee dampfend in eine Tasse eingeschenkt wird · Text: "Der Geruch von frischem Kaffee"
+4–8s — Bild: Jemand deckt die Tische, Kuchen wird hingestellt · Text: "gedeckte Tische, ein bisschen Kuchen"
+8–12s — Bild: Detail Hände/Tassen, dazu Originalton: leises Stimmengewirr auf Deutsch, ein Lachen · Text: "Stimmen in deiner Sprache"
+12–16s — Bild: Warmes Schlussbild vom Kirchenkaffee, dann Endcard: Lutherrose + "Ein Stück Zuhause · So 09:30 · Miodowa 21"
+🎵 Musik: ruhig und warm, sehr leise, damit das deutsche Stimmengewirr durchklingt · 💡 Tipp: Den Originalton der deutschen Stimmen bewusst mit aufnehmen und leise mitlaufen lassen — er macht das Reel emotional echt, mehr als jede Musik.</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1358,9 +1493,22 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~28s
+0–3s — Bild: Person sitzt entspannt, Handy auf Augenhöhe · Sprich: "Fünf Fragen, die uns neue Leute am häufigsten stellen — ganz ehrlich beantwortet."
+3–8s — Textkarte: "Kostet das was?" · Sprich: "Nein, nichts. Du zahlst keinen Eintritt und musst auch nichts spenden."
+8–13s — Textkarte: "Muss ich mitsingen?" · Sprich: "Nur wenn du magst. Zuhören ist völlig okay."
+13–18s — Textkarte: "Was zieh ich an?" · Sprich: "Das, worin du dich wohlfühlst. Es gibt keinen Dresscode."
+18–22s — Textkarte: "Kenn ich da jemanden?" · Sprich: "Beim ersten Mal meistens nicht — aber das ändert sich schnell beim Kaffee danach."
+22–25s — Textkarte: "Darf ich einfach wieder gehen?" · Sprich: "Jederzeit. Du entscheidest, wie lange du bleibst."
+25–28s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: leicht, freundlich, dezent · 💡 Tipp: Jede Frage als kurzen eigenen Clip aufnehmen und hart aneinanderschneiden — der schnelle Rhythmus hält die Aufmerksamkeit über alle fünf Fragen.</t>
+        </is>
+      </c>
       <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1416,9 +1564,18 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~14s
+0–5s — Bild: Langsamer Schwenk über die leeren Stuhlreihen im Synodalsaal, sanftes Morgenlicht · Text: "Siehst du diesen Platz?"
+5–10s — Bild: Kamera kommt zur Ruhe auf einem einzelnen freien Platz, hält still · Sprich (leise, warm): "Der ist nicht vergeben. Der wartet auf dich."
+10–14s — Bild: Der Platz bleibt im Bild, dann Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr ruhig, getragen, ein einzelnes Instrument · 💡 Tipp: Am Ende bewusst 2 Sekunden auf dem leeren Platz verweilen, ohne Schnitt — die Stille lässt die Einladung wirken.</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1474,9 +1631,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1 (Hook, Aubergine-Hintergrund): "Neu-in-Warschau-Starterkit — die ersten 4 To-dos"
+Slide 2 (Foto SIM-Karte/Handy): "1. SIM-Karte — hol dir eine polnische Prepaid-Karte, das macht Alltag und Behörden viel leichter."
+Slide 3 (Foto Amt/Formular): "2. Ummeldung — kümmer dich früh um die Anmeldung deines Wohnsitzes, vieles hängt daran."
+Slide 4 (Foto Tram/Ticket-App): "3. Öffi-App — lad dir die Ticket-App, dann kommst du ohne Automaten-Suche durch die Stadt."
+Slide 5 (Foto Bankkarte): "4. Bankkonto — ein lokales Konto spart dir Gebühren und Kopfschmerzen."
+Slide 6 (Abschluss, warm): "Und wenn zwischen all den Erledigungen jemand zum Reden fehlt — unsere Tür ist sonntags offen. Link in Bio."
+💡 Tipp: Bewusst keine konkreten Anbieter/Ämter-Namen nennen (ändern sich, könnten falsch sein) — beim allgemeinen, ehrlichen Rat bleiben. Für harte Fakten auf die WhatsApp-Gruppe verweisen.</t>
+        </is>
+      </c>
       <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1532,9 +1700,19 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Handy-Screen-Aufnahme der Gruppe, Namen und Profilbilder verpixelt/anonymisiert · Sprich (locker): "Kurz gezeigt, wie unsere WhatsApp-Gruppe von innen aussieht."
+4–10s — Bild: Langsam durch den Chat scrollen — Termine, ein freundliches "Bis Sonntag!", ein Foto · Sprich: "Hier teilen wir Termine, Infos und ein bisschen Alltag. Mehr nicht — kein Spam."
+10–15s — Bild: Screen ruht auf der Teilnehmerzahl/Info-Seite · Sprich: "Und das Wichtigste: Du darfst einfach still mitlesen. Niemand muss sofort schreiben."
+15–18s — Endcard: Lutherrose + "Link in Bio → WhatsApp-Gruppe"
+🎵 Musik: locker, leicht, unaufdringlich · 💡 Tipp: Vor der Aufnahme wirklich alle Namen und Fotos verpixeln oder eine leere Test-Gruppe nachbauen — Datenschutz geht vor, echte Kontakte niemals erkennbar zeigen.</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1590,9 +1768,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s (ohne gesprochenen Text, Bild-Rhythmus auf Musik)
+0–3s — Bild: Tür geht auf, Morgenlicht fällt in den Raum · Text: "Sonntagmorgen bei uns"
+3–6s — Bild: Detail Gesangbuch aufgeschlagen, daneben eine Kerze · (kein Text)
+6–9s — Bild: Menschen im Gottesdienst, Gesang klingt als Originalton an · (kein Text)
+9–12s — Bild: Dampfende Kaffeetasse beim Kirchenkaffee · (kein Text)
+12–15s — Bild: Ein Lächeln, dann Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, angenehm, mit klarem Beat für die Schnitte — der O-Ton des Gesangs darf kurz durchbrechen · 💡 Tipp: Schnitte jeweils auf den Takt der Musik legen; 5 kurze Clips à ~3s reichen völlig — lieber wenige gute Bilder als viele hektische.</t>
+        </is>
+      </c>
       <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1648,9 +1837,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~30s (frei erzählt — Sätze als Leitplanken)
+0–4s — Bild: Person sitzt entspannt, Handy auf Augenhöhe · Sprich: "Ich lebe hier zwischen zwei Sprachen — Deutsch und Polnisch, jeden Tag."
+4–14s — Bild: Zwischenschnitte Familie, zweisprachige Details (Bücher, Schilder) · Sprich: "Zuhause reden wir mal so, mal so. Das ist ein Reichtum — und manchmal auch ein kleiner Spagat."
+14–24s — Bild: Kirchenkaffee, Gruppe im Gespräch · Sprich: "Was ich an unserer Gemeinde mag: Hier müssen die beiden Welten nicht auseinander. Beide dürfen dazugehören."
+24–27s — Bild: Zurück zur Person, ruhiges Lächeln · Sprich: "Egal, wo du dazwischen stehst — hier ist Platz für dich."
+27–30s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, leise, unauffällig hinter der Stimme · 💡 Tipp: Die Person vorher nicht "proben" lassen — der erste, ungeplante Take klingt fast immer am nahbarsten. Lieber zweimal frei erzählen und das Echtere nehmen.</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1706,9 +1906,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Menschen im warmen, ungezwungenen Gespräch beim Kirchenkaffee (echt, kein gestelltes Gruppenfoto) · Bildaufbau/Licht: Am Fenster mit natürlichem Tageslicht fotografieren, leicht schräg von der Seite für Tiefe; Vordergrund unscharf (eine Tasse, eine Hand), Menschen im Fokus; warme, weiche Stimmung suchen · Text im Bild: "Du gehörst dazu — nicht ab dem zehnten Mal, sondern ab dem ersten Sonntag. Miodowa 21"
+💡 Tipp: Vorher die abgebildeten Personen um Einverständnis fragen. Ein Bild, auf dem niemand direkt in die Kamera schaut, wirkt natürlicher und einladender als ein Posing-Foto.</t>
+        </is>
+      </c>
       <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1764,9 +1970,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Sprechende Person direkt in die Kamera, freundlich · Sprich: "Ich sag's ehrlich: Wir sind eine kleine Gemeinde. Ganz ehrenamtlich."
+4–10s — Bild: Zwischenschnitte überschaubarer Kreis beim Gottesdienst, Gesichter beim Kaffee · Sprich: "Aber genau das ist unsere Stärke — bei uns verschwindest du nicht in der Menge."
+10–15s — Bild: Persönliche Begrüßung an der Tür, Handschlag, Lächeln · Sprich: "Hier merkt jemand, wenn du neu bist. Und freut sich, dass du da bist."
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, freundlich, leicht · 💡 Tipp: Das "klein" nicht verstecken, sondern selbstbewusst aussprechen — die ehrliche Ansage direkt in die Kamera macht genau die Nähe glaubwürdig, um die es geht.</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1822,9 +2038,19 @@
           <t>Antworte auf den Umfrage-Sticker</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~4 Story-Frames à ~5s, hochkant
+Story 1 (0–5s) — Bild: Kurzer Clip der Anreise, Straße oder Metro-Station · Text: "Ein Sonntag bei uns — los geht's" · Sticker: Standort "Warschau"
+Story 2 (0–5s) — Bild: Ankunft an der Tür Miodowa 21, Hand öffnet die Tür · Text: "Angekommen. Miodowa 21." · Sticker: Ort/Adresse
+Story 3 (0–5s) — Bild: Kurzer, respektvoller Blick in den Gottesdienst (von hinten, keine Gesichter groß) · Text: "Etwa eine Stunde: Lieder, Worte, Ruhe."
+Story 4 (0–5s) — Bild: Kirchenkaffee danach, Tassen, Gespräch · Text: "Und danach der beste Teil: Kaffee &amp; Reden." · Sticker: Umfrage "Bist du neu in Warschau?" (Ja / Noch nicht)
+💡 Tipp: Beim Filmen im Gottesdienst niemanden ungefragt frontal zeigen — von hinten oder unscharf halten. Auf den Umfrage-Sticker eingehende Antworten am selben Tag persönlich beantworten, das ist der ganze Sinn.</t>
+        </is>
+      </c>
       <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1880,9 +2106,18 @@
           <t>Schreib deine Frage in den Sticker</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~2 Story-Frames zum Start + Folge-Stories, hochkant
+Story 1 (0–5s, Aufruf) — Bild: Ruhiger Aubergine-Hintergrund oder ein warmes Foto der Tür · Text: "Neu in Warschau? Frag uns alles." · Sticker: Frage-Box mit Prompt "Was willst du über Warschau oder über uns wissen?"
+Story 2 (0–5s, Ermutigung) — Bild: Freundliches Gesicht oder Textkarte · Sprich/Text: "Keine Frage ist zu klein — wir antworten heute ehrlich in den Stories."
+Folge-Stories (im Lauf des Tages) — Bild: Person spricht direkt in die Kamera oder Textkarte; die eingegangene Frage oben einblenden · Sprich: "Deine Frage: '…' — hier unsere ehrliche Antwort: …"
+💡 Tipp: Auch simple oder skeptische Fragen ernst und warm beantworten — genau das senkt die Hemmschwelle für die stillen Mitleser, die sich sonst nie melden würden.</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1938,9 +2173,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–4s — Bild: Nahaufnahme einer Kirchenbank/eines Stuhls im warmen Licht · Sprich (leise, poetisch): "Diese Bank hat schon viele erste Male gesehen."
+4–10s — Bild: Langsamer Schwenk über die Sitzfläche, das Holz, die Maserung · Sprich: "Menschen, die unsicher Platz nahmen, nicht wussten, ob sie richtig sind — und dann einfach blieben."
+10–13s — Bild: Kamera hält still auf dem freien Platz · Sprich: "Vielleicht bist du die oder der Nächste."
+13–16s — Endcard: Lutherrose + "Der Platz ist frei · So 09:30 · Miodowa 21"
+🎵 Musik: sehr ruhig, warm, ein einzelnes Instrument, viel Raum · 💡 Tipp: Sehr langsam schwenken und wenig Text — das Reel lebt von der Ruhe. Lieber eine Zeile zu wenig sagen als eine zu viel.</t>
+        </is>
+      </c>
       <c r="M25" s="4" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1996,9 +2241,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–5s — Bild: Dunkle, kalte Warschauer Straße am Abend, Regen oder Schnee, wenige Menschen · Text: "Der Winter in Warschau ist lang"
+5–9s — Bild: Blick hoch zu einem warm erleuchteten Fenster in der dunklen Fassade · Sprich (ruhig, warm): "und wenn die Heimat weit weg ist, fühlt er sich noch länger an."
+9–15s — Bild: Schnitt in den warmen Innenraum der Gemeinde: Licht, Kaffee, Menschen · Sprich: "Aber du musst ihn nicht allein durchstehen. Bei uns ist es warm."
+15–17s — Bild: Jemand reicht eine dampfende Tasse ins Bild · Sprich: "Komm einfach rein."
+17–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, anfangs kühl/leer, beim Schnitt nach innen wärmer und voller werdend · 💡 Tipp: Draußen kalt filmen (bläulicher Weißabgleich), drinnen warm (gelbliches Licht) — dieser Farbkontrast trägt die Wende von einsam zu geborgen ganz ohne Worte.</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2054,9 +2310,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: POV beim Aussteigen aus Tram/Bus, Handy auf Brusthöhe · Text: "9:30 – so beginnt dein Sonntag"
+3–9s — Bild: ruhig durch die stillen Gassen laufen, Kamera leicht mitschwingend · Text: "Ein paar ruhige Schritte durch Warschau"
+9–15s — Bild: Ankunft an der Tür, Hausnummer 21 kurz einfangen · Text: "bis zu dieser Tür"
+15–18s — Bild: jemand öffnet, lächelt in die Kamera · Sprich: "Komm rein – schön, dass du da bist."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: Ellbogen leicht an den Körper drücken, dann wackelt der POV weniger – das wirkt ruhiger als jede App-Stabilisierung.</t>
+        </is>
+      </c>
       <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2112,9 +2379,19 @@
           <t>Adresse in Bio → Google Maps</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Foto der Altstadt-Ecke mit Pfeil-Overlay · Text: "So findest du uns – folg einfach diesen 3 Punkten."
+Slide 2: Landmark 1 im Bild · Text: "1 – an der Altstadt-Ecke. Hier geht's los."
+Slide 3: Kirchturm/markantes Gebäude · Text: "2 – am Kirchturm vorbei. Du bist auf dem richtigen Weg."
+Slide 4: Nahaufnahme Hausnummer 21 am Eingang · Text: "3 – Hausnummer 21. Du bist da."
+Slide 5: Adresse + Maps-Hinweis · Text: "ul. Miodowa 21 · So 09:30 · Maps-Link in Bio"
+💡 Tipp: Alle Fotos im Hochformat 4:5 und aus Augenhöhe knipsen – dann wirkt die Serie wie aus einem Guss und die Pfeile sitzen überall gleich.</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="3" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2170,9 +2447,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–4s — Bild: statische Aufnahme der geschlossenen Tür von außen, ruhig halten · Text: "Hinter dieser Tür"
+4–6s — Bild: Tür noch zu, kurz halten · Text: "sieht man erstmal nichts Besonderes"
+6–7s — Bild: harter Schnitt · Text: "und dann …"
+7–13s — Bild: Tür öffnet sich, Kamera gleitet langsam in den warm beleuchteten Saal, Schwenk über Stühle · Text: "ein Ort, an dem du willkommen bist"
+13–15s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, mit einem sanften Anschwellen genau beim Schnitt · 💡 Tipp: Für den harten Schnitt beide Clips an derselben Türposition starten – dann sitzt der Übergang sauber.</t>
+        </is>
+      </c>
       <c r="M29" s="4" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2228,9 +2516,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: POV im Treppenhaus, Kamera folgt den Stufen nach oben · Text: "Der letzte Meter"
+3–8s — Bild: weiter die Treppe hoch, Handkamera leicht wackelig, ganz echt · Text: "Treppe hoch"
+8–13s — Bild: den Flur entlang Richtung Saaltür · Text: "Flur entlang"
+13–16s — Bild: Tür zum Saal geht auf, Blick in den Raum · Sprich: "Und hier feiern wir Gottesdienst."
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: Lauf gleichmäßig und atme ruhig – das Wackeln darf echt sein, aber Tempo halten, sonst wirkt es hektisch statt nahbar.</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2286,9 +2585,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–5s — Bild: weite Aufnahme einer leeren Gasse im weichen Morgenlicht, Kamera ganz ruhig · Text: "Warschau um 9:00 Uhr"
+5–10s — Bild: langsamer Schwenk über stille Häuserfassaden · Text: "die Stadt schläft noch"
+10–14s — Bild: ein einzelner Fußgänger, weit weg, im Bild · (kein Text, nur Atmosphäre)
+14–16s — Bild: der Weg biegt Richtung Miodowa ab · Text: "und wir machen uns auf den Weg"
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, sehr dezent – am besten nur ein leiser Klavierteppich · 💡 Tipp: Bewusst ohne gesprochene Worte lassen – hier trägt die Stille. Filme wirklich früh, bevor Autos und Menschen die Gassen füllen.</t>
+        </is>
+      </c>
       <c r="M31" s="4" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2344,9 +2654,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~25s
+0–4s — Bild: Start am Altstadtmarkt, Person schaut in die Kamera · Sprich: "Los geht's – vom Altstadtmarkt zu uns sind es nur ein paar Minuten."
+4–12s — Bild: gehend, Handy vorne mitführend, Sehenswertes am Weg zeigen · Sprich: "Einmal hier vorbei, dann links – schau, wie schön das hier morgens ist."
+12–19s — Bild: weiter laufen, kurz aufs Handy/die Uhr zeigen · Sprich: "Sind wir keine fünf Minuten gelaufen – gleich sind wir da."
+19–23s — Bild: Ankunft an der Tür Miodowa 21 · Sprich: "Und schon sind wir da. So schnell war das."
+23–25s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, leicht beschwingt, aber leise unter der Stimme · 💡 Tipp: Halt beim Sprechen nicht an – locker weiterlaufen wirkt natürlicher; sprich etwas lauter als du denkst, Straßengeräusche schlucken die Stimme.</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2402,9 +2723,15 @@
           <t>Link in Bio → Google Maps</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: der Eingang Miodowa 21 frontal, mit gut sichtbarer Hausnummer · Bildaufbau/Licht: gerade von vorn auf Augenhöhe, Kamera parallel zur Fassade halten (keine kippenden Linien), weiches Tageslicht am Vormittag, Hausnummer im oberen Drittel · ggf. Text im Bild: "Miodowa 21 – Adresse zum Merken"
+💡 Tipp: Nutz das Gitternetz der Kamera und richte die Türkanten daran aus – ein gerades Bild wirkt sofort seriöser und würdevoller als ein leicht schiefes.</t>
+        </is>
+      </c>
       <c r="M33" s="4" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2460,9 +2787,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Kamera setzt langsam am Eingang des leeren Saals an · Text: "Kurz bevor alle kommen"
+4–10s — Bild: ruhiger, langsamer horizontaler Schwenk über Stühle und Tisch · Text: "steht der Saal noch still"
+10–14s — Bild: Detail auf Kerze oder warmes Licht auf dem Tisch · Text: "gedeckt und bereit"
+14–16s — Bild: sanftes Verweilen auf dem Licht · Text: "für dich"
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, andächtig, ohne Kitsch · 💡 Tipp: Schwenke extra langsam und gleichmäßig – zähl innerlich mit; ein zu schneller Schwenk zerstört die andächtige Stimmung sofort.</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -2518,9 +2856,15 @@
           <t>Folg uns für die ganze Serie</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: derselbe markante Wegpunkt auf dem Weg zur Kirche, aus immer gleichem Winkel · Bildaufbau/Licht: feste Kameraposition merken (Standpunkt mit Fußmarkierung oder Referenzobjekt im Bild), gleicher Ausschnitt und gleiche Augenhöhe pro Jahreszeit, weiches Tageslicht · ggf. Text im Bild: "Vier Jahreszeiten – ein Weg zur selben Tür"
+💡 Tipp: Mach beim ersten Foto einen Screenshot als Overlay-Referenz – so triffst du Monate später exakt denselben Ausschnitt und die Serie wirkt wie aus einer Kamera.</t>
+        </is>
+      </c>
       <c r="M35" s="4" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2576,9 +2920,19 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~14s
+0–4s — Bild: POV nähert sich der Tür Miodowa 21 · Text: "Mitten in Warschau"
+4–8s — Bild: Person am Eingang schaut auf, lächelt · Text: "ein Ort, wo Deutsch klingt"
+8–12s — Bild: die Person direkt in die Kamera · Sprich: "Schön, dass du da bist." (dazu kurzer Handschlag oder herzliche Geste)
+12–14s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, leise – die Stimme muss klar im Vordergrund stehen · 💡 Tipp: Den O-Ton wirklich sprechen lassen, nicht nachstellen; nimm ruhig zwei, drei Takes, bis das Lächeln echt und entspannt ist.</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2634,9 +2988,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: der Blick aus einem alten Fenster des Gebäudes hinaus auf die Stadt (oder ein anderes stilles Detail wie ein abgegriffener Handlauf) · Bildaufbau/Licht: nah rangehen, das Fenster als Rahmen nutzen (der dunkle Fensterrahmen umschließt den hellen Ausblick), weiches Seitenlicht, auf den Ausblick scharfstellen · ggf. Text im Bild: "Eine Ecke, die kaum jemand kennt"
+💡 Tipp: Tippe zum Scharfstellen bewusst auf den hellen Ausblick und zieh die Belichtung etwas runter – sonst überstrahlt das Fensterlicht und der Blick verschwindet im Weiß.</t>
+        </is>
+      </c>
       <c r="M37" s="4" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2692,9 +3052,19 @@
           <t>Speichern → Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Foto der Tram/Bus-Linie oder des Haltestellenschilds · Text: "Mit dem Tram zur Kirche – so einfach geht's."
+Slide 2: Nahaufnahme der Liniennummer / Anzeige · Text: "1 – diese Linie nehmen."
+Slide 3: Foto des Ausstiegspunkts mit Orientierungspunkt im Bild · Text: "2 – hier aussteigen."
+Slide 4: Foto des Fußwegs von der Haltestelle · Text: "3 – zwei Minuten zu Fuß."
+Slide 5: Ankunftsfoto an der Tür Miodowa 21 · Text: "4 – angekommen. ul. Miodowa 21 · So 09:30"
+💡 Tipp: Prüf die Liniennummer vor dem Posten noch mal im WTP-Fahrplan, damit die Info wirklich stimmt – eine falsche Tram-Nummer ärgert genau die Neuankömmlinge, denen du helfen willst.</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2750,9 +3120,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~5s (nahtloser Loop)
+0–1.5s — Bild: Nahaufnahme der Türklinke · Text: "3 Sekunden"
+1.5–3s — Bild: Hand drückt die Klinke herunter, Tür öffnet sich · Text: "Tür auf"
+3–5s — Bild: warmes Licht dahinter wird sichtbar, Kamera hält kurz · Text: "willkommen"
+(Loop: letztes Bild wieder auf die geschlossene Klinke schneiden, damit es nahtlos von vorn läuft)
+🎵 Musik: leise, warm, ein kurzes Motiv das sich wiederholt · 💡 Tipp: Kamera auf ein Stativ oder eine feste Fläche legen – für einen sauberen Loop muss der Bildausschnitt am Anfang und Ende exakt gleich sein.</t>
+        </is>
+      </c>
       <c r="M39" s="4" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2808,9 +3188,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~25s
+0–5s — Bild: Person vor der eigenen Haustür, schaut in die Kamera · Sprich: "Hi, ich bin's – und das ist mein Weg zur Kirche, den ich jeden zweiten Sonntag gehe."
+5–13s — Bild: der echte Weg durch die Stadt, ehrlich mitgefilmt · Sprich: "Für mich ist das schon fast ein kleines Ritual – die Stadt ist noch ruhig, und ich komme dabei runter."
+13–20s — Bild: weiter unterwegs, näher an der Miodowa · Sprich: "Und am Ende warten Leute, mit denen ich mich einfach wohlfühle. Deshalb mag ich ihn."
+20–23s — Bild: Ankunft an der Tür, zufriedenes Lächeln · Sprich: "Und da sind wir. Vielleicht wird's ja bald auch dein Weg."
+23–25s — Endcard: Lutherrose + "So 09:30 · Miodowa 21 · WhatsApp-Gruppe in Bio"
+🎵 Musik: warm, persönlich, sehr leise unter der Stimme · 💡 Tipp: Lass die Person wirklich frei erzählen statt abzulesen – ein, zwei kleine Versprecher machen es glaubwürdiger als ein perfekter Werbetext.</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2866,9 +3257,18 @@
           <t>Speichern → Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Foto einer nahen Parkmöglichkeit · Text: "Parken &amp; Ankommen – mit dem Auto ganz entspannt."
+Slide 2: dieselbe Parkmöglichkeit mit Hinweis/Orientierung · Text: "Hier parkst du – nah und unkompliziert."
+Slide 3: Foto des Fußwegs vom Parkplatz Richtung Miodowa · Text: "So kurz ist es zu Fuß."
+Slide 4: Foto des Eingangs mit Erkennungsmerkmal · Text: "Daran erkennst du den Eingang. ul. Miodowa 21 · So 09:30"
+💡 Tipp: Fotografiere den Parkplatz zur gleichen Uhrzeit wie den Gottesdienst (So früh), damit die gezeigte Parksituation realistisch ist – sonntags ist meist deutlich mehr frei als werktags.</t>
+        </is>
+      </c>
       <c r="M41" s="4" t="inlineStr"/>
-      <c r="N41" s="5" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2924,9 +3324,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–4s — Bild: POV unter dem Regenschirm, Blick auf nasse Pflastersteine · Text: "Regen ist kein Grund zu bleiben"
+4–8s — Bild: Regentropfen und graue Straße einfangen · Text: "draußen grau und nass"
+8–11s — Bild: Ankunft an der Tür, Schirm zuklappen · Text: "drinnen warm und geborgen"
+11–14s — Bild: Schnitt ins warme, helle Innere · Sprich: "Komm rein – hier ist's trocken und warm."
+14–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, ein Hauch geborgen; beim Schnitt nach innen leicht wärmer werden · 💡 Tipp: Wisch die Linse vor jedem Take kurz trocken – ein Wassertropfen auf dem Objektiv verwischt sonst das ganze Bild.</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="3" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2982,9 +3393,18 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – und bleib danach</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Foto eines netten Cafés in der Nähe · Text: "Rund um die Miodowa – bleib nach dem Gottesdienst noch ein bisschen."
+Slide 2: dasselbe Café gemütlich im Bild · Text: "Ein Café für danach – gleich um die Ecke."
+Slide 3: Foto einer kleinen Buchhandlung · Text: "Eine kleine Buchhandlung zum Stöbern."
+Slide 4: Foto eines schönen Platzes im Viertel · Text: "Ein Platz zum Verweilen. Komm So 09:30, Miodowa 21 – und bleib danach."
+💡 Tipp: Frag die Café- oder Ladenbesitzer kurz, ob du sie zeigen darfst, und verlink sie im Post – das schafft Wohlwollen im Viertel und die verlinkten Orte teilen euch oft in ihrer Story.</t>
+        </is>
+      </c>
       <c r="M43" s="4" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3040,9 +3460,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–4s — Bild: POV startet an der offenen Eingangstür · Text: "Von der Tür"
+4–9s — Bild: weiter durch den Flur in den Saal, ruhige Schritte · Text: "bis zu deinem Platz"
+9–13s — Bild: Kamera geht auf einen freien Stuhl zu, setzt sich, Blick nach vorn · Sprich: "Hier ist auch Platz für dich."
+13–15s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: Senk die Kamera am Ende sanft auf Sitzhöhe ab, wenn der Stuhl "eingenommen" wird – diese kleine Bewegung macht das "du sitzt jetzt hier"-Gefühl körperlich spürbar.</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="3" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -3098,9 +3528,21 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L45" s="4" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–5s — Bild: Abendaufnahme der belebten Straße, Lichter und Bewegung · Text: "Warschau bei Nacht"
+5–7s — Bild: noch die laute Abendszene · Text: "laut und in Bewegung"
+7–8s — Bild: harter Schnitt auf denselben Ort am Sonntagmorgen · (Übergang)
+8–13s — Bild: gleicher Bildausschnitt, jetzt still und leer · Text: "dieselbe Ecke am Sonntag – still"
+13–15s — Bild: sanfter Schwenk auf die Kirchentür · Text: "und wir sind da"
+15–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: abends treibend/lebendig, beim Schnitt abrupt in Ruhe kippen – der Musikbruch verstärkt den Kontrast · 💡 Tipp: Filme beide Clips vom exakt gleichen Standpunkt (Fußmarkierung merken), sonst geht der Aha-Effekt des Vorher-Nachher verloren.</t>
+        </is>
+      </c>
       <c r="M45" s="4" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -3156,9 +3598,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: scharfe Nahaufnahme des Klingel- bzw. Hinweisschilds am Eingang, Schrift gut lesbar · Bildaufbau/Licht: frontal und gerade auf das Schild, gutes Tageslicht ohne harte Schatten oder Blitz-Reflexe, Schild mittig oder im oberen Drittel · ggf. Text im Bild: "Das Schild, nach dem du suchst – hier klingelst du richtig."
+💡 Tipp: Achte auf Spiegelungen auf glänzenden Schildern – geh leicht seitlich zur Sonne, bis keine Reflexe die Schrift überdecken, dann wieder gerade ausrichten.</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -3214,9 +3662,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~17s
+0–4s — Bild: jemand kommt herein und legt die Jacke ab · Text: "5 Minuten früher da"
+4–8s — Bild: kurzes, leises Gespräch zwischen zwei Personen · Text: "ein leises Hallo"
+8–12s — Bild: eine Tasse Kaffee wird eingeschenkt · Text: "ein Kaffee, bevor es beginnt"
+12–15s — Bild: ruhiger Blick in den sich langsam füllenden Saal · Sprich: "Diese Ruhe vorher – die gehört dir auch."
+15–17s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, leise, gemütlich – wie ein Sonntagmorgen · 💡 Tipp: Halt jede Szene 3–4 Sekunden ruhig; kurze hektische Schnitte zerstören genau die entspannte Vor-Gottesdienst-Stimmung, die du zeigen willst.</t>
+        </is>
+      </c>
       <c r="M47" s="4" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -3272,9 +3731,20 @@
           <t>Bis in zwei Wochen – Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–4s — Bild: POV von innen, Tür öffnet sich nach draußen ins Sonntagslicht · Text: "Der Weg zurück"
+4–8s — Bild: Schritt hinaus ins helle Licht · Text: "Tür auf ins Sonntagslicht"
+8–12s — Bild: jemand winkt zum Abschied · Sprich: "Bis in zwei Wochen!"
+12–14s — Bild: Blick zurück auf die Tür beim Weggehen · Text: "der Ort bleibt – du kommst wieder"
+14–16s — Endcard: Lutherrose + "Bis in zwei Wochen · So 09:30 · Miodowa 21"
+🎵 Musik: warm, leicht wehmütig-hoffnungsvoll, sanftes Ausklingen · 💡 Tipp: Beim Schritt von drinnen nach draußen tippt die Kamera-Belichtung oft über – geh langsam durch die Tür, dann gleicht das Handy die Helligkeit weicher aus.</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="3" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -3330,9 +3800,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: kurzer POV-Weg-Clip Richtung Miodowa, ruhige Schritte · Text: "Neu in Warschau?"
+4–9s — Bild: weiter auf dem Weg, weiches Licht · Text: "Wir sind nur einen Weg entfernt"
+9–14s — Bild: Ankunft an der Tür, freundliche Geste ins Bild · Sprich: "Du musst niemanden kennen, um zu kommen."
+14–16s — Bild: freundliches Winken / offene Tür · Text: "Schreib uns in der WhatsApp-Gruppe"
+16–18s — Endcard: Lutherrose + "WhatsApp-Gruppe in Bio · So 09:30 · Miodowa 21"
+🎵 Musik: warm, einladend, dezent · 💡 Tipp: Sprich den Kernsatz "Du musst niemanden kennen" ruhig und direkt in die Kamera – genau dieser eine Satz nimmt die Hemmschwelle, gib ihm Zeit.</t>
+        </is>
+      </c>
       <c r="M49" s="4" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -3388,9 +3869,18 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Nahaufnahme von altem Holz / einer Maserung · Text: "Die Miodowa im Detail"
+Slide 2: Detail eines alten Türgriffs · Text: "altes Holz, ein abgegriffener Türgriff"
+Slide 3: Lichtreflexe auf einer Oberfläche · Text: "Licht, das durchs Fenster fällt"
+Slide 4: eine brennende Kerze, weich · Text: "und eine Kerze. Spür der Stimmung nach – So 09:30, Miodowa 21."
+💡 Tipp: Halte alle vier Fotos in derselben warmen, gedämpften Bildstimmung (gleiche Belichtung, kein Blitz) – so wirkt das Carousel wie ein zusammengehöriges kleines Gedicht statt vier zufälliger Schnappschüsse.</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="3" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -3446,9 +3936,20 @@
           <t>Link in Bio → WhatsApp-Gruppe · Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L51" s="4" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: ruhiges POV, Start irgendwo in der Stadt · Sprich: "Stell dir vor, du gehst diesen Weg."
+4–10s — Bild: gleichmäßige Schritte Richtung Miodowa, weiches Licht · Text: "ein paar ruhige Schritte"
+10–14s — Bild: Ankunft vor der Tür, kurz innehalten · Text: "bis zu einer offenen Tür"
+14–16s — Bild: Blick auf die offene Tür, Bild beginnt zu verblassen · Text: "Nächsten Sonntag mit dabei?"
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21 · WhatsApp-Gruppe in Bio"
+🎵 Musik: ruhig, warm, offen ausklingend – nicht auflösen, damit die Frage nachhallt · 💡 Tipp: Lass die letzte Frage 2 Sekunden allein auf ruhigem Bild stehen, bevor die Endcard kommt – ein sanfter offener Schluss lädt eher zum Antworten ein als ein harter CTA.</t>
+        </is>
+      </c>
       <c r="M51" s="4" t="inlineStr"/>
-      <c r="N51" s="5" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3504,9 +4005,20 @@
           <t>Folg uns für dein wöchentliches Wort – oder komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Du am Fenster mit Morgenlicht, Handy auf Augenhöhe, kurz in die Kamera lächeln · Sprich: "Hey, guten Morgen – neue Woche."
+3–8s — Bild: Ruhig bleiben, freundlich in die Kamera · Sprich: "Ein Wort begleitet uns diese Woche:"
+8–14s — Bild: Kurze Pause, dann den Vers ruhig sprechen · Sprich: "[Vers der Woche wörtlich]."
+14–18s — Bild: Persönlich, ehrlich · Sprich: "Für mich heißt das heute: Ich muss nicht alles allein schaffen."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Hab eine gute Woche."
+🎵 Musik: ruhig/warm/dezent im Hintergrund · 💡 Tipp: Ein einziger Take ohne Schnitt wirkt am nahbarsten – lieber dreimal neu starten als hart schneiden. Untertitel nicht vergessen.</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="3" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -3562,9 +4074,19 @@
           <t>Speichern &amp; mitnehmen – mehr davon: folg uns</t>
         </is>
       </c>
-      <c r="L53" s="4" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s (ohne Stimme, nur Text)
+0–4s — Bild: Blick aus dem Fenster über den grauen Warschauer Morgen, Handy ganz ruhig · Text: "Ein Segen für deinen Tag"
+4–8s — Bild: Gleiche Einstellung, leichte Wolkenbewegung · Text: "Gott behüte deine Wege"
+8–12s — Bild: Weiter statisch, evtl. ein Vogel/Licht das sich ändert · Text: "und schenke dir Ruhe im Trubel"
+12–15s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Amen"
+🎵 Musik: sehr leise, warm, getragen · 💡 Tipp: Handy an die Fensterscheibe lehnen oder auf ein Buch stützen für einen absolut ruhigen Bild – kein Zittern. Text langsam einblenden, damit man ihn in Ruhe lesen kann.</t>
+        </is>
+      </c>
       <c r="M53" s="4" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3620,9 +4142,15 @@
           <t>Teil den Post mit jemandem, an den du gerade denkst</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Schlichte Textkarte in Aubergine (#480048), quadratisch, viel ruhiger Weißraum um die Frage herum · Bildaufbau/Licht: Frage groß und zentriert in heller, klarer Schrift; oben klein der Zusatz "Frag dich das heute:", unten dezent Logo/Gemeindename – nichts überladen, damit die Frage atmen kann · Text im Bild: "Wem könntest du heute schreiben, nur um zu fragen: Wie geht's dir wirklich?"
+💡 Tipp: In Canva ein festes Serien-Template anlegen (gleiche Schrift, gleiche Position), dann sind alle künftigen Frage-Posts in 2 Minuten gebaut und sofort als Reihe wiedererkennbar.</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="3" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -3678,9 +4206,20 @@
           <t>Folg uns für mehr Worte für unterwegs</t>
         </is>
       </c>
-      <c r="L55" s="4" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–3s — Bild: Du gehst durch Park oder Straße, Handy in Selfie-Haltung, Stadt im Hintergrund · Sprich: "Kommst du kurz mit? Ein Psalm für unterwegs."
+3–8s — Bild: Weiter im Gehen, ruhiger Blick · Sprich: "[Psalmvers 1 wörtlich]."
+8–13s — Bild: Ampel, Tram oder Menschen ziehen vorbei · Sprich: "[Psalmvers 2 wörtlich]."
+13–19s — Bild: Ruhiger Moment, evtl. stehenbleiben · Sprich: "[Psalmvers 3 wörtlich]."
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Nimm sie mit in deinen Weg."
+🎵 Musik: keine oder sehr dezent – Stadtgeräusche bewusst mitlaufen lassen · 💡 Tipp: Handy leicht kippen und den Ellbogen an den Körper drücken, damit das Bild beim Gehen nicht wackelt. Untertitel sind hier Pflicht, weil im Freien der Ton unruhig ist.</t>
+        </is>
+      </c>
       <c r="M55" s="4" t="inlineStr"/>
-      <c r="N55" s="5" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3736,9 +4275,19 @@
           <t>Folg uns für deine tägliche Portion Ermutigung</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–4s — Bild: Nahaufnahme dampfende Kaffeetasse neben aufgeschlagener Bibel, warmes Morgenlicht, langsamer Schwenk über den Tisch · Sprich (Off): "Erst mal ein Kaffee. Und ein guter Gedanke dazu."
+4–9s — Bild: Näher ran an die Bibelseite, Finger blättert sanft · Sprich (Off): "[kurzer Ermutigungsvers wörtlich]."
+9–13s — Bild: Tasse wird gehoben oder Dampf steigt auf · Sprich (Off): "Was auch kommt heute – du bist nicht allein damit."
+13–15s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Guten Start in den Tag"
+🎵 Musik: warm, gemütlich, sehr leise unter der Stimme · 💡 Tipp: Nimm die Off-Stimme separat und leise in einem ruhigen Raum auf – das klingt intimer als direkt beim Filmen. Echtes Morgenlicht am Fenster schlägt jede Lampe.</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="3" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -3794,9 +4343,20 @@
           <t>Teil deine Geschichte mit uns – Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L57" s="4" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~50s
+0–5s — Bild: Person sitzt ruhig, Handy auf Augenhöhe, schaut direkt in die Kamera · Sprich: "Ich sag's mal ehrlich – das war keine leichte Woche für mich."
+5–20s — Bild: Gleiche Einstellung, ruhig erzählen · Sprich: "[Kurz und konkret der schwere Moment – ehrlich, ohne Drama, ein bis zwei Sätze]."
+20–35s — Bild: Weiter im Take, etwas ruhiger werden · Sprich: "Und dann war da dieser eine Gedanke, der mich wieder aufgerichtet hat:"
+35–46s — Bild: Kurze Pause, dann den Vers/Gedanken benennen · Sprich: "[Vers oder Gedanke wörtlich] – das hat mich getragen."
+46–50s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Was hat dich diese Woche getragen?"
+🎵 Musik: sehr dezent oder gar keine – die Stimme trägt das Reel · 💡 Tipp: Ein einziger, unpolierter Take ist hier Gold wert – kleine Pausen und ein Stocken machen es glaubwürdig, nicht schlechter. Nicht auswendig lernen, frei erzählen.</t>
+        </is>
+      </c>
       <c r="M57" s="4" t="inlineStr"/>
-      <c r="N57" s="5" t="inlineStr"/>
+      <c r="N57" s="4" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3852,9 +4412,18 @@
           <t>Speichern &amp; durchwischen – folg uns für mehr</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: "Übersetzt." – Titel groß, darunter klein: "Alte Bibelworte, in dein Heute übersetzt. Wisch weiter →"
+Slide 2: Oben "So steht's da:" mit dem Originalvers [Vers wörtlich]. Unten "Heißt konkret:" – "Du bist nicht allein in dieser Stadt, auch wenn's sich gerade so anfühlt."
+Slide 3: Oben "So steht's da:" mit einem zweiten Vers [Vers wörtlich]. Unten "Heißt konkret:" – "Du musst nicht alles im Griff haben, um dazuzugehören."
+Slide 4: Sanfte Einladung – "Solche Worte hörst du bei uns jeden Sonntag. 09:30 · Miodowa 21. Kein Druck – komm einfach vorbei."
+💡 Tipp: Original und Übersetzung optisch klar trennen (z. B. Original in Aubergine oben, Deutung in hellem Feld unten), damit man auf einen Blick versteht, was gemeint ist.</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="3" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -3910,9 +4479,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – dein Platz ist frei</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Ein einzelner leerer Stuhl im Synodalsaal, leicht seitlich fotografiert, sodass Licht auf die Sitzfläche fällt · Bildaufbau/Licht: Warmes, weiches Seitenlicht (Fensterlicht am besten), aufgeräumter, ruhiger Hintergrund; der Stuhl klar im Fokus, drumherum Raum lassen – die Leere ist die Botschaft · Text im Bild: "Ein Platz ist frei. Vielleicht deiner." – dezent, unten oder in einer ruhigen Bildecke, plus kleines Logo
+💡 Tipp: Etwas unterhalb der Augenhöhe fotografieren und den Stuhl leicht aus der Bildmitte rücken (Drittel-Regel) – das wirkt einladend statt symmetrisch-steif. Kein Blitz, nur natürliches Licht.</t>
+        </is>
+      </c>
       <c r="M59" s="4" t="inlineStr"/>
-      <c r="N59" s="5" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3968,9 +4543,20 @@
           <t>Schreib deine drei Dinge in die Kommentare</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Du in Selfie-Haltung, spontan und locker, natürliche Umgebung · Sprich: "Drei Dinge, für die ich heute echt dankbar bin – ganz spontan."
+4–9s — Bild: Ein Finger hoch, lächeln · Sprich: "Erstens: der erste Kaffee, als draußen alles noch grau war."
+9–13s — Bild: Zweiter Finger · Sprich: "Zweitens: eine Nachricht von jemandem, den ich mag."
+13–17s — Bild: Dritter Finger · Sprich: "Und drittens: dass heute einfach nichts kaputtgegangen ist."
+17–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Und du? Schreib deine drei in die Kommentare."
+🎵 Musik: leicht, warm, unaufdringlich · 💡 Tipp: Die drei Dinge klein und echt halten – je alltäglicher, desto mehr fühlen sich andere eingeladen, mitzumachen. Nicht perfekt aufsagen, ruhig spontan wirken.</t>
+        </is>
+      </c>
       <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="3" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -4026,9 +4612,15 @@
           <t>Speichern &amp; sammeln – folg uns für die ganze Serie</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Bildschirmfüllende Textkarte in Aubergine (#480048), das Gebet als einziges Element groß und mittig · Bildaufbau/Licht: Ein einzelner Satz zentriert, viel Ruhe drumherum, klare helle Schrift; oben klein die Serien-Markierung "Gebet in einem Satz", unten dezent der Gemeindename · Text im Bild: "Gott, hilf mir, heute freundlich zu sein."
+💡 Tipp: Ein festes Serien-Layout definieren (immer gleiche Schriftgröße, Position, Farbe) – so erkennt man die Reihe im Feed sofort wieder und Follower sammeln die Karten gern.</t>
+        </is>
+      </c>
       <c r="M61" s="4" t="inlineStr"/>
-      <c r="N61" s="5" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -4084,9 +4676,18 @@
           <t>Antworte anonym über den Sticker</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~12s (Story)
+0–4s — Bild: Ruhiger, warmer Hintergrund (Fenster, Kerze oder aubergine Fläche), Frage-Sticker platziert · Text: "Wo war Gott heute für dich?"
+4–8s — Bild: Gleicher Hintergrund, Blick auf den Sticker lenken (Pfeil/Emoji) · Text: "Erzähl uns einen kleinen guten Moment – anonym &amp; ehrlich"
+8–12s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Die schönsten teilen wir morgen hier"
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: Den Frage-Sticker mittig und groß platzieren, damit der Daumen ihn sofort trifft. Wichtig: Bei jeder Antwort, die du reposten willst, vorher per DM um Erlaubnis fragen und immer anonymisieren.</t>
+        </is>
+      </c>
       <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="3" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -4142,9 +4743,19 @@
           <t>Link in Bio → WhatsApp-Gruppe für den ersten Kontakt</t>
         </is>
       </c>
-      <c r="L63" s="4" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Du warm und ruhig in die Kamera, Selfie-Haltung, weicher Hintergrund · Sprich: "Kurz an alle, die gerade Heimweh haben:"
+4–10s — Bild: Ehrlich, nah · Sprich: "Fremd in einer neuen Stadt zu sein, ist echt schwer. Das darf man auch mal sagen."
+10–16s — Bild: Ruhiger werden, den Vers als Anker · Sprich: "Aber in der Bibel steht ein Satz, der mich da trägt: 'Ich bin bei dir, wohin du auch gehst.'"
+16–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Du bist nicht allein."
+🎵 Musik: ruhig, warm, tröstend · 💡 Tipp: Direkt in die Linse sprechen, nicht aufs Display schauen – so entsteht echter Blickkontakt, der bei diesem Thema Nähe schafft. Untertitel für die stillen Abend-Scroller.</t>
+        </is>
+      </c>
       <c r="M63" s="4" t="inlineStr"/>
-      <c r="N63" s="5" t="inlineStr"/>
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -4200,9 +4811,15 @@
           <t>Zeig uns dein Warschau-Bild in den Kommentaren</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr"/>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Ein echtes Alltagsfoto aus Warschau – z. B. eine Tram im Regen, die Weichsel im Abendlicht oder eine nasse Straße mit Spiegelungen · Bildaufbau/Licht: Stimmungsvolles Licht bewusst nutzen (Regen, Dämmerung, Gegenlicht); ein klares Hauptmotiv, ruhiger Bildaufbau – die Reflexion kommt in die Caption, nicht ins Bild · Text im Bild: dezent oben "Ein Bild sagt mehr", der geistliche Gedanke bleibt bewusst in der Bildunterschrift, z. B. "Warschau im Regen – und der Gedanke: Auch graue Tage haben ihren eigenen Glanz."
+💡 Tipp: Auf das Handy tippen, um scharf auf das Hauptmotiv zu stellen, dann die Belichtung leicht runterziehen – Regen- und Abendbilder wirken so viel atmosphärischer als überbelichtet.</t>
+        </is>
+      </c>
       <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="3" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -4258,9 +4875,20 @@
           <t>Speichern für einen schweren Tag – folg uns für mehr</t>
         </is>
       </c>
-      <c r="L65" s="4" t="inlineStr"/>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Ruhig in die Kamera, warmes Licht, ehrliche Ansprache · Sprich: "Liegt diese Woche auch so schwer auf dir?"
+4–9s — Bild: Nah, ruhig bleiben · Sprich: "Dann darf ich dir kurz was sagen: Erschöpft zu sein ist okay. Wirklich."
+9–14s — Bild: Warm, ohne Beschönigung · Sprich: "Du musst hier nicht stark tun. Nicht alles muss ein Erfolg sein."
+14–18s — Bild: Ruhiger werden, Vers dagegensetzen · Sprich: "'Kommt her zu mir, ihr Mühseligen – ich will euch Ruhe geben.'"
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Sei heute freundlich zu dir."
+🎵 Musik: ruhig, warm, tröstend · 💡 Tipp: Bewusst langsam und leise sprechen – bei diesem Thema wirkt Ruhe glaubwürdiger als Energie. Keine schnellen Schnitte, kein aufmunternder Ton, der über die Erschöpfung hinweggeht.</t>
+        </is>
+      </c>
       <c r="M65" s="4" t="inlineStr"/>
-      <c r="N65" s="5" t="inlineStr"/>
+      <c r="N65" s="4" t="inlineStr"/>
+      <c r="O65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -4316,9 +4944,18 @@
           <t>Speichern &amp; durchwischen – folg uns für mehr Luther heute</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: "Luther heute." – groß, darunter das Zitat in Anführungszeichen: "[Lutherzitat wörtlich]." Klein unten: "Wisch weiter →"
+Slide 2: Überschrift "Was er meinte:" – 1–2 kurze Sätze in Alltagssprache, was Luther damit sagen wollte, ohne Fachbegriffe.
+Slide 3: Überschrift "Für deinen Alltag heißt das:" – eine ganz konkrete heutige Situation, z. B. "Du musst dir Gottes Zuneigung nicht verdienen – auch nicht an dem Tag, an dem du das Gefühl hast, nichts geschafft zu haben."
+Slide 4: Einladung – "Solche Gedanken teilen wir sonntags. 09:30 · Miodowa 21. Welches Lutherwort sollen wir als Nächstes erklären?"
+💡 Tipp: Zitat immer wörtlich und mit Quelle prüfen, bevor du es postest – lieber ein gesichertes Kurzzitat als ein hübsches, das Luther nie gesagt hat. Einheitliches Farbschema über alle Slides.</t>
+        </is>
+      </c>
       <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="3" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -4374,9 +5011,15 @@
           <t>Antworte in den Kommentaren – jede Woche neu</t>
         </is>
       </c>
-      <c r="L67" s="4" t="inlineStr"/>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Quadratische Textkarte im festen Serien-Design (Gemeindefarben, Aubergine), die Frage als Hauptelement · Bildaufbau/Licht: Frage groß und zentriert, viel ruhiger Raum drumherum; oben klein und immer gleich der Serien-Titel "Die Frage der Woche", unten dezent das Logo – so wird die Reihe im Feed sofort erkannt · Text im Bild: "Wann hast du zuletzt jemandem verziehen?"
+💡 Tipp: Ein einziges Master-Template bauen und wöchentlich nur die Frage austauschen – gleiche Schrift, gleiche Position, gleiche Farbe. Konsistenz macht aus Einzelposts eine wiedererkennbare Serie.</t>
+        </is>
+      </c>
       <c r="M67" s="4" t="inlineStr"/>
-      <c r="N67" s="5" t="inlineStr"/>
+      <c r="N67" s="4" t="inlineStr"/>
+      <c r="O67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -4432,9 +5075,20 @@
           <t>Speichern für eine kleine Pause – folg uns für mehr Ruhe</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~30s (ohne Stimme, nur Text)
+0–8s — Bild: Ruhiges Motiv, z. B. eine flackernde Kerze oder Regen am Fenster, ganz statisch · Text: "Stille für 30 Sekunden"
+8–16s — Bild: Gleiches Motiv, nichts passiert – das ist gewollt · Text: "Atme."
+16–24s — Bild: Weiter ruhig, evtl. leichte Bewegung (Flamme, Wasser) · Text: "Du musst gerade nichts leisten."
+24–28s — Bild: Ruhiger Ausklang · Text: "Einfach nur sein."
+28–30s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: gar keine oder ein einzelner, sehr leiser Klang · 💡 Tipp: Bewusst NICHT schneiden – ein einziger langer, ruhiger Take ist der ganze Sinn. Text sehr langsam ein- und ausblenden, damit auch das Lesen entschleunigt.</t>
+        </is>
+      </c>
       <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="3" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -4490,9 +5144,20 @@
           <t>Folg uns für mehr Glauben im Gewöhnlichen</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr"/>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–4s — Bild: Nahaufnahme Hände, die Brot schneiden, warmes Licht · Sprich (Off): "Schau mal auf deine Hände."
+4–9s — Bild: Hände öffnen eine Tür, Schlüssel im Schloss · Sprich (Off): "Türen öffnen. Brot schneiden. Kleine Dinge, den ganzen Tag."
+9–15s — Bild: Hände falten sich langsam zum Gebet · Sprich (Off): "Und manchmal falten sie sich ganz von selbst."
+15–19s — Bild: Ruhige Nahaufnahme ruhender Hände · Sprich (Off): "Gott ist genau da nah – im ganz Konkreten. Auch in deinen Händen heute."
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, getragen unter der Off-Stimme · 💡 Tipp: Jeden Hand-Clip ruhig 3–4 Sek. laufen lassen und aus nächster Nähe filmen – weiches Fensterlicht von der Seite macht Haut und Bewegung schön plastisch. Off-Stimme separat und leise aufnehmen.</t>
+        </is>
+      </c>
       <c r="M69" s="4" t="inlineStr"/>
-      <c r="N69" s="5" t="inlineStr"/>
+      <c r="N69" s="4" t="inlineStr"/>
+      <c r="O69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -4548,9 +5213,20 @@
           <t>Verrate uns deinen Vers – folg uns für die ganze Serie</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~30s
+0–4s — Bild: Person sitzt ruhig, Handy auf Augenhöhe, freundlicher Blick in die Kamera · Sprich: "Es gibt diesen einen Vers, der mich einfach nicht loslässt."
+4–11s — Bild: Gleiche Einstellung, ruhig · Sprich: "Mein Lieblingsvers ist: '[Vers wörtlich].'"
+11–24s — Bild: Persönlich werden, etwas erzählen · Sprich: "[Kurz und ehrlich, warum genau dieser – eine Situation, in der er getragen hat, zwei bis drei Sätze]."
+24–27s — Bild: Warm, offen · Sprich: "Und du – welcher Vers begleitet dich?"
+27–30s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Verrate uns deinen Vers"
+🎵 Musik: sehr dezent, warm · 💡 Tipp: Als Serie über Wochen immer im gleichen Bildaufbau drehen (gleicher Ausschnitt, gleicher Untertitel-Stil), nur die Person wechselt – so wird aus vielen Einzel-Reels eine wiedererkennbare Porträtreihe.</t>
+        </is>
+      </c>
       <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="3" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -4606,9 +5282,18 @@
           <t>Komm morgen 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L71" s="4" t="inlineStr"/>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~12s (Story, Samstagabend)
+0–4s — Bild: Warmes Abendmotiv (Kerze, Fenster in der Dämmerung) oder ruhige Textkarte in Aubergine · Text: "Sonntagvorfreude"
+4–8s — Bild: Gleiche Stimmung, sanft · Text: "Morgen ist Gottesdienst – ein ruhiger Start in den Sonntag"
+8–12s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Ein Platz ist für dich frei. Wir freuen uns auf dich."
+🎵 Musik: warm, ruhig, dezent · 💡 Tipp: Nur an tatsächlichen Gottesdienst-Sonntagen posten (2×/Monat) – lieber eine Story weniger als eine falsche Erwartung wecken. Am frühen Samstagabend planen, wenn die Leute aufs Handy schauen.</t>
+        </is>
+      </c>
       <c r="M71" s="4" t="inlineStr"/>
-      <c r="N71" s="5" t="inlineStr"/>
+      <c r="N71" s="4" t="inlineStr"/>
+      <c r="O71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -4664,9 +5349,19 @@
           <t>Folg uns für mehr Theologie im Kleinen</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Du hältst einen Regenschirm in die Kamera, natürliche Umgebung · Sprich: "Ein Regenschirm. Ganz banal, oder?"
+4–10s — Bild: Schirm kurz auf- und zuklappen, zeigen · Sprich: "Den nimmt man mit, bevor es regnet – nicht erst, wenn man schon nass ist."
+10–16s — Bild: Ruhiger, direkter Blick · Sprich: "Und manchmal ist Glaube genau das: ein Schutz, den man schon dabeihat, bevor der schwere Tag kommt."
+16–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Kleine Theologie des Alltags"
+🎵 Musik: leicht, warm, mit einem kleinen Augenzwinkern · 💡 Tipp: Die überraschende Wendung erst spät bringen – zuerst der ganz banale Gegenstand, dann der Aha-Moment. Der Kontrast ist der ganze Reiz des Reels.</t>
+        </is>
+      </c>
       <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="3" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -4722,9 +5417,19 @@
           <t>Speichern &amp; durchwischen – folg uns für mehr</t>
         </is>
       </c>
-      <c r="L73" s="4" t="inlineStr"/>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: "Worte, die bleiben." – Titel groß, darunter klein: "Für die Momente, in denen dir die Worte fehlen. Wisch weiter →"
+Slide 2: Überschrift "Bei Angst:" – Vers [wörtlich], schlicht und groß gesetzt.
+Slide 3: Überschrift "Bei Einsamkeit:" – Vers [wörtlich].
+Slide 4: Überschrift "Bei einem Neuanfang:" – Vers [wörtlich].
+Slide 5: Überschrift "Aus Dankbarkeit:" – Vers [wörtlich]. Darunter: "Speicher dir das für den Tag, an dem du es brauchst."
+💡 Tipp: Alle Slides im exakt gleichen Layout halten (Lebenslage oben, Vers mittig) – das ruhige, einheitliche Design macht das Carousel wertig und lädt zum Speichern ein. Verse vorher gegenprüfen.</t>
+        </is>
+      </c>
       <c r="M73" s="4" t="inlineStr"/>
-      <c r="N73" s="5" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -4780,9 +5485,20 @@
           <t>Deine Fragen sind willkommen – Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~35s
+0–5s — Bild: Person sitzt ruhig, Handy auf Augenhöhe, ehrlicher Blick · Sprich: "Ich sag mal was, das man in der Kirche selten hört:"
+5–14s — Bild: Gleiche Einstellung, offen · Sprich: "Auch ich zweifle manchmal. Es gibt Tage, da hab ich mehr Fragen als Antworten."
+14–25s — Bild: Ruhig, nahbar · Sprich: "Und ich hab gemerkt: Glaube heißt nicht, alles zu wissen. Zweifeln und Glauben liegen oft ganz nah beieinander."
+25–31s — Bild: Warm, einladend · Sprich: "Wenn du also Fragen hast – du bist damit nicht allein und bei uns genau richtig."
+31–35s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Fragen sind erlaubt."
+🎵 Musik: sehr dezent oder keine · 💡 Tipp: Bewusst KEINE fromme Fassade – ein Take, ruhig, mit echten kleinen Pausen. Genau diese Unperfektheit baut Nähe zu Suchenden auf. Nicht auswendig aufsagen.</t>
+        </is>
+      </c>
       <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="3" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -4838,9 +5554,19 @@
           <t>Folg uns für deinen Freitagssegen</t>
         </is>
       </c>
-      <c r="L75" s="4" t="inlineStr"/>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–3s — Bild: Warmes Abendlicht, du ruhig in die Kamera, entspannt · Sprich: "Freitagabend. Die Woche ist geschafft."
+3–8s — Bild: Ruhig, warm, direkt in die Linse · Sprich: "Ein Segen für dich, bevor das Wochenende beginnt:"
+8–12s — Bild: Ruhig bleiben, langsam sprechen · Sprich: "Gott behüte dich, schenke dir Ruhe – und geh gesegnet ins Wochenende."
+12–15s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Bis nächsten Freitag."
+🎵 Musik: warm, ruhig, leise · 💡 Tipp: Als wöchentliches Ritual immer im gleichen Licht und Ton drehen (goldene Abendstunde am Fenster) – die Wiederholung macht daraus ein festes Freitags-Ritual, auf das Follower sich freuen.</t>
+        </is>
+      </c>
       <c r="M75" s="4" t="inlineStr"/>
-      <c r="N75" s="5" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr"/>
+      <c r="O75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -4896,9 +5622,18 @@
           <t>Komm vorbei – Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: "Zwei Sprachen, ein Trost." – Titel groß, darunter zweisprachig klein: "Zwei Sprachen · Dwa języki". Hinweis "Wisch weiter →"
+Slide 2: Der Vers auf Deutsch, oben mit dezentem "DE" markiert: "[Vers auf Deutsch, wörtlich]."
+Slide 3: Derselbe Vers auf Polnisch, oben mit "PL" markiert: "[Vers auf Polnisch, wörtlich]."
+Slide 4: Kurzer Gedanke + Einladung: "Ein Glaube verbindet. Für alle deutsch-polnischen Familien – ihr seid willkommen. So 09:30 · Miodowa 21. Zapraszamy serdecznie."
+💡 Tipp: DE und PL optisch absolut gleichwertig behandeln (gleiche Schriftgröße, gleiche Farbe) – so wird die Botschaft der Verbundenheit auch im Design sichtbar. Polnische Übersetzung von einer muttersprachlichen Person gegenlesen lassen.</t>
+        </is>
+      </c>
       <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="3" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -4954,9 +5689,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L77" s="4" t="inlineStr"/>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–3s — Bild: Ruhiger Platz im Saal, Person im Brustbild, Fensterlicht von der Seite · Text: "Warum kommst du sonntags?"
+3–11s — Bild: Nah aufs Gesicht, Person sieht ruhig in die Kamera · Sprich: "Weil ich hier meine Sprache höre. Und weil mich nach dem ersten Mal jemand beim Namen gegrüßt hat."
+11–13s — Bild: Schnittbild Hände auf dem Gesangbuch, warme Kaffeetasse · Text: "Deutschsprachiger Gottesdienst in Warschau"
+13–15s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhiges Klavier, sehr leise · 💡 Tipp: Person zwei, drei Takes sagen lassen und den natürlichsten nehmen — nicht den perfektesten. Handy am Fenster abstützen, nicht gegen das Licht filmen.</t>
+        </is>
+      </c>
       <c r="M77" s="4" t="inlineStr"/>
-      <c r="N77" s="5" t="inlineStr"/>
+      <c r="N77" s="4" t="inlineStr"/>
+      <c r="O77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -5012,9 +5757,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–3s — Bild: Person am Kaffeetisch, weiches Tageslicht · Text: "Seit ein paar Monaten in Warschau"
+3–9s — Bild: Person nah, ruhig · Sprich: "Als ich herkam, kannte ich niemanden. Ehrlich — am Anfang war alles fremd."
+9–15s — Bild: Schnittbild Tür, Treppe, freundliches Gesicht am Eingang · Sprich: "Beim ersten Sonntag hab ich mich an die Tür getraut und dachte: einmal reinschauen."
+15–19s — Bild: Person wieder nah, ein kleines Lächeln · Sprich: "Und hier hab ich mich zum ersten Mal wieder ein bisschen zuhause gefühlt."
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, dezent · 💡 Tipp: In drei kurzen Häppchen aufnehmen, dann zusammenschneiden — das nimmt der Person den Druck, alles am Stück zu sagen.</t>
+        </is>
+      </c>
       <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="3" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -5070,9 +5826,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr"/>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Totale — drei Menschen (jung, mittel, älter) nebeneinander in der Bank · Text: "Drei Generationen, eine Bank"
+3–8s — Bild: Nahbild jüngste Person · Sprich: "Für mich ist Gemeinde: Heimat — auch weit weg von zuhause."
+8–13s — Bild: Nahbild mittlere Person · Sprich: "Für mich: Ruhe. Einmal in der Woche durchatmen."
+13–17s — Bild: Nahbild älteste Person · Sprich: "Für mich: dass ich nie allein bin."
+17–20s — Endcard: Totale von allen dreien, dann Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warmes Klavier, ruhig · 💡 Tipp: Erst die Totale filmen, dann jede Person einzeln nah — aus derselben Position, damit die Schnitte sauber sitzen. Jede/r bekommt nur einen Satz, das hält es dicht.</t>
+        </is>
+      </c>
       <c r="M79" s="4" t="inlineStr"/>
-      <c r="N79" s="5" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr"/>
+      <c r="O79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -5128,9 +5895,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Person rückt Stühle zurecht, Handy folgt locker mit · Text: "Was machst du hier eigentlich?"
+3–8s — Bild: Detailaufnahmen: Liedzettel auslegen, Tassen bereitstellen · Text: "Sie stellt jeden Sonntag die Stühle"
+8–14s — Bild: Person hält kurz inne, sieht in die Kamera · Sprich: "Ich mach das, weil jemand es tun muss — und weil ich es ehrlich gern tue. Am Ende sitzt jeder auf einem Platz."
+14–16s — Bild: Kurzes Lächeln in die Kamera
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, unaufdringlich · 💡 Tipp: Erst beim Arbeiten mitfilmen, dann für den O-Ton einmal kurz stoppen lassen — nicht beim Reden gleichzeitig schleppen, sonst wackelt der Ton.</t>
+        </is>
+      </c>
       <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="3" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -5186,9 +5964,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L81" s="4" t="inlineStr"/>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Nah auf zwei Hände, die ein Streichholz an eine Kerze halten · Text: "Wessen Hände sind das?"
+3–8s — Bild: Hände schenken Kaffee in eine Tasse ein · Off-Stimme: "Das sind die Hände von Maria. Seit Jahren zündet sie die Kerzen an, bevor jemand kommt."
+8–14s — Bild: Hände blättern langsam Seiten im Gesangbuch auf · Off-Stimme: "Sie steht nie vorn. Und ohne sie wäre der Sonntag ein anderer."
+14–16s — Bild: Ruhige Hände falten sich kurz · Text: "Gemeinde ist das, was viele Hände tragen"
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr ruhig, warm · 💡 Tipp: Off-Stimme getrennt aufnehmen (im ruhigen Raum, Handy nah am Mund) und erst danach unter die Handbilder legen — das klingt viel sauberer als live.</t>
+        </is>
+      </c>
       <c r="M81" s="4" t="inlineStr"/>
-      <c r="N81" s="5" t="inlineStr"/>
+      <c r="N81" s="4" t="inlineStr"/>
+      <c r="O81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -5244,9 +6033,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–5s — Bild: Person von der Seite am Klavier, ein paar Takte spielen lassen — Originalton laut! · Text: "Der Mensch hinter der Musik"
+5–9s — Bild: Nah auf die Hände auf den Tasten, Spiel läuft weiter
+9–16s — Bild: Person hält kurz inne, dreht sich zur Kamera · Sprich: "Musik ist für mich das, was anfängt, wo die Worte aufhören. Manchmal sagt eine Melodie mehr als eine ganze Predigt."
+16–18s — Bild: Hände nehmen das Spiel wieder auf, Ton klingt aus · Text: "Jeden Gottesdienst — live gespielt"
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: KEINE zusätzliche — das echte Klavierspiel ist die Musik · 💡 Tipp: Nah genug ans Instrument, damit der Ton trägt, aber nicht direkt in die Saiten/Pfeifen — sonst übersteuert das Handy-Mikro.</t>
+        </is>
+      </c>
       <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="3" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -5302,9 +6102,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L83" s="4" t="inlineStr"/>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–4s — Bild: Person entspannt sitzend, gedämpftes Licht · Text: "Ich dachte, Kirche ist nichts für mich."
+4–10s — Bild: Person nah, ehrlich · Sprich: "Ehrlich, ich war skeptisch. Ich dachte, da wird geredet und ich müsste irgendwas glauben."
+10–15s — Bild: Ruhiges Schnittbild leere Bank, offener Türspalt · Sprich: "Was mich überrascht hat: Keiner hat was von mir erwartet. Ich durfte einfach da sein."
+15–19s — Bild: Person wieder nah · Sprich: "Skeptisch bin ich manchmal immer noch. Und trotzdem bin ich geblieben."
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr dezent, zurückhaltend · 💡 Tipp: Die Skepsis nicht wegschneiden — genau die macht es glaubwürdig. Kein Bekehrungston, ruhig sprechen lassen.</t>
+        </is>
+      </c>
       <c r="M83" s="4" t="inlineStr"/>
-      <c r="N83" s="5" t="inlineStr"/>
+      <c r="N83" s="4" t="inlineStr"/>
+      <c r="O83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -5360,9 +6171,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–3s — Bild: Familie zusammen am Kaffeetisch, natürliches Licht · Text: "Deutsch-polnisch — und mittendrin"
+3–9s — Bild: Ein Elternteil erzählt, Kind sitzt daneben · Sprich: "Bei uns zuhause reden wir Deutsch und Polnisch durcheinander. Hier hören die Kinder mal einen ganzen Sonntag auf Deutsch."
+9–14s — Bild: Beiläufig: Kinder spielen, ein Lächeln zwischen den Eltern · Sprich: "Für die Sprache, für die Kinder — und für ein Stück Heimat für uns."
+14–19s — Bild: Familie zusammen, ruhig · Sprich: "Zwei Sprachen, ein Zuhause. Hier hat beides Platz."
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, familiär, leise · 💡 Tipp: Kinder nicht auf Text drillen — beiläufige Momente (Spielen, Lachen) einfach mitlaufen lassen, die tragen das Reel. Bei Kindern im Bild vorher kurz das Einverständnis der Eltern zum Posten einholen.</t>
+        </is>
+      </c>
       <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="3" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -5418,9 +6240,21 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L85" s="4" t="inlineStr"/>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1 (Titel): Ruhiges Foto vom Saal oder Kaffeetisch · Text im Bild: "Das sind wir" + klein darunter "Ein paar Gesichter aus unserer Gemeinde →"
+Slide 2: Porträt Person 1 · Text: "Anna, seit 2019 dabei — kocht den besten Kirchenkaffee."
+Slide 3: Porträt Person 2 · Text: "Thomas, neu dabei — sitzt am liebsten ganz hinten."
+Slide 4: Porträt Person 3 · Text: "Marek, zum Studium in Warschau — hier ist ein Stück Zuhause."
+Slide 5: Porträt Person 4 · Text: "Renate, seit über 20 Jahren — kennt jede Geschichte."
+Slide 6: Porträt Person 5 · Text: "Familie K., deutsch-polnisch — kommen mit den Kindern."
+Slide 7 (Abschluss): Foto offene Kirchentür oder Gruppe · Text: "…und viele mehr. Dein Platz ist frei — So 09:30 · Miodowa 21"
+💡 Tipp: Alle Porträts mit gleichem Licht und Abstand fotografieren (am besten am selben Fenster, in einer Session) — dann wirkt das Carousel wie aus einem Guss. Namen/Details vor dem Posten von jeder Person freigeben lassen.</t>
+        </is>
+      </c>
       <c r="M85" s="4" t="inlineStr"/>
-      <c r="N85" s="5" t="inlineStr"/>
+      <c r="N85" s="4" t="inlineStr"/>
+      <c r="O85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -5476,9 +6310,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–4s — Bild: Person ruhig sitzend, weiches Licht, würdevoller Ausschnitt · Text: "Seit vielen Jahren dabei"
+4–11s — Bild: Person erzählt, ruhig · Sprich: "Als ich anfing, waren wir eine Handvoll Leute. Man kannte jeden mit Namen."
+11–16s — Bild: Altes Foto in der Hand der Person, langsam einblenden · Sprich: "Vieles hat sich verändert — die Gesichter, die Zeiten."
+16–19s — Bild: Person wieder nah, kleines Lächeln · Sprich: "Aber das Wichtigste ist geblieben: dass niemand allein bleiben muss."
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr ruhig, würdevoll · 💡 Tipp: Stille aushalten — nach dem letzten Satz eine Sekunde stehen lassen, nicht sofort wegschneiden. Das gibt dem Porträt Würde.</t>
+        </is>
+      </c>
       <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="3" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -5534,9 +6379,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L87" s="4" t="inlineStr"/>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Schlichte Titelkarte, Aubergine-Hintergrund · Text: "Was gibt dir Kraft?"
+3–8s — Bild: Person 1, Brustbild · Sprich: "Ehrlich? Der Sonntagmorgen. Eine Stunde, in der die Woche mal stillsteht."
+8–12s — Bild: Person 2, gleicher Look · Sprich: "Zu wissen, dass jemand für mich betet — auch wenn ich's grad selbst nicht schaffe."
+12–16s — Bild: Person 3, gleicher Look · Sprich: "Diese Gemeinschaft. Dass ich nirgends erklären muss, warum ich da bin."
+16–18s — Endcard: "Und dir? Schreib's in die Kommentare" + Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, rhythmisch, leise · 💡 Tipp: Alle drei aus gleicher Distanz und mit gleichem Licht filmen (gleicher Bildlook) — dann wirken die schnellen Schnitte wie eine Einheit. Frage jedem einzeln stellen, ohne dass sie die Antwort der anderen hören.</t>
+        </is>
+      </c>
       <c r="M87" s="4" t="inlineStr"/>
-      <c r="N87" s="5" t="inlineStr"/>
+      <c r="N87" s="4" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -5592,9 +6448,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–4s — Bild: Füße/Person geht los auf der Straße, von hinten gefilmt · Text: "Der Weg hierher"
+4–10s — Bild: Tramhaltestelle, Straße, Handy folgt locker · Off-Stimme: "Beim ersten Mal war ich unsicher. Ich hab dreimal überlegt, ob ich wirklich reingehe."
+10–16s — Bild: Näher an der Miodowa 21, Blick auf den Eingang · Off-Stimme: "Was mich hergeführt hat? Ich wollte einfach mal meine Sprache hören. Und nicht allein sein."
+16–20s — Bild: Ankunft an der Tür, Hand an der Klinke · Off-Stimme: "Heute ist das mein Sonntagsweg geworden."
+20–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, mit sanftem Puls (wie Gehen) · 💡 Tipp: Off-Stimme separat im ruhigen Raum aufnehmen, dann unter die Weg-Bilder legen — draußen wird der Live-Ton vom Straßenlärm geschluckt.</t>
+        </is>
+      </c>
       <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="3" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -5650,9 +6517,14 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L89" s="4" t="inlineStr"/>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Ein Gemeindemitglied im ruhigen Halbporträt, leicht zur Seite gedreht, Blick entweder in die Kamera oder weich am Objektiv vorbei. · Bildaufbau/Licht: Person seitlich ans Fenster stellen, sodass weiches Tageslicht von einer Seite kommt (weiche Schatten, kein Blitz). Porträtmodus, auf die Augen scharfstellen, viel ruhiger Hintergrund. Zwei, drei Aufnahmen: einmal ernst, einmal lächelnd — bestes wählen, optional in Schwarzweiß für den stillen Look. · Text im Bild (optional): "Porträt der Woche" klein oben, sonst Bild pur wirken lassen; das Zitat lieber in die Caption. 💡 Tipp: Auf Augenhöhe fotografieren, nicht von oben — das wirkt respektvoller und nahbarer. Zitat direkt bei der Aufnahme notieren, solange die Person noch da ist.</t>
+        </is>
+      </c>
       <c r="M89" s="4" t="inlineStr"/>
-      <c r="N89" s="5" t="inlineStr"/>
+      <c r="N89" s="4" t="inlineStr"/>
+      <c r="O89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -5708,9 +6580,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Person locker sitzend, freundliches Licht · Text: "Was ich beim ersten Mal nicht wusste"
+3–9s — Bild: Person nah, erzählend · Sprich: "Ich hatte echt Bammel: Muss ich mitsingen? Kenn ich die Lieder? Steh ich blöd rum?"
+9–15s — Bild: Beruhigende Schnittbilder: offene Tür, Kaffeetisch, freundliche Gesichter · Sprich: "Und dann: Man muss keine Lieder kennen, keinen Ablauf. Man darf einfach dasitzen."
+15–18s — Bild: Person wieder nah, entspannt · Sprich: "Kurz gesagt — ich musste gar nichts können."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: freundlich, leicht, dezent · 💡 Tipp: Mit dem entlastenden Satz enden — das ist die Botschaft. Die Person soll locker und alltäglich reden, nicht wie eine Werbung.</t>
+        </is>
+      </c>
       <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="3" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -5766,9 +6649,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L91" s="4" t="inlineStr"/>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Person tippt am Handy/Laptop eine Nachricht, natürliches Licht · Text: "Wenn du uns schreibst …"
+4–10s — Bild: Person schaut auf, direkt in die Kamera · Sprich: "Hi — wenn du uns schreibst, lande ich bei dir. Ich lese jede Nachricht selbst."
+10–15s — Bild: Nahbild freundliches Lächeln, Hand am Handy · Sprich: "Kein Formular, kein Amtston. Einfach ein 'Hallo' reicht."
+15–17s — Bild: Person winkt kurz oder nickt · Sprich: "Trau dich — meld dich einfach."
+17–18s — Endcard: "Link in Bio → WhatsApp" + Lutherrose
+🎵 Musik: warm, freundlich, leise · 💡 Tipp: Direkt in die Kamera sprechen lassen (Blick ins Objektiv, nicht auf den Bildschirm) — das schafft den persönlichen 'ich rede mit dir'-Effekt.</t>
+        </is>
+      </c>
       <c r="M91" s="4" t="inlineStr"/>
-      <c r="N91" s="5" t="inlineStr"/>
+      <c r="N91" s="4" t="inlineStr"/>
+      <c r="O91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -5824,9 +6718,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~30s
+0–3s — Bild: Person mit Kaffeetasse an gemütlichem Platz, Handy abgestützt · Text: "Zwei Minuten mit [Name]"
+3–11s — Bild: Person antwortet locker, hält die Tasse · Frage aus dem Off: "Seit wann bist du dabei?" · Sprich (Antwort): "Seit zwei Jahren. Bin eher zufällig reingestolpert und irgendwie geblieben."
+11–20s — Bild: Gleicher Platz, kleiner Schluck Kaffee zwischendurch · Frage aus dem Off: "Was magst du hier am meisten?" · Sprich: "Das Ungezwungene. Keiner tut so, als hätte er alles im Griff."
+20–27s — Bild: Person lächelt · Frage aus dem Off: "Ein Satz für jemand, der überlegt vorbeizukommen?" · Sprich: "Komm einfach. Der schlimmste Fall ist ein guter Kaffee."
+27–30s — Endcard: "Neue Folge jede Woche" + Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr leise oder gar keine — Kaffeehaus-Atmo zulassen · 💡 Tipp: Wenig schneiden, der Charme liegt im Ungefilterten. Handy fest abstützen und den Ton nah halten (Person nicht zu weit weg setzen).</t>
+        </is>
+      </c>
       <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="3" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -5882,9 +6787,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L93" s="4" t="inlineStr"/>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Person deckt den Kaffeetisch ein — Kanne, Tassen, Kuchen, Handy folgt locker · Text: "Der Mensch hinterm Kaffeetisch"
+4–10s — Bild: Person schenkt Kaffee ein, blickt kurz auf · Sprich: "Der Gottesdienst ist das eine. Aber ehrlich — der Kaffee danach ist fast wichtiger."
+10–15s — Bild: Schnittbilder: dampfende Tasse, Menschen im Gespräch am Tisch, Gemurmel im Ton · Sprich: "Hier bleibt keiner allein stehen. Hier fängt das Reden erst an."
+15–17s — Bild: Person lächelt in die Runde · Text: "Das Danach ist genauso wichtig."
+17–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, leise — Hintergrund-Gemurmel bewusst zulassen · 💡 Tipp: Die echte Kaffeetisch-Atmo (Klappern, Stimmen) mit aufnehmen, das macht die Wärme aus. Nicht steril filmen.</t>
+        </is>
+      </c>
       <c r="M93" s="4" t="inlineStr"/>
-      <c r="N93" s="5" t="inlineStr"/>
+      <c r="N93" s="4" t="inlineStr"/>
+      <c r="O93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -5940,9 +6856,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L94" s="2" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–3s — Bild: Person nah, Brustbild, weiches Fensterlicht · Text: "Warum ich geblieben bin"
+3–10s — Bild: Person ruhig in die Kamera · Sprich: "Ich kam einmal, aus Neugier. Geblieben bin ich, weil ich hier gebraucht werde — und weil ich dazugehöre."
+10–13s — Bild: Ruhige Schnittbilder: vertraute Ecke im Saal, ein Lächeln · Text: "Aus 'ein Mal' wurde 'immer'"
+13–15s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: leise, warm · 💡 Tipp: Den einen Satz in mehreren Takes sagen lassen und den ruhigsten nehmen. Bewusst als Gegenstück zu 'Warum ich herkomme' gleich gerahmt (gleiches Fensterlicht) — als Serie erkennbar.</t>
+        </is>
+      </c>
       <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="3" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -5998,9 +6924,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L95" s="4" t="inlineStr"/>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Junge Person mit Rucksack unterwegs oder auf der Bank, lebendiges Licht · Text: "Zum Studium in Warschau"
+3–9s — Bild: Person locker, direkt · Sprich: "Ich bin für ein Semester hier. Und ganz ehrlich — ich dachte, Kirche ist was für Ältere."
+9–15s — Bild: Schnittbilder: Kaffee, junge Gesichter, Uni-Atmosphäre · Sprich: "Dann war ich einmal da. Deutsch reden, ohne Uni-Stress, echte Leute — das hat gefehlt."
+15–18s — Bild: Person lächelt · Sprich: "Hier hab ich ein Stück Zuhause gefunden."
+18–20s — Endcard: "Link in Bio → WhatsApp" + Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, aber etwas lebendiger/jünger · 💡 Tipp: Etwas dynamischer schneiden als bei den älteren Porträts (kürzere Takes), aber nicht hektisch — die Wärme muss bleiben.</t>
+        </is>
+      </c>
       <c r="M95" s="4" t="inlineStr"/>
-      <c r="N95" s="5" t="inlineStr"/>
+      <c r="N95" s="4" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -6056,9 +6993,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L96" s="2" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Person geht durch den Saal zu ihrem festen Platz und setzt sich · Text: "Mein Lieblingsplatz"
+3–9s — Bild: Person zeigt auf den Platz, tippt auf die Lehne · Sprich: "Ich sitz immer hier — dritte Reihe, am Fenster. Seit Jahren derselbe Platz."
+9–13s — Bild: Bildwechsel — Blick vom Platz aus nach vorn, was die Person sieht · Sprich: "Von hier sehe ich alles. Und komme trotzdem zur Ruhe."
+13–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, dezent · 💡 Tipp: Unbedingt den Perspektivwechsel filmen (einmal die Person am Platz, einmal ihr Blick nach vorn) — das macht den Ort für den Zuschauer erlebbar.</t>
+        </is>
+      </c>
       <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="3" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -6114,9 +7061,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L97" s="4" t="inlineStr"/>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Die beiden tragen zusammen Stühle, Handy folgt mit · Text: "Das Ehrenamt-Duo"
+3–9s — Bild: Beide nebeneinander, stellen sich gegenseitig vor · Sprich (Person A, deutet auf B): "Der trägt die schweren Sachen." · Sprich (Person B, grinst): "Und sie dirigiert. Sehr gründlich."
+9–14s — Bild: Neckischer Moment — einer verstellt dem anderen den Stuhl, beide lachen · Sprich (beide): "Aber zusammen kriegen wir jeden Sonntag hin."
+14–16s — Bild: Beide klatschen ab oder lachen in die Kamera
+16–18s — Endcard: "Lust mitzumachen? Link in Bio" + Lutherrose
+🎵 Musik: leicht, gutgelaunt, aber warm · 💡 Tipp: Den Humor echt lassen — nicht Sätze vorschreiben, sondern die beiden einfach necken lassen und die besten Momente rausschneiden.</t>
+        </is>
+      </c>
       <c r="M97" s="4" t="inlineStr"/>
-      <c r="N97" s="5" t="inlineStr"/>
+      <c r="N97" s="4" t="inlineStr"/>
+      <c r="O97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -6172,9 +7130,22 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L98" s="2" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Schlichte Titelkarte, Aubergine · Text: "Ein Wort, das für mich Gemeinde ist"
+3–6s — Bild: Person 1, Nahbild frontal · Sprich: "Heimat." · Text einblenden: "Heimat."
+6–8s — Bild: Person 2, gleicher Look · Sprich: "Ruhe." · Text: "Ruhe."
+8–10s — Bild: Person 3 · Sprich: "Zusammen." · Text: "Zusammen."
+10–13s — Bild: Person 4 · Sprich: "Ankommen." · Text: "Ankommen."
+13–14s — Bild: Titelkarte · Text: "Und für dich?"
+14–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, gleichmäßiger Rhythmus, warmer Ausklang · 💡 Tipp: Alle frontal, gleicher Abstand, gleiches Licht — dann sitzen die schnellen Schnitte im Takt der Musik. Jedes Wort auf den Beat schneiden.</t>
+        </is>
+      </c>
       <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="3" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -6230,9 +7201,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L99" s="4" t="inlineStr"/>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Pfarrer/in locker, ohne Talar, freundliches Licht · Text: "Unser/e Pfarrer/in — mal ganz privat"
+3–8s — Bild: Textkarte "Kaffee oder Tee?", dann Antwort · Sprich: "Kaffee. Immer. Am liebsten der aus unserer eigenen Kanne nach dem Gottesdienst."
+8–13s — Bild: Textkarte "Was hörst du im Auto?", dann Antwort · Sprich: "Ehrlich? Meistens irgendwas Lautes. Nicht immer Kirchenmusik."
+13–18s — Bild: Textkarte "Was macht dir am Sonntag Freude?", dann Antwort · Sprich: "Wenn ein neues Gesicht in der letzten Reihe sitzt. Das macht meinen Tag."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: freundlich, leicht · 💡 Tipp: Spontan antworten lassen — nicht vorher üben. Die überraschendste oder lustigste Antwort ans Ende setzen, das bleibt hängen.</t>
+        </is>
+      </c>
       <c r="M99" s="4" t="inlineStr"/>
-      <c r="N99" s="5" t="inlineStr"/>
+      <c r="N99" s="4" t="inlineStr"/>
+      <c r="O99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -6288,9 +7270,21 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr"/>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Titelkarte oder erste Person, Nahbild · Text: "Von wie weit kommst du?"
+3–6s — Bild: Person 1, Nahbild · Sprich: "Aus Praga — einmal quer über die Weichsel." · Text: "Praga"
+6–9s — Bild: Person 2, gleicher Look · Sprich: "Aus Mokotów, 40 Minuten mit der Tram." · Text: "Mokotów · 40 Min"
+9–12s — Bild: Person 3 · Sprich: "Vom Stadtrand — und einmal war ich sogar aus Łódź da." · Text: "…und noch weiter"
+12–14s — Bild: Schlichte Karte Warschaus mit ein paar Punkten · Text: "Wir kommen aus ganz Warschau zusammen"
+14–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: leicht, warm, gleichmäßig · 💡 Tipp: Ort/Distanz als Text unter jede Person legen — dann versteht man die Vielfalt auch ohne Ton (viele schauen stumm).</t>
+        </is>
+      </c>
       <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="3" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -6346,9 +7340,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L101" s="4" t="inlineStr"/>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Person sitzt allein im Saal, ein leerer Stuhl daneben deutlich sichtbar, weiches Licht · Text: "Der Stuhl daneben ist frei"
+4–11s — Bild: Person ruhig, halb zum leeren Stuhl gewandt · Sprich: "Wenn ich hier sitze, denke ich oft an die, die noch nicht da sind. An alle, die zögern."
+11–15s — Bild: Langsames Nahbild auf den leeren Stuhl · Sprich: "An die, die glauben, sie gehören nicht dazu. Dieser Platz — der ist für dich freigehalten."
+15–17s — Bild: Person schaut ruhig in die Kamera · Text: "Vielleicht ist er für dich."
+17–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr still, ein einzelnes Klavier oder gar nichts · 💡 Tipp: Stille bewusst zulassen — nicht jede Pause füllen. Der leere Stuhl ist der Hauptdarsteller, ihn klar ins Bild setzen und am Ende allein zeigen.</t>
+        </is>
+      </c>
       <c r="M101" s="4" t="inlineStr"/>
-      <c r="N101" s="5" t="inlineStr"/>
+      <c r="N101" s="4" t="inlineStr"/>
+      <c r="O101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -6404,9 +7409,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr"/>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–3s — Bild: langsamer Schwenk durch die noch leeren Stuhlreihen im stillen Saal · Text (On-Screen): "07:30 Uhr. Noch zwei Stunden bis alle kommen."
+3–9s — Bild: im Hintergrund rückt jemand Stühle zurecht, deckt einen Tisch · Sprich (ruhig, aus dem Off): "Bevor du sonntags reinkommst, sind schon ein paar Hände hier."
+9–15s — Bild: Zeitraffer-Montage — Kerzen an, Gesangbücher raus, Blumen an den Altar · Text: "Damit du einfach nur ankommen musst."
+15–19s — Bild: langsamer Schwenk über den jetzt fertig gedeckten, warmen Raum · Sprich: "Und wenn alles bereit ist, fehlst nur noch du."
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent (leises Klavier) · 💡 Tipp: Für den Zeitraffer das Handy auf einen Stuhl oder eine Fensterbank lehnen und nicht in der Hand halten — dann ist das Bild stabil.</t>
+        </is>
+      </c>
       <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="3" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -6462,9 +7478,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 — Kaffee gibt's danach</t>
         </is>
       </c>
-      <c r="L103" s="4" t="inlineStr"/>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Nahaufnahme, Wasser läuft in die große Kaffeemaschine · Sprich (warm, leise): "Womit fängt bei uns ein Gottesdienst an?"
+3–8s — Bild: der Schalter wird gedrückt, es blubbert, erste Tropfen laufen durch · Sprich: "Nicht mit dem ersten Ton. Sondern mit einer Kanne Kaffee."
+8–14s — Bild: leere Tassen werden ordentlich in einer Reihe aufgestellt · Sprich: "Denn Gemeinschaft fängt schon in der Küche an — lange bevor jemand da ist."
+14–18s — Endcard: dampfende Tasse, dann Lutherrose + "So 09:30 · Miodowa 21 — Kaffee danach"
+🎵 Musik: warm, gemütlich, dezent · 💡 Tipp: Ton der blubbernden Maschine bewusst laut mitnehmen — dieses Geräusch macht das Reel gemütlich, also nicht mit lauter Musik übertönen.</t>
+        </is>
+      </c>
       <c r="M103" s="4" t="inlineStr"/>
-      <c r="N103" s="5" t="inlineStr"/>
+      <c r="N103" s="4" t="inlineStr"/>
+      <c r="O103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -6520,9 +7546,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: extreme Nahaufnahme, ein Streichholz wird angerissen, kurzes Aufflammen · Text (On-Screen): "Eine Kerze."
+4–9s — Bild: die erste Altarkerze fängt Feuer, die Flamme wird ruhig · Text: "Und noch eine."
+9–14s — Bild: die zweite, dann die dritte Kerze wird entzündet, langsame Schnitte · Text: "Und noch eine."
+14–17s — Bild: der Blick weitet sich, mehrere Flammen leuchten warm im halbdunklen Raum · (kein Text, nur Stille)
+17–20s — Endcard: sanftes Kerzenlicht, ein Wort erscheint: "Willkommen" + klein darunter "So 09:30 · Miodowa 21"
+🎵 Musik: sehr ruhig, fast still — nur ein leiser, getragener Ton · 💡 Tipp: In einem halbdunklen Raum filmen, damit die Flammen richtig leuchten; Handy-Blitz aus, sonst geht die Stimmung verloren.</t>
+        </is>
+      </c>
       <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="3" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -6578,9 +7615,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L105" s="4" t="inlineStr"/>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: das aufgeschlagene, abgegriffene Gesangbuch — Eselsohren und eine handschriftliche Randnotiz gut sichtbar, im Hintergrund unscharf ein Stapel weiterer Bücher · Bildaufbau/Licht: weiches Seitenlicht vom Fenster, leicht von schräg oben fotografiert, sodass die gewellten Seiten Schatten werfen und Struktur zeigen; Fokus auf die Notiz am Rand · ggf. Text im Bild: "Schon durch viele Hände gegangen — vielleicht bald durch deine."
+💡 Tipp: Nah rangehen und einmal auf die Randnotiz tippen, um dort scharfzustellen — die Gebrauchsspuren sind das Herz des Bildes, nicht das ganze Buch.</t>
+        </is>
+      </c>
       <c r="M105" s="4" t="inlineStr"/>
-      <c r="N105" s="5" t="inlineStr"/>
+      <c r="N105" s="4" t="inlineStr"/>
+      <c r="O105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -6636,9 +7679,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L106" s="2" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: POV — du blickst von oben auf einen hohen Stapel Teller in deinen Händen · Text (On-Screen): "POV: Du deckst 30 Kuchenteller."
+3–8s — Bild: die Teller werden schnell und leicht schief auf den Tischen verteilt, einer klappert · Sprich (locker, mit Augenzwinkern): "Und egal wie sehr du dich anstrengst — keiner steht gerade."
+8–12s — Bild: du schiebst einen Teller zurecht, dann kippt der nächste minimal — kleines Chaos · Sprich: "Ehrenamt eben."
+12–16s — Bild: Schnitt auf die fertige, überraschend schöne Kaffeetafel · Text: "...aber am Ende passt's doch." + klein "So 09:30 · Miodowa 21"
+🎵 Musik: leicht, verspielt, mit Schwung · 💡 Tipp: Das Handy dicht vor der Brust halten und leicht mitwackeln beim Gehen — dieser echte POV-Wackler macht den Clip nahbar, glatte Stabilisierung wäre hier zu steril.</t>
+        </is>
+      </c>
       <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="3" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -6694,9 +7747,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L107" s="4" t="inlineStr"/>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1 (Cover): Foto der vollen Kaffeetafel von oben · Text: "Wer bringt eigentlich den Kuchen mit?"
+Slide 2: Nahaufnahme von Kuchen Nr. 1 · Text: "Anna hat den Streuselkuchen gebacken." (Name nur mit Einverständnis)
+Slide 3: Nahaufnahme von Kuchen Nr. 2 · Text: "Thomas den Marmorkuchen."
+Slide 4: Nahaufnahme von Kuchen Nr. 3 · Text: "Und irgendwer bringt immer die Kekse."
+Slide 5: die ganze Tafel in der Totale · Text: "Keiner bringt alles. Alle bringen ein bisschen."
+Slide 6 (Abschluss): warmes Bild der Tafel mit Menschen im Hintergrund · Text: "So schmeckt Gemeinschaft. So 09:30 · Miodowa 21 — bring einfach dich mit."
+💡 Tipp: Alle Kuchen-Nahaufnahmen aus demselben Winkel und Abstand fotografieren — dann wirkt das Carousel als Reihe stimmig und wie aus einem Guss.</t>
+        </is>
+      </c>
       <c r="M107" s="4" t="inlineStr"/>
-      <c r="N107" s="5" t="inlineStr"/>
+      <c r="N107" s="4" t="inlineStr"/>
+      <c r="O107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -6752,9 +7816,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L108" s="2" t="inlineStr"/>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: ruhiger, statischer Blick in den fertig gedeckten, noch leeren Saal · Sprich (leise, warm): "Es gibt diesen einen Moment, kurz bevor die Türen aufgehen."
+4–9s — Bild: eine Hand rückt einen letzten Stuhl zurecht, sonst nichts als Stille · Sprich: "Der Raum ist fertig. Die Kerzen brennen."
+9–14s — Bild: langsamer Schwenk über Kerzen, Blumen, die ausgelegten Gesangbücher · Sprich: "Und jedes Mal fragen wir uns: Wer kommt heute?"
+14–18s — Endcard: der stille Raum, dann Text "Vielleicht du?" + Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, erwartungsvoll, sehr dezent · 💡 Tipp: Das Handy für die statischen Einstellungen irgendwo auflegen und wirklich 4–5 Sekunden ruhig halten — die Stille ist hier der Inhalt, hektische Schnitte würden sie zerstören.</t>
+        </is>
+      </c>
       <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="3" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -6810,9 +7884,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L109" s="4" t="inlineStr"/>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~24s
+0–4s — Bild: bunter Blumenstand auf einem Warschauer Markt, eine Hand greift nach einem Strauß · Sprich (warm, erzählend): "Die Blumen auf unserem Altar kommen nicht aus dem Großhandel."
+4–9s — Bild: kurzer Moment beim Bezahlen, ein Nicken zum Verkäufer · Sprich: "Sondern vom Markt hier um die Ecke."
+9–15s — Bild: der Strauß in der Hand, unterwegs durch Warschauer Straßen Richtung Miodowa · Sprich: "Ein kurzer Weg mitten durch die Stadt."
+15–20s — Bild: die Blumen werden am Altar ins Gesteck arrangiert · Sprich: "Deutschsprachig — aber ganz und gar Teil dieser Stadt."
+20–24s — Endcard: das fertige Gesteck im warmen Licht + Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, leicht, mit sanftem Vorwärtsgefühl · 💡 Tipp: Beim Gehen mit den Blumen das Handy tief und ruhig führen und die Blumen im Vordergrund lassen — so wird der Weg durch die Stadt zur roten Linie des Clips.</t>
+        </is>
+      </c>
       <c r="M109" s="4" t="inlineStr"/>
-      <c r="N109" s="5" t="inlineStr"/>
+      <c r="N109" s="4" t="inlineStr"/>
+      <c r="O109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -6868,9 +7953,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L110" s="2" t="inlineStr"/>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Nahaufnahme der Kaffeemaschine, jemand drückt den Schalter — nichts passiert · Text (On-Screen): "Panne des Sonntags."
+3–8s — Bild: ratloses Schulterzucken, eine Hand klopft leicht gegen die Maschine · Sprich (locker, lachend): "Ausgerechnet heute streikt die Kaffeemaschine."
+8–13s — Bild: das Team beratschlagt lachend, jemand kommt mit einem Wasserkocher an · Sprich: "Aber aufgeben? Kommt bei uns nicht vor."
+13–18s — Bild: eine dampfende Tasse, ein Daumen hoch in die Kamera · Sprich: "Keine Hochglanz-Gemeinde. Nur echte Menschen. Komm so wie du bist — So 09:30, Miodowa 21."
+🎵 Musik: locker, augenzwinkernd, leicht · 💡 Tipp: Echt drehen, wenn wirklich mal was klemmt — das ehrliche Lachen des Teams kann man nicht nachstellen, und genau das macht den Clip sympathisch.</t>
+        </is>
+      </c>
       <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="3" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -6926,9 +8021,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L111" s="4" t="inlineStr"/>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: die letzten Gäste gehen durch die Tür, der Raum leert sich · Sprich (ruhig, warm): "Der Gottesdienst endet mit dem Segen. Die Arbeit noch nicht."
+4–9s — Bild: ein paar Hände stapeln Stühle, ordnen die Reihen · Sprich: "Während alle nach Hause gehen, bleiben ein paar da."
+9–15s — Bild: in der Küche wird Geschirr gespült und abgetrocknet · Sprich: "Sie spülen, räumen, machen sauber — Woche für Woche."
+15–20s — Bild: ein letzter Blick in den aufgeräumten Raum, dann geht das Licht aus · Text: "Danke an die Hände, die bleiben." + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, dankbar, leise · 💡 Tipp: Den Moment, in dem das Licht ausgeht, als letzte Einstellung nehmen und danach eine halbe Sekunde Schwarz stehen lassen — das gibt dem "Danke" Gewicht.</t>
+        </is>
+      </c>
       <c r="M111" s="4" t="inlineStr"/>
-      <c r="N111" s="5" t="inlineStr"/>
+      <c r="N111" s="4" t="inlineStr"/>
+      <c r="O111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -6984,9 +8089,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr"/>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1 (Cover): Foto des gedeckten Altars in der Totale · Text: "3 Dinge, die immer auf dem Altar stehen — und warum."
+Slide 2: Nahaufnahme der brennenden Kerzen · Text: "Die Kerzen. Licht, das bleibt — auch wenn's draußen dunkel wird."
+Slide 3: Nahaufnahme der aufgeschlagenen Bibel · Text: "Die Bibel. Das Wort, das trägt — Geschichten, die schon vielen Halt gegeben haben."
+Slide 4: Nahaufnahme Kreuz und Blumen · Text: "Das Kreuz. Der Grund, warum wir überhaupt da sind."
+Slide 5 (Abschluss): der ganze Altar im warmen Licht · Text: "Du musst nichts davon wissen, um willkommen zu sein. Sieh's dir aus der Nähe an — So 09:30, Miodowa 21."
+💡 Tipp: Jede Erklärung kurz halten (ein Satz pro Slide) und die Schrift unten platzieren, damit das Foto oben frei atmen kann — belehrend wird's, sobald der Text zu lang wird.</t>
+        </is>
+      </c>
       <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="3" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -7042,9 +8157,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L113" s="4" t="inlineStr"/>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Nahaufnahme der Hände am Klavier, ein paar erste Takte erklingen · Text (On-Screen): "Die Playlist vor dem Gottesdienst?"
+4–9s — Bild: kurzes Innehalten, eine schwierige Passage wird noch einmal gespielt · Text: "Kein Konzert. Kein Streaming."
+9–14s — Bild: Blick über die Schulter auf die handschriftlichen Noten · Sprich (leise, warm): "Nur jemand, der allein die Lieder durchgeht — damit sonntags alles klingt."
+14–18s — Bild: die letzten Töne klingen aus, leiser Raumklang · Text: "Hör's dir live an — So 09:30, Miodowa 21."
+🎵 Musik: KEINE zusätzliche Musik — nur das echte Klavier aus dem Bild · 💡 Tipp: Das Klavier direkt als Ton nehmen und nichts drüberlegen; nah ans Instrument gehen, damit der warme, unpolierte Klang trägt.</t>
+        </is>
+      </c>
       <c r="M113" s="4" t="inlineStr"/>
-      <c r="N113" s="5" t="inlineStr"/>
+      <c r="N113" s="4" t="inlineStr"/>
+      <c r="O113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -7100,9 +8225,21 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L114" s="2" t="inlineStr"/>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–2s — Bild: jemand deckt einen Tisch, große Zahl "1" blendet ein · Sprich (mit Schwung): "Wie viele Menschen stecken in einem einzigen Sonntag?"
+2–5s — Bild: schneller Schnitt, jemand zündet Kerzen an — Zahl "2" · Sprich: "Zwei..."
+5–8s — Bild: Hände am Klavier — Zahl "3" · Sprich: "drei..."
+8–11s — Bild: jemand begrüßt an der Tür — Zahl "4" · Sprich: "vier..."
+11–13s — Bild: jemand gießt Kaffee ein — Zahl "5" · Sprich: "fünf."
+13–16s — Endcard: Schlussbild mit Text "...und du wärst Nummer 6." + "So 09:30 · Miodowa 21"
+🎵 Musik: rhythmisch, treibend, jeder Beat auf einem Schnitt · 💡 Tipp: Alle Einstellungen ungefähr gleich lang schneiden und die Zahl im Takt der Musik einblenden — der Zähl-Effekt lebt vom gleichmäßigen Rhythmus.</t>
+        </is>
+      </c>
       <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="3" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
@@ -7158,9 +8295,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L115" s="4" t="inlineStr"/>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Start in der Küche, Handkamera setzt sich in Bewegung · Sprich (verspielt, wie ein Guide): "Willkommen zur exklusivsten Tour der Gemeinde."
+3–8s — Bild: die Kamera geht durch den Flur, vorbei an der Vorratsecke · Sprich: "Der kürzeste Weg von der Küche zum Altar — den kennt sonst nur das Team."
+8–13s — Bild: kurzer Stopp an einem Regal · Sprich: "Hier liegen die Kerzen. Streng geheim."
+13–18s — Bild: weiter bis zum Altar, Ankunft mit einem Augenzwinkern in die Kamera · Text: "Jetzt kennst du ihn auch. Komm vorbei — So 09:30, Miodowa 21."
+🎵 Musik: verspielt, leicht, mit Bewegung · 💡 Tipp: In einem einzigen durchgehenden Take laufen (kein Schnitt) und das Handy vor dem Körper führen — dieser "Walk-and-talk" wirkt am authentischsten, wenn er nicht zerschnitten ist.</t>
+        </is>
+      </c>
       <c r="M115" s="4" t="inlineStr"/>
-      <c r="N115" s="5" t="inlineStr"/>
+      <c r="N115" s="4" t="inlineStr"/>
+      <c r="O115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -7216,9 +8363,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L116" s="2" t="inlineStr"/>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–4s — Bild: Tassen werden eine nach der anderen aufgereiht, eine Zahl zählt bis "40" hoch · Sprich (locker): "Wir haben heute mal nachgezählt. Vierzig Tassen."
+4–9s — Bild: jetzt die Untertassen — die Zahl stockt bei "39" · Sprich: "Und... neununddreißig Untertassen."
+9–13s — Bild: ratloser Blick, jemand sucht kurz unter dem Tisch · Sprich: "Irgendwo lebt bei uns eine Tasse ganz ohne Partner."
+13–16s — Bild: Schulterzucken, Lachen in die Kamera · Text: "...passt schon. Komm auf einen Kaffee — So 09:30, Miodowa 21."
+🎵 Musik: leicht, tickend, augenzwinkernd · 💡 Tipp: Die Zahl beim Hochzählen groß und mittig einblenden und das Stocken bei 39 einen Tick länger stehen lassen — die kleine Pause ist die Pointe.</t>
+        </is>
+      </c>
       <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="3" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
@@ -7274,9 +8431,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L117" s="4" t="inlineStr"/>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: menschenleere Straße vor der Miodowa 21 im frühen Morgenlicht · Text (On-Screen): "Sonntagmorgen, 8 Uhr."
+4–8s — Bild: eine Person schließt die schwere Tür auf und geht hinein · Sprich (aus dem Off): "Während Warschau noch schläft, dreht sich hier schon ein Schlüssel im Schloss."
+8–13s — Bild: erste Handgriffe drinnen — Licht an, Jacke abgelegt · Sprich: "Jemand kommt immer zuerst."
+13–18s — Bild: O-Ton, die Person schaut kurz in die Kamera und sagt: "Ich mag die Stille, bevor alle kommen."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, morgendlich, sehr leise (im O-Ton-Moment ganz raus) · 💡 Tipp: Für den O-Ton nah rangehen und die Person einfach in einem Satz frei sprechen lassen — nicht auswendig lernen lassen, das echte Zögern macht ihn glaubwürdig.</t>
+        </is>
+      </c>
       <c r="M117" s="4" t="inlineStr"/>
-      <c r="N117" s="5" t="inlineStr"/>
+      <c r="N117" s="4" t="inlineStr"/>
+      <c r="O117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -7332,9 +8500,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L118" s="2" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: getropftes, erstarrtes Kerzenwachs am Altar in Nahaufnahme — daneben (oder als zweites Bild im Post) eine halb leere Tasse mit Kaffeerand und ein paar Kuchenkrümel · Bildaufbau/Licht: warmes, tief einfallendes Nachmittagslicht von der Seite, das die Wachstropfen glänzen und Schatten werfen lässt; nah und ruhig, viel Freiraum um das Detail · ggf. Text im Bild: "Die Spuren eines guten Sonntags."
+💡 Tipp: Kurz nach dem Kaffee fotografieren, solange das Licht noch warm ist — und die "Unordnung" bewusst nicht aufräumen, gerade das Ungeschönte trägt die Botschaft.</t>
+        </is>
+      </c>
       <c r="M118" s="2" t="inlineStr"/>
-      <c r="N118" s="3" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
@@ -7390,9 +8564,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L119" s="4" t="inlineStr"/>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–3s — Bild: die volle Kaffeetafel mit mehreren Kuchen nebeneinander · Sprich (locker, augenzwinkernd): "Wir haben eine wissenschaftlich fundierte Erkenntnis."
+3–7s — Bild: der Streuselkuchen wird angeschnitten, die ersten Stücke wandern auf Teller · Sprich: "Der Streuselkuchen ist IMMER als Erstes weg."
+7–12s — Bild: Zeitraffer der Tafel — der Streuselkuchen leert sich sichtbar schneller als die anderen · Sprich: "Jede Woche aufs Neue. Man kann drauf wetten."
+12–15s — Bild: der leere Streusel-Teller, daneben noch volle Kuchen · Text: "Sichere dir deins — So 09:30, Miodowa 21."
+🎵 Musik: leicht, fröhlich, mit Schmunzel-Faktor · 💡 Tipp: Für den Zeitraffer das Handy fest auf ein Stativ oder einen Stapel Bücher stellen und über die ganze Kaffeezeit laufen lassen — nur ein wirklich fixer Bildausschnitt macht das Leerwerden sichtbar.</t>
+        </is>
+      </c>
       <c r="M119" s="4" t="inlineStr"/>
-      <c r="N119" s="5" t="inlineStr"/>
+      <c r="N119" s="4" t="inlineStr"/>
+      <c r="O119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -7448,9 +8632,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L120" s="2" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: der leere Saal, absolute Ruhe (nur Raumton) · Text (On-Screen): "Dreh mal den Ton auf. 🔊"
+4–8s — Bild: erste Schritte, eine Tür geht, ein leises "Hallo" im Off · Text: "So klingt es, wenn sich ein leerer Raum füllt."
+8–13s — Bild: mehr Menschen kommen rein, Stühlerücken, das Gemurmel wächst · Text: "Von Stille zu Stimmen."
+13–18s — Bild: der volle Raum, warmes deutsches Stimmengewirr und Lachen · Text: "Von allein zu gemeinsam. Dieser Klang könnte auch deiner sein — So 09:30, Miodowa 21."
+🎵 Musik: KEINE Musik — der echte Raumton IST der Inhalt · 💡 Tipp: Ganz ohne Gerede aus dem Off filmen und den Originalton unbearbeitet lassen; wichtig ist ein ruhiger Drehort ohne Straßenlärm, damit der Übergang von Stille zu Stimmen hörbar wird.</t>
+        </is>
+      </c>
       <c r="M120" s="2" t="inlineStr"/>
-      <c r="N120" s="3" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
@@ -7506,9 +8700,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L121" s="4" t="inlineStr"/>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–4s — Bild: Nahaufnahme des leeren Liednummern-Bretts · Sprich (ruhig, warm): "Kein Bildschirm. Kein Beamer."
+4–9s — Bild: eine Hand nimmt eine Ziffernkarte und steckt sie sorgfältig ein · Sprich: "Bei uns werden die Liednummern noch von Hand gesteckt."
+9–13s — Bild: weitere Zahlen kommen nacheinander dazu, ruhige Schnitte · Sprich: "Ein kleines Stück Handarbeit in einer schnellen Welt."
+13–16s — Bild: das fertige Brett mit den Liednummern des Tages · Text: "Ja, das gibt's noch. Sing mit — So 09:30, Miodowa 21."
+🎵 Musik: ruhig, warm, ein wenig nostalgisch · 💡 Tipp: Ganz nah ans Brett gehen und den leisen Klick beim Einstecken der Zahlen als Ton mitnehmen — dieses kleine Geräusch macht das Analoge fühlbar.</t>
+        </is>
+      </c>
       <c r="M121" s="4" t="inlineStr"/>
-      <c r="N121" s="5" t="inlineStr"/>
+      <c r="N121" s="4" t="inlineStr"/>
+      <c r="O121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -7564,9 +8768,21 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L122" s="2" t="inlineStr"/>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–2s — Bild: Titelkarte über dem noch leeren Raum · Text (On-Screen): "Setup-Checkliste."
+2–5s — Bild: Kerzen werden angezündet · Text: "Kerzen ✓" (Häkchen ploppt auf)
+5–8s — Bild: Gesangbücher werden auf die Stühle gelegt · Text: "Gesangbücher ✓"
+8–10s — Bild: die Kaffeemaschine wird eingeschaltet · Text: "Kaffee ✓"
+10–12s — Bild: Blumen kommen an den Altar · Text: "Blumen ✓"
+12–15s — Bild: langsamer Schwenk über den fertigen Raum · Text: "Bereit für dich. Jetzt fehlst nur noch du — So 09:30, Miodowa 21."
+🎵 Musik: rhythmisch, befriedigend, jedes Häkchen auf einem Beat · 💡 Tipp: Jeden Handgriff nur 2–3 Sekunden filmen und das Häkchen exakt im Moment des "Fertig" einblenden — der Satisfying-Effekt kommt aus dem präzisen Timing von Bild und Haken.</t>
+        </is>
+      </c>
       <c r="M122" s="2" t="inlineStr"/>
-      <c r="N122" s="3" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
@@ -7622,9 +8838,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L123" s="4" t="inlineStr"/>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–4s — Bild: Nahaufnahme, jemand setzt sich auf den Stuhl — er kippelt hörbar · Text (On-Screen): "Jede Gemeinde hat diesen einen Stuhl."
+4–8s — Bild: ein zusammengefalteter Pappdeckel wird untergeschoben — er wackelt trotzdem weiter · Sprich (liebevoll, schmunzelnd): "Seit Jahren wackelt er. Und wird trotzdem nicht ausgetauscht."
+8–12s — Bild: augenzwinkernder Blick in die Kamera, kurzes Kippeln vorgeführt · Sprich: "Er gehört einfach dazu — so wie die Macken, die uns menschlich machen."
+12–15s — Bild: der Stuhl steht stolz in der Reihe · Text: "Wir lieben ihn trotzdem. Komm vorbei — So 09:30, Miodowa 21."
+🎵 Musik: leicht, verschmitzt, gemütlich · 💡 Tipp: Das leise Knarzen des Stuhls als Originalton mitnehmen — dieses echte Geräusch ist die Pointe und funktioniert besser als jeder Soundeffekt.</t>
+        </is>
+      </c>
       <c r="M123" s="4" t="inlineStr"/>
-      <c r="N123" s="5" t="inlineStr"/>
+      <c r="N123" s="4" t="inlineStr"/>
+      <c r="O123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -7680,9 +8906,19 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L124" s="2" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1 (Cover): ruhiges Foto des leeren, aufgeräumten Saals · Text: "Zwei Sonntage im Monat — aber was passiert dazwischen?"
+Slide 2: Foto vom Einkauf (Kaffee, Kerzen, Zutaten im Wagen) · Text: "Es wird eingekauft für den nächsten Gottesdienst."
+Slide 3: anonymisierter Screenshot der WhatsApp-Gruppe (Namen/Nummern unkenntlich) · Text: "In der Gruppe bleibt man in Kontakt — auch unter der Woche."
+Slide 4: jemand notiert die Liednummern oder plant den Ablauf am Küchentisch · Text: "Es wird geplant, überlegt, vorbereitet."
+Slide 5 (Abschluss): warmes Bild des vorbereiteten Raums · Text: "Gemeinde ist mehr als ein Sonntag. Sei auch dazwischen dabei — Link in Bio → WhatsApp-Gruppe."
+💡 Tipp: Beim WhatsApp-Screenshot unbedingt alle Namen, Profilbilder und Nummern schwärzen, bevor er in den Post kommt — lieber einmal zu vorsichtig als eine Nummer versehentlich öffentlich.</t>
+        </is>
+      </c>
       <c r="M124" s="2" t="inlineStr"/>
-      <c r="N124" s="3" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
@@ -7738,9 +8974,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L125" s="4" t="inlineStr"/>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: nur Hände — sie gießen Kaffee in eine Tasse ein · Sprich (leise, warm): "Manche Hände stehen nie im Rampenlicht."
+4–8s — Bild: Hände zünden eine Kerze an · Sprich: "Sie zünden Kerzen an..."
+8–11s — Bild: Hände rücken einen Stuhl gerade · Sprich: "...rücken Stühle zurecht..."
+11–14s — Bild: Hände legen Gesangbücher aus · Sprich: "...legen alles bereit. Ganz ohne Applaus."
+14–18s — Bild: Schlussbild des fertigen Raums · Text: "Ohne sie kein Sonntag. Danke. Lern sie kennen — So 09:30, Miodowa 21."
+🎵 Musik: ruhig, warm, dankbar · 💡 Tipp: Konsequent nur die Hände filmen, nie die Gesichter — dieser bewusste Bildausschnitt macht die Botschaft "die man nicht sieht" auch visuell spürbar und schützt die Privatsphäre der Helfer:innen.</t>
+        </is>
+      </c>
       <c r="M125" s="4" t="inlineStr"/>
-      <c r="N125" s="5" t="inlineStr"/>
+      <c r="N125" s="4" t="inlineStr"/>
+      <c r="O125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -7796,9 +9043,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L126" s="2" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~17s
+0–3s — Bild: eine Hand zieht die Schublade auf, die Kamera blickt hinein · Sprich (neugierig, verspielt): "Jede Gemeinde hat diese eine Schublade."
+3–7s — Bild: Ersatzkerzen werden herausgehalten · Sprich: "Ersatzkerzen — logisch."
+7–11s — Bild: ein altes Nähset taucht auf · Sprich: "Ein Nähset, das schon ewig hier liegt."
+11–14s — Bild: eine zweifelhafte Packung Teegebäck · Sprich: "Und... wie lange liegt DAS eigentlich hier?"
+14–17s — Bild: die Schublade wird zugeschoben, Lachen · Text: "So echt, so unperfekt, so wir. Lern uns kennen — So 09:30, Miodowa 21."
+🎵 Musik: verspielt, neugierig, leicht · 💡 Tipp: Beim Öffnen der Schublade nah rangehen und den Fund beim Teegebäck einen Moment länger stehen lassen — die kleine Überraschung ist die Pointe und braucht Zeit zum Wirken.</t>
+        </is>
+      </c>
       <c r="M126" s="2" t="inlineStr"/>
-      <c r="N126" s="3" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
@@ -7854,9 +9112,19 @@
           <t>Link in Bio → neue Website ansehen</t>
         </is>
       </c>
-      <c r="L127" s="4" t="inlineStr"/>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Person sitzt ruhig am Fenster, warmes Licht, schaut kurz auf und dann direkt in die Kamera · Text: "Wir haben kurz nachgedacht."
+3–9s — Bild: Naher Einzeltake, direkt in die Kamera gesprochen · Sprich: "Ehrlich gesagt: Wir wollten einfach, dass man uns leichter findet."
+9–14s — Bild: Weiter im selben Take, ein kleines Lächeln · Sprich: "Deshalb haben wir eine neue Seite gebaut — schlicht, klar, für dich."
+14–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Neue Seite. Gleiche offene Tür."
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: Handy an ein Fensterbrett lehnen für einen stabilen Take, dann fühlt sich der Blick in die Kamera ruhig an — nicht verkrampft halten.</t>
+        </is>
+      </c>
       <c r="M127" s="4" t="inlineStr"/>
-      <c r="N127" s="5" t="inlineStr"/>
+      <c r="N127" s="4" t="inlineStr"/>
+      <c r="O127" s="5" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -7912,9 +9180,19 @@
           <t>Link in Bio → neue Startseite entdecken</t>
         </is>
       </c>
-      <c r="L128" s="2" t="inlineStr"/>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Screenrecording, die neue Startseite öffnet sich · Sprich (Voice-over): "Das hier ist der erste Klick auf unsere neue Seite."
+3–10s — Bild: Langsames, ruhiges Scrollen über die Startseite · Sprich: "Wir wollten, dass du nicht suchen musst — sondern sofort siehst, was zählt."
+10–16s — Bild: Kurz anhalten auf der Gottesdienst-Info (Zeit &amp; Ort) · Sprich: "Das hier war mir am wichtigsten: wann wir feiern und wo. Ganz oben, gleich sichtbar."
+16–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Alles auf einen Blick"
+🎵 Musik: warm, leise, im Hintergrund unter der Stimme · 💡 Tipp: Beim Screenrecording langsam scrollen — lieber zu langsam als zu schnell, das wirkt ruhig und wertig.</t>
+        </is>
+      </c>
       <c r="M128" s="2" t="inlineStr"/>
-      <c r="N128" s="3" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
@@ -7970,9 +9248,15 @@
           <t>Link in Bio → die neue Seite live sehen</t>
         </is>
       </c>
-      <c r="L129" s="4" t="inlineStr"/>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Screenshot der alten Seite, oben klein die Textmarke "Vorher" — kein Spott, nur ehrlich. / Slide 2: Screenshot der neuen Startseite, Textmarke "Jetzt" — klar und aufgeräumt. / Slide 3: Textkarte in Aubergine mit Lutherrose, groß: "Es war Zeit." / Slide 4: Textkarte, warm: "Gleiche offene Tür — nur ein neuer Weg dorthin. Sonntag 09:30, Miodowa 21."
+💡 Tipp: Beide Screenshots im gleichen Handy-Hochformat aufnehmen, damit Slide 1 und 2 exakt gleich groß wirken — der Vergleich zieht nur, wenn der Rahmen identisch ist.</t>
+        </is>
+      </c>
       <c r="M129" s="4" t="inlineStr"/>
-      <c r="N129" s="5" t="inlineStr"/>
+      <c r="N129" s="4" t="inlineStr"/>
+      <c r="O129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -8028,9 +9312,15 @@
           <t>Link in Bio → Termine &amp; Adresse ansehen</t>
         </is>
       </c>
-      <c r="L130" s="2" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Textkarte in Aubergine, groß: "In 10 Sekunden gefunden." Klein darunter: "3 Fragen, 3 Klicks." / Slide 2: Screenshot der Termin-Übersicht, Überschrift "1. Wann ist Gottesdienst?" — Antwort schon im Bild sichtbar: So 09:30. / Slide 3: Screenshot der Karte, Überschrift "2. Wo genau ist das?" — ul. Miodowa 21. / Slide 4: Screenshot der Kontaktseite, Überschrift "3. Wen kann ich fragen?" / Slide 5: Textkarte, warm: "Und wenn du magst: komm einfach vorbei. Wir freuen uns auf dich."
+💡 Tipp: Auf jedem Screenshot die relevante Stelle mit einem dezenten Aubergine-Rahmen oder Pfeil markieren, damit das Auge sofort weiß, wo es hinschauen soll.</t>
+        </is>
+      </c>
       <c r="M130" s="2" t="inlineStr"/>
-      <c r="N130" s="3" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
@@ -8086,9 +9376,19 @@
           <t>Link in Bio → selbst überzeugen</t>
         </is>
       </c>
-      <c r="L131" s="4" t="inlineStr"/>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~19s
+0–4s — Bild: Person am Küchentisch, Kaffeetasse daneben, warmes Morgenlicht, schaut ruhig auf · Sprich: "Warum überhaupt eine neue Seite? Ganz ehrlich?"
+4–11s — Bild: Nah, entspannt, kein Skript-Gefühl · Sprich: "Wer neu nach Warschau kommt, googelt zuerst. Und wir wollten, dass man uns dann auch findet."
+11–16s — Bild: Weiter im Take, ruhiger Ton · Sprich: "Nicht nur findet — sondern sich gleich willkommen fühlt."
+16–19s — Endcard: Handy mit geöffneter Seite, Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, sehr leise · 💡 Tipp: Am Küchentisch mit echtem Tageslicht filmen — kein Deckenlicht. Morgenlicht von der Seite macht das Gesicht weich und nahbar.</t>
+        </is>
+      </c>
       <c r="M131" s="4" t="inlineStr"/>
-      <c r="N131" s="5" t="inlineStr"/>
+      <c r="N131" s="4" t="inlineStr"/>
+      <c r="O131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -8144,9 +9444,20 @@
           <t>Link in Bio → WhatsApp-Gruppe beitreten</t>
         </is>
       </c>
-      <c r="L132" s="2" t="inlineStr"/>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Person halbnah in vertrauter Umgebung, schaut ruhig auf · Text: "Der Mensch hinter der Seite"
+3–8s — Bild: Ruhiger Einzeltake · Sprich: "Ich bin kein Techniker, ehrlich nicht."
+8–15s — Bild: Weiter im Take, warm und leise · Sprich: "Mir ging es nur um eins: dass sich niemand verloren fühlt, der uns sucht."
+15–18s — Bild: Schnitt auf Hände am Handy mit geöffneter Seite · Text: "Von Hand gemacht, mit Herz."
+18–20s — Endcard: Lutherrose + "Schreib uns · WhatsApp in Bio"
+🎵 Musik: warm, dezent, fast unhörbar · 💡 Tipp: Bewusst eine kleine Sprechpause vor dem Satz "dass sich niemand verloren fühlt" lassen — die Stille macht den Satz stark.</t>
+        </is>
+      </c>
       <c r="M132" s="2" t="inlineStr"/>
-      <c r="N132" s="3" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
@@ -8202,9 +9513,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L133" s="4" t="inlineStr"/>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–2s — Bild: Person A hält handgeschriebenen Zettel hoch, senkt ihn vors Gesicht weg · Text/Zettel: "Offen."
+2–5s — Bild: Harter Schnitt, Person B, gleiche Bewegung, gleicher Bildausschnitt · Text/Zettel: "Nah."
+5–8s — Bild: Person C · Text/Zettel: "Deutschsprachig."
+8–11s — Bild: Person D · Text/Zettel: "Für dich."
+11–15s — Endcard: Alle vier Zettel kurz nebeneinander, dann Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm mit klarem Beat, damit die Schnitte auf den Takt sitzen · 💡 Tipp: Alle Personen an derselben Stelle mit gleichem Bildausschnitt filmen — dann sitzen die Zettel im Schnitt exakt übereinander und die Serie wirkt wie aus einem Guss.</t>
+        </is>
+      </c>
       <c r="M133" s="4" t="inlineStr"/>
-      <c r="N133" s="5" t="inlineStr"/>
+      <c r="N133" s="4" t="inlineStr"/>
+      <c r="O133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -8260,9 +9582,19 @@
           <t>Link in Bio → Route zur Miodowa 21 öffnen</t>
         </is>
       </c>
-      <c r="L134" s="2" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~17s
+0–3s — Bild: Screenrecording, neue Seite offen, Finger tippt auf die Karte · Sprich (Voice-over): "In einer neuen Stadt willst du dich nicht verlaufen."
+3–9s — Bild: Route nach Miodowa 21 öffnet sich, kurz die Strecke zeigen · Sprich: "Ein Klick auf der Seite — und die Route zu uns ist offen."
+9–14s — Bild: Schnitt auf ein echtes Foto der Tür an der Miodowa 21 · Sprich: "Hier ist es. Genau diese Tür."
+14–17s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Wir sehen uns dort."
+🎵 Musik: ruhig, freundlich · 💡 Tipp: Für das Türfoto kurz warten, bis natürliches Licht auf die Tür fällt — eine offene oder leicht angelehnte Tür wirkt einladender als eine geschlossene.</t>
+        </is>
+      </c>
       <c r="M134" s="2" t="inlineStr"/>
-      <c r="N134" s="3" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
@@ -8318,9 +9650,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L135" s="4" t="inlineStr"/>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Ruhige Nahaufnahme einer brennenden Kerze am Altar, Flamme bewegt sich leicht · Text: "Was bleibt?"
+4–9s — Bild: Aufgeschlagenes Gesangbuch, eine Hand blättert sanft eine Seite um · Text: "Neue Seite."
+9–14s — Bild: Langsamer Schwenk durch den warmen Kirchenraum · Text: "Gleiche offene Tür."
+14–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Gleicher Glaube, gleiche Wärme."
+🎵 Musik: sehr ruhig, getragen, fast still · 💡 Tipp: Dieses Reel lebt von Langsamkeit — jede Einstellung mindestens 4 Sekunden halten und die Kamera nur ganz behutsam bewegen. Keine schnellen Schnitte.</t>
+        </is>
+      </c>
       <c r="M135" s="4" t="inlineStr"/>
-      <c r="N135" s="5" t="inlineStr"/>
+      <c r="N135" s="4" t="inlineStr"/>
+      <c r="O135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -8376,9 +9718,20 @@
           <t>Folgen für Teil 2 &amp; 3</t>
         </is>
       </c>
-      <c r="L136" s="2" t="inlineStr"/>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Person halbnah im Synodalsaal, ruhig gefilmt · Text: "Neuausrichtung — Teil 1"
+3–9s — Bild: Ruhiger Take, direkt gesprochen · Sprich: "Bevor wir sagen, wohin wir wollen — kurz, woher wir kommen."
+9–15s — Bild: Weiter im Take, warm · Sprich: "Eine kleine, ehrenamtliche Gemeinde. Seit vielen Jahren ein Stück Heimat für Deutschsprachige hier in Warschau."
+15–18s — Bild: Schnitt auf ein Detail des Raumes oder ein altes Foto · Text: "Das Fundament fürs Wohin"
+18–20s — Endcard: Lutherrose + "Teil 2 &amp; 3 folgen — bleib dran"
+🎵 Musik: ruhig, leicht nostalgisch, dezent · 💡 Tipp: Am Ende bewusst auf das Wort "bleib dran" enden — das lädt zum Folgen ein und hält die Mini-Reihe zusammen.</t>
+        </is>
+      </c>
       <c r="M136" s="2" t="inlineStr"/>
-      <c r="N136" s="3" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
@@ -8434,9 +9787,19 @@
           <t>Link in Bio → WhatsApp-Gruppe beitreten</t>
         </is>
       </c>
-      <c r="L137" s="4" t="inlineStr"/>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~19s
+0–3s — Bild: Person direkt in die Kamera, warmes Licht · Text: "Neuausrichtung — Teil 2"
+3–10s — Bild: Ruhiger, warmer Take · Sprich: "Für wen sind wir da? Für dich — wenn du neu in Warschau bist und deine Sprache vermisst."
+10–15s — Bild: Schnitt auf Menschen im Gespräch beim Kirchenkaffee · Sprich (Voice-over): "Hier hörst du sonntags ein deutsches: Schön, dass du da bist."
+15–19s — Endcard: Lutherrose + "Komm dazu · WhatsApp in Bio"
+🎵 Musik: warm, einladend, leise · 💡 Tipp: Den Satz "Schön, dass du da bist" wörtlich und langsam sprechen — er ist das Herz des Clips und darf nicht untergehen.</t>
+        </is>
+      </c>
       <c r="M137" s="4" t="inlineStr"/>
-      <c r="N137" s="5" t="inlineStr"/>
+      <c r="N137" s="4" t="inlineStr"/>
+      <c r="O137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -8492,9 +9855,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L138" s="2" t="inlineStr"/>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Person ruhig in die Kamera, gedämpftes, warmes Licht · Text: "Neuausrichtung — Teil 3"
+3–10s — Bild: Ruhiger, leiser Take · Sprich: "Wir haben keine große Vision. Ehrlich nicht."
+10–15s — Bild: Weiter im Take, sehr warm · Sprich: "Nur einen leisen Wunsch: dass sich hier jemand weniger allein fühlt. Vielleicht du."
+15–18s — Endcard: Schnitt auf offene Kirchentür mit warmem Licht dahinter, Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, getragen · 💡 Tipp: Das Schlussbild mit der offenen Tür ein paar Sekunden stehen lassen — das offene Licht ist die Einladung, kein Text nötig.</t>
+        </is>
+      </c>
       <c r="M138" s="2" t="inlineStr"/>
-      <c r="N138" s="3" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
@@ -8550,9 +9923,19 @@
           <t>Link in Bio → nächsten Gottesdienst finden</t>
         </is>
       </c>
-      <c r="L139" s="4" t="inlineStr"/>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~17s
+0–3s — Bild: Screenrecording, neue Seite öffnet sich · Sprich (Voice-over): "Diese eine Seite haben wir ganz für dich gebaut."
+3–9s — Bild: Zügig zur Gottesdienst-Übersicht scrollen, kurz anhalten · Sprich: "In fünf Sekunden siehst du, wann wir uns das nächste Mal treffen."
+9–13s — Bild: Auf das nächste Datum tippen/zeigen · Sprich: "Kein Suchen, keine Ausreden."
+13–17s — Endcard: Schnitt auf den vorbereiteten Synodalsaal, Lutherrose + "So 09:30 · Miodowa 21" · Text: "Komm einfach vorbei."
+🎵 Musik: freundlich, leicht, dezent · 💡 Tipp: Beim Schlussbild vom Synodalsaal ein paar Stühle bewusst hell und einladend ins Licht rücken — ein vorbereiteter Raum sagt "wir warten auf dich".</t>
+        </is>
+      </c>
       <c r="M139" s="4" t="inlineStr"/>
-      <c r="N139" s="5" t="inlineStr"/>
+      <c r="N139" s="4" t="inlineStr"/>
+      <c r="O139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -8608,9 +9991,15 @@
           <t>Link in Bio → neue Seite ansehen</t>
         </is>
       </c>
-      <c r="L140" s="2" t="inlineStr"/>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Eine Person hält das Handy mit der geöffneten neuen Startseite, schaut darauf mit einem echten, unposierten Lächeln — kein Blick in die Kamera. · Bildaufbau/Licht: Weiches, natürliches Fensterlicht von der Seite, Person leicht aus der Mitte, das Handy-Display gut lesbar und scharf. Ruhiger, warmer Hintergrund (Kirchenraum oder Küchentisch), nicht überladen. Hochformat. · ggf. Text im Bild: "Von Hand gemacht, mit Herz."
+💡 Tipp: Auf den Auslöser drücken, während die Person wirklich auf den Bildschirm schaut, nicht in die Kamera — echte Blicke aufs eigene Werk wirken warm; gestellte Kamerablicke wirken sofort kühl.</t>
+        </is>
+      </c>
       <c r="M140" s="2" t="inlineStr"/>
-      <c r="N140" s="3" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
@@ -8666,9 +10055,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L141" s="4" t="inlineStr"/>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Ruhige Aufnahme einer offenen Tür mit warmem Licht dahinter · Text: "Du musst nichts mitbringen."
+3–6s — Bild: Warmer, leerer Raum, sanftes Licht · Text: "Kein Login."
+6–9s — Bild: Brennende Kerze in Nahaufnahme · Text: "Keine Anmeldung."
+9–12s — Bild: Blick in den einladenden Raum · Text: "Kein Vorwissen."
+12–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Nur du. Das reicht."
+🎵 Musik: ruhig, warm, leicht · 💡 Tipp: Die Textkarten immer an derselben Bildposition einblenden, damit das Auge ruhig bleibt und die Botschaft "nichts nötig" auch visuell entspannt wirkt.</t>
+        </is>
+      </c>
       <c r="M141" s="4" t="inlineStr"/>
-      <c r="N141" s="5" t="inlineStr"/>
+      <c r="N141" s="4" t="inlineStr"/>
+      <c r="O141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -8724,9 +10124,17 @@
           <t>Frage per Sticker stellen → Antwort mit Link zur Seite</t>
         </is>
       </c>
-      <c r="L142" s="2" t="inlineStr"/>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Story-Serie ~15s pro Slide
+Story 1 (Frage sammeln) — Bild: Ruhiger Aubergine-Hintergrund oder kurzes Video aus dem Kirchenraum, mittig der Frage-Sticker · Text/Sticker: "Was wolltet ihr schon immer über uns wissen? 💬" · dazu On-Screen: "Anlässlich unserer neuen Seite — fragt uns alles, wir antworten ehrlich."
+Story 2+ (Antworten, je eingegangene Frage) — Bild: Person spricht kurz in die Kamera ODER Screenrecording der passenden Website-Stelle · Sprich: "Gute Frage — hier die ehrliche Antwort:" [Antwort in 1–2 Sätzen] · dann Link-Sticker auf die passende Seite setzen, On-Screen: "Mehr dazu auf der Seite ⬆️"
+🎵 Musik: dezent, warm · 💡 Tipp: Jede Antwort-Story mit dem Link-Sticker direkt auf die passende Unterseite (Termine, Karte, Kontakt) verlinken — so wird aus jeder Frage ein sanfter Klick auf die Website.</t>
+        </is>
+      </c>
       <c r="M142" s="2" t="inlineStr"/>
-      <c r="N142" s="3" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n">
@@ -8782,9 +10190,19 @@
           <t>Link in Bio → WhatsApp-Gruppe beitreten</t>
         </is>
       </c>
-      <c r="L143" s="4" t="inlineStr"/>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Screenrecording, neue Seite offen, Finger fährt zum WhatsApp-Button · Sprich (Voice-over): "Warten bis Sonntag kann lang sein, wenn man neu ist."
+3–8s — Bild: Auf den WhatsApp-Button tippen, der Beitritts-Dialog öffnet sich · Sprich: "Deshalb ist unsere Gruppe jetzt nur einen Klick entfernt."
+8–13s — Bild: Kurz den Dialog zeigen · Sprich: "Und keine Sorge — du darfst auch einfach still mitlesen. Niemand muss sofort was schreiben."
+13–16s — Endcard: Lutherrose + "WhatsApp-Gruppe · Link in Bio" · Text: "Nicht allein bis Sonntag."
+🎵 Musik: warm, freundlich, leise · 💡 Tipp: Beim Screenrecording vorher alle privaten Namen und Nummern im Beitritts-Dialog prüfen — im Zweifel den Dialog nur kurz und unscharf zeigen oder einen leeren Test-Screen verwenden.</t>
+        </is>
+      </c>
       <c r="M143" s="4" t="inlineStr"/>
-      <c r="N143" s="5" t="inlineStr"/>
+      <c r="N143" s="4" t="inlineStr"/>
+      <c r="O143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -8840,9 +10258,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L144" s="2" t="inlineStr"/>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Vertraute Person aus der Gemeinde, ruhig, warm in die Kamera · Sprich: "An alle, die uns schon lange kennen: keine Sorge."
+4–11s — Bild: Ruhiger Einzeltake · Sprich: "Neuausrichtung heißt nicht, dass wir andere werden. Es bleibt eure Gemeinde, euer Raum, euer Sonntag."
+11–15s — Bild: Schnitt auf die weit geöffnete Kirchentür · Sprich: "Nur die Tür steht jetzt für noch mehr Menschen offen."
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Text: "Wir sehen uns."
+🎵 Musik: warm, beruhigend, dezent · 💡 Tipp: Für dieses Reel bewusst ein bekanntes, vertrautes Gesicht aus der Gemeinde wählen — bei den Stammleuten wirkt Vertrautheit stärker als jede schöne Formulierung.</t>
+        </is>
+      </c>
       <c r="M144" s="2" t="inlineStr"/>
-      <c r="N144" s="3" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
@@ -8898,9 +10326,19 @@
           <t>Countdown-Erinnerung aktivieren → zum Launch Link in Bio</t>
         </is>
       </c>
-      <c r="L145" s="4" t="inlineStr"/>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Story-Serie, 1 Slide pro Tag (~10s)
+Tag 3 — Bild: Verschwommener Teaser-Screenshot der Startseite, darüber der Countdown-Sticker (3 Tage) · Text: "In 3 Tagen live. 👀 Aktiviert die Erinnerung am Sticker."
+Tag 2 — Bild: Verschwommenes Detail der Karte / Adresse, Countdown-Sticker (2 Tage) · Text: "Bald findest du alles auf einen Blick — auch den Weg zu uns."
+Tag 1 — Bild: Verschwommene Gottesdienst-Übersicht, Countdown-Sticker (1 Tag) · Text: "Morgen ist es so weit. Countdown läuft."
+Launch-Tag — Bild: Scharfer Reveal der Live-Seite, kleines Screenrecording · Text: "Jetzt live! Link in Bio ⬆️"
+🎵 Musik: leicht, vorfreudig, dezent · 💡 Tipp: Die Teaser-Screenshots nur leicht verwischen (Weichzeichner), nicht komplett unkenntlich — man soll neugierig werden, nicht ratlos.</t>
+        </is>
+      </c>
       <c r="M145" s="4" t="inlineStr"/>
-      <c r="N145" s="5" t="inlineStr"/>
+      <c r="N145" s="4" t="inlineStr"/>
+      <c r="O145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -8956,9 +10394,19 @@
           <t>Link in Bio → uns finden &amp; teilen</t>
         </is>
       </c>
-      <c r="L146" s="2" t="inlineStr"/>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–3s — Bild: Nahaufnahme der Hände am Handy, leere Suchleiste · Sprich (Voice-over): "Kleiner Moment, große Freude."
+3–8s — Bild: Wort für Wort "evangelisch deutsch Warschau" in die Suche tippen, dann Enter · Sprich: "Man tippt einfach ein, was einem im Kopf ist."
+8–13s — Bild: Das eigene Suchergebnis erscheint, kurzer Zoom drauf · Sprich: "Und da sind wir. Genau dafür war die neue Seite da."
+13–15s — Endcard: Lutherrose + "Finde uns · Link in Bio" · Text: "Wieder auffindbar."
+🎵 Musik: freundlich, leicht beschwingt · 💡 Tipp: Das Tippen in echter Handy-Perspektive von schräg oben filmen — reale Finger auf echter Tastatur wirken glaubwürdiger als ein sauberes Screenrecording.</t>
+        </is>
+      </c>
       <c r="M146" s="2" t="inlineStr"/>
-      <c r="N146" s="3" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="3" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
@@ -9014,9 +10462,15 @@
           <t>Link in Bio → die neue Seite ansehen</t>
         </is>
       </c>
-      <c r="L147" s="4" t="inlineStr"/>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Sehr nahe, ruhige Aufnahme der Lutherrose oder einer satten Aubergine-Fläche der neuen Seite — ein einziges Detail, formatfüllend. · Bildaufbau/Licht: Weiches, seitliches Licht, das die Farbe tief und würdevoll wirken lässt; ruhiger, unaufgeregter Bildaufbau, viel Farbe, wenig Ablenkung. Optional als zweites Bild dasselbe Motiv als echtes Detail im Kirchenraum daneben. · ggf. Text im Bild: "Warum diese Farbe? Aubergine &amp; Lutherrose — Würde, die man sehen soll."
+💡 Tipp: Die Aubergine-Farbe nicht mit Blitz fotografieren — Blitz macht sie flach und grell. Weiches Tageslicht lässt den tiefen, würdevollen Ton erst richtig wirken.</t>
+        </is>
+      </c>
       <c r="M147" s="4" t="inlineStr"/>
-      <c r="N147" s="5" t="inlineStr"/>
+      <c r="N147" s="4" t="inlineStr"/>
+      <c r="O147" s="5" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -9072,9 +10526,19 @@
           <t>Teilen → schick den Link an jemanden, der neu hier ist</t>
         </is>
       </c>
-      <c r="L148" s="2" t="inlineStr"/>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~17s
+0–4s — Bild: Ruhige Bilder vom Ankommen — ein Koffer, fremde Warschauer Straßen · Sprich (Voice-over): "Neu in einer Stadt zu sein, ist manchmal ganz schön einsam."
+4–10s — Bild: Schnitt auf die offene Kirchentür, dann die Seite am Handy · Sprich: "Kennst du jemanden, der gerade neu hier ist und Anschluss sucht?"
+10–14s — Bild: Textkarte über warmem Bild · Sprich: "Schick ihm einfach diesen Link. Als kleines Geschenk."
+14–17s — Endcard: Lutherrose + "Teilen · Link in Bio" · Text: "Damit niemand allein ankommt."
+🎵 Musik: warm, leicht wehmütig, dann aufhellend · 💡 Tipp: Den Koffer-/Straßen-Teil bewusst etwas kühler und einsamer filmen, den Kirchen-Teil warm und hell — der Bildkontrast erzählt die Botschaft schon ohne Worte.</t>
+        </is>
+      </c>
       <c r="M148" s="2" t="inlineStr"/>
-      <c r="N148" s="3" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
@@ -9130,9 +10594,15 @@
           <t>Link in Bio → in 10 Sekunden zu uns finden</t>
         </is>
       </c>
-      <c r="L149" s="4" t="inlineStr"/>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Screenshot der alten Seite, darüber warme Textkarte: "Vorher-Gefühl: kaum zu finden." / Slide 2: Screenshot der neuen Startseite, Textkarte: "Nachher-Gefühl: in 10 Sekunden hin." / Slide 3: Textkarte in Aubergine mit Lutherrose, groß: "Damit dich nichts mehr aufhält, uns kennenzulernen." / Slide 4: Textkarte, warm: "Wisch durch — und komm gern vorbei. Sonntag 09:30, Miodowa 21."
+💡 Tipp: Hier zählt das Gefühl, nicht die Technik — die Textkarten emotional halten ("kaum zu finden" / "in 10 Sekunden hin"), nicht über Ladezeiten oder Menüs reden.</t>
+        </is>
+      </c>
       <c r="M149" s="4" t="inlineStr"/>
-      <c r="N149" s="5" t="inlineStr"/>
+      <c r="N149" s="4" t="inlineStr"/>
+      <c r="O149" s="5" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -9188,9 +10658,20 @@
           <t>Link in Bio → neue Seite entdecken</t>
         </is>
       </c>
-      <c r="L150" s="2" t="inlineStr"/>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s · komplett ohne gesprochene Worte
+0–4s — Bild: Offene Kirchentür, Morgenlicht fällt langsam in den Raum · kein Text
+4–8s — Bild: Hände richten ruhig eine Stuhlreihe, rücken sie gerade · kein Text
+8–12s — Bild: Ein Tisch wird gedeckt, eine Kerze wird angezündet · kein Text
+12–16s — Bild: Ein Handy mit der geöffneten neuen Seite wird sanft ins Bild gehalten · kein Text
+16–20s — Endcard: Schwarz/Aubergine, Lutherrose erscheint, ein Wort: "Willkommen." darunter klein "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, getragen, warm — die Musik trägt das ganze Reel, da keine Stimme · 💡 Tipp: Alle Bewegungen langsam und bewusst filmen und die Schnitte auf die Musik legen — ohne Worte entscheidet allein der Rhythmus über die Stimmung.</t>
+        </is>
+      </c>
       <c r="M150" s="2" t="inlineStr"/>
-      <c r="N150" s="3" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" s="3" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
@@ -9246,9 +10727,15 @@
           <t>Komm vorbei → Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L151" s="4" t="inlineStr"/>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Textkarte in Aubergine mit Lutherrose, groß: "Danke an die, die mitgebaut haben." / Slide 2: Porträt eines Ehrenamtlichen, natürliches Licht, echtes Lächeln, Text: "Anna — hat die Texte geschrieben." (Vorname + ein Wort zur Rolle, nur mit Einverständnis) / Slide 3: Nächstes Porträt, Text: "Thomas — hat die Fotos gemacht." / Slide 4: Nächstes Porträt, Text: "Martin — hatte die Idee." / Slide 5: Textkarte, warm: "Von Hand gemacht, mit Herz." / Slide 6: Textkarte: "Und du? Komm vorbei und lern uns kennen. Sonntag 09:30, Miodowa 21."
+💡 Tipp: Vor dem Posten von jedem abgebildeten Menschen kurz das Einverständnis einholen — bei einem kleinen Ehrenamts-Team ist das schnell gefragt und schützt alle.</t>
+        </is>
+      </c>
       <c r="M151" s="4" t="inlineStr"/>
-      <c r="N151" s="5" t="inlineStr"/>
+      <c r="N151" s="4" t="inlineStr"/>
+      <c r="O151" s="5" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -9304,9 +10791,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L152" s="2" t="inlineStr"/>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Person sitzt ruhig, schaut in die Kamera, Handy auf Augenhöhe, weiches Tageslicht am Fenster · Text: "Muss ich glauben, um zu kommen?"
+3–8s — Bild: gleiche Einstellung, Person spricht ruhig · Sprich: "Du musst nichts glauben, nichts können, nichts sagen."
+8–14s — Bild: Person hält kurz inne, leichtes Lächeln · Sprich: "Komm einfach, wie du bist."
+14–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, sehr dezent im Hintergrund · 💡 Tipp: Ein einziger Take, kein Schnitt mitten im Satz – lieber 3-mal aufnehmen und den ehrlichsten nehmen.</t>
+        </is>
+      </c>
       <c r="M152" s="2" t="inlineStr"/>
-      <c r="N152" s="3" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" s="3" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
@@ -9362,9 +10859,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – in dem, worin du dich wohlfühlst</t>
         </is>
       </c>
-      <c r="L153" s="4" t="inlineStr"/>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Textkarte in Aubergine, große Schrift · Text: "Was ziehst du an?"
+3–12s — Bild: 6–8 kurze Clips einzelner Leute, je ~1s, im Takt geschnitten – Jeans-Pulli, Sakko, Bluse, Sneaker, Mantel · Text (wandert mit): "Jeans?" … "Sakko?" … "Pulli?"
+12–16s — Bild: letzte Person zuckt lachend mit den Schultern · Text: "Es gibt keinen Dresscode"
+16–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" + kleine Zeile "Komm, worin du dich wohlfühlst"
+🎵 Musik: locker, leichter Beat mit klarem Takt für die Schnitte · 💡 Tipp: Alle Clips gleich hoch (hochkant 9:16) filmen und die Schnitte genau auf den Beat setzen – das macht den Rhythmus.</t>
+        </is>
+      </c>
       <c r="M153" s="4" t="inlineStr"/>
-      <c r="N153" s="5" t="inlineStr"/>
+      <c r="N153" s="4" t="inlineStr"/>
+      <c r="O153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -9420,9 +10927,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – Weg im Reel</t>
         </is>
       </c>
-      <c r="L154" s="2" t="inlineStr"/>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–3s — Bild: Start an der Tram-Haltestelle, Handy in der Hand · Sprich: "So findest du uns – ganz easy."
+3–9s — Bild: mitlaufen, ruhig geführt, die Straße entlang Richtung Miodowa · Text: "Von der Tram → 5 Min zu Fuß"
+9–14s — Bild: kurzer Schwenk zum nächsten Parkplatz um die Ecke · Text: "Mit dem Auto? Parkplatz gleich um die Ecke"
+14–19s — Bild: die letzten Meter bis zur Tür, Kamera stoppt am Eingang · Sprich: "Und hier bist du richtig."
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: freundlich, unaufdringlich, mittleres Tempo · 💡 Tipp: Beim Laufen das Handy mit beiden Händen dicht am Körper halten und langsam gehen – das ersetzt den Gimbal und hält das Bild ruhig.</t>
+        </is>
+      </c>
       <c r="M154" s="2" t="inlineStr"/>
-      <c r="N154" s="3" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr"/>
+      <c r="O154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
@@ -9478,9 +10996,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – kostenlos</t>
         </is>
       </c>
-      <c r="L155" s="4" t="inlineStr"/>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Person schaut ruhig und freundlich in die Kamera · Text: "Kostet das was?"
+3–7s — Bild: gleiche Einstellung · Sprich: "Nein. Der Gottesdienst ist kostenlos."
+7–10s — Bild: kurzer Cut auf eine Kollektenschale, weiches Licht · Text: "Es gibt nur eine Kollekte"
+10–15s — Bild: zurück zur Person · Sprich: "Du gibst, was du möchtest – oder nichts. Niemand schaut hin."
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, ruhig, sehr leise · 💡 Tipp: Beim Satz zur Kollekte locker mit den Schultern zucken – die entspannte Geste nimmt dem Thema den Ernst.</t>
+        </is>
+      </c>
       <c r="M155" s="4" t="inlineStr"/>
-      <c r="N155" s="5" t="inlineStr"/>
+      <c r="N155" s="4" t="inlineStr"/>
+      <c r="O155" s="5" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -9536,9 +11065,21 @@
           <t>Link in Bio → WhatsApp-Gruppe für deine Fragen</t>
         </is>
       </c>
-      <c r="L156" s="2" t="inlineStr"/>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Titelkarte in Aubergine, Lutherrose klein in der Ecke · Text groß: "5 Fragen, die sich jeder vor dem ersten Mal stellt" · darunter klein: "→ wisch dich durch"
+Slide 2: Oben groß: "Muss ich mitsingen?" · darunter warm: "Nein. Du darfst einfach zuhören – niemand schaut, ob deine Lippen sich bewegen."
+Slide 3: Oben groß: "Wann muss ich aufstehen?" · darunter: "Wir zeigen es dir. Schau einfach, was die anderen machen – oder bleib sitzen, das ist okay."
+Slide 4: Oben groß: "Kenne ich da überhaupt jemanden?" · darunter: "Beim ersten Mal meist nicht. Nach dem Kaffee danach schon ein, zwei Gesichter."
+Slide 5: Oben groß: "Muss ich beten?" · darunter: "Nein. Du darfst still dabei sein. Glaube ist kein Eintrittsticket."
+Slide 6: Oben groß: "Darf ich früher gehen?" · darunter: "Klar. Setz dich hinten hin, dann kannst du leise raus, wann du magst."
+Slide 7: Abschluss in Gemeindefarben · Text: "Noch eine Frage? Schreib uns – ganz unkompliziert." + "So 09:30 · Miodowa 21" + "Link in Bio → WhatsApp-Gruppe"
+💡 Tipp: Gleiche Schrift, gleiche Farben und gleiche Textposition auf allen Slides – dann wirkt das Wischen wie ein sauberer roter Faden.</t>
+        </is>
+      </c>
       <c r="M156" s="2" t="inlineStr"/>
-      <c r="N156" s="3" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr"/>
+      <c r="O156" s="3" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
@@ -9594,9 +11135,22 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L157" s="4" t="inlineStr"/>
+      <c r="L157" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~45s
+0–4s — Bild: Tür geht auf, jemand wird begrüßt · Sprich: "So läuft ein Gottesdienst bei uns – ganz ohne Insider-Wissen."
+4–11s — Bild: Liedblatt wird gereicht, Hände blättern · Text: "1. Ankommen &amp; Liedblatt"
+11–19s — Bild: Menschen singen, weites ruhiges Bild · Text: "2. Ein Lied"
+19–27s — Bild: Predigt-Moment, Kanzel, aufmerksame Gesichter · Text: "3. Die Predigt"
+27–34s — Bild: gefaltete Hände, stiller Moment · Text: "4. Gebet &amp; Segen"
+34–41s — Bild: Kaffeetassen, Gespräche, Lachen · Sprich: "Und danach: Kaffee und reden."
+41–45s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, leise, getragen – nichts Dramatisches · 💡 Tipp: Alle Stationen an einem Sonntag hintereinander abfilmen, dann hast du das ganze Reel in einem Rutsch im Kasten.</t>
+        </is>
+      </c>
       <c r="M157" s="4" t="inlineStr"/>
-      <c r="N157" s="5" t="inlineStr"/>
+      <c r="N157" s="4" t="inlineStr"/>
+      <c r="O157" s="5" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -9652,9 +11206,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – bleib auf einen Kaffee</t>
         </is>
       </c>
-      <c r="L158" s="2" t="inlineStr"/>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Der Kaffee-Moment nach dem Gottesdienst – zwei, drei Hände an dampfenden Tassen, im Hintergrund unscharf Menschen im Gespräch, ein echtes Lachen. · Bildaufbau/Licht: Natürliches Fensterlicht, halbnah, Fokus auf die Tassen und Hände, Hintergrund weich verschwommen; keine gestellte Pose, im Vorbeigehen einfangen. Hochformat für den Feed. · ggf. Text im Bild: "Nach dem Segen? Kaffee." oben klein, unten dezent "So 09:30 · Miodowa 21"
+💡 Tipp: Nah rangehen und auf die Hände scharfstellen, Gesichter dürfen unscharf bleiben – das wirkt warm und echt und braucht kein Einverständnis fürs Erkennbarsein.</t>
+        </is>
+      </c>
       <c r="M158" s="2" t="inlineStr"/>
-      <c r="N158" s="3" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr"/>
+      <c r="O158" s="3" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -9710,9 +11270,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – auch wenn's später wird</t>
         </is>
       </c>
-      <c r="L159" s="4" t="inlineStr"/>
+      <c r="L159" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Person schaut ruhig und warm in die Kamera · Text: "Was, wenn ich zu spät komme?"
+3–9s — Bild: gleiche Einstellung · Sprich: "Dann setzt du dich einfach hinten hin. Keiner dreht sich um, keiner urteilt."
+9–12s — Bild: kurzer Cut auf eine leise geöffnete Kirchentür, hintere Bank · Text: "Ehrlich."
+12–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, sehr dezent · 💡 Tipp: Das Wort "Ehrlich." mit einer kleinen Pause davor sprechen – die Ruhe macht es glaubwürdig.</t>
+        </is>
+      </c>
       <c r="M159" s="4" t="inlineStr"/>
-      <c r="N159" s="5" t="inlineStr"/>
+      <c r="N159" s="4" t="inlineStr"/>
+      <c r="O159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -9768,9 +11338,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – einfach nur da sein</t>
         </is>
       </c>
-      <c r="L160" s="2" t="inlineStr"/>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Person ruhig vor neutralem Hintergrund, Blick in die Kamera · Text: "Kann ich einfach nur zuhören?"
+3–10s — Bild: gleiche Einstellung, ruhig gesprochen · Sprich: "Du musst nicht mitsingen, nicht mitbeten, nicht mitreden. Du darfst einfach nur da sein."
+10–13s — Bild: kurzer Cut auf eine ruhig sitzende Person in der Bank, die zuhört · Text: "Nur da sein reicht."
+13–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, leise · 💡 Tipp: Beim Sprechen ein bewusst langsames Tempo halten – Ruhe in der Stimme unterstreicht genau die Botschaft.</t>
+        </is>
+      </c>
       <c r="M160" s="2" t="inlineStr"/>
-      <c r="N160" s="3" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr"/>
+      <c r="O160" s="3" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
@@ -9826,9 +11406,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L161" s="4" t="inlineStr"/>
+      <c r="L161" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: sanfter Schwenk über die leeren Bänke, Licht fällt weich ein · Text: "Bevor du kommst… ein Blick in den Raum"
+4–10s — Bild: langsame Einstellung auf Fenster und Lichteinfall · Sprich (leise, optional): "Das ist der Ort, an dem wir uns treffen."
+10–16s — Bild: ruhiger Schwenk zur Kanzel, dann über die Reihen · Text: "Bänke, Licht, Stille"
+16–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" + kleine Zeile "Damit dir der Ort schon vertraut ist"
+🎵 Musik: warm, getragen, leise – gern mit sanftem Nachhall · 💡 Tipp: Handy an eine Bank oder Säule anlehnen und nur ganz langsam schwenken; jede Einstellung mindestens 4 Sekunden halten, sonst wirkt es hektisch.</t>
+        </is>
+      </c>
       <c r="M161" s="4" t="inlineStr"/>
-      <c r="N161" s="5" t="inlineStr"/>
+      <c r="N161" s="4" t="inlineStr"/>
+      <c r="O161" s="5" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -9884,9 +11474,21 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L162" s="2" t="inlineStr"/>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~40s (Interview, frei erzählt – die Sätze sind Ankerpunkte, kein Ablesetext)
+0–4s — Bild: Person sitzt entspannt, schaut in die Kamera · Text: "Neu in Warschau – mein erster Gottesdienst hier"
+4–14s — Bild: Person erzählt frei · Anker-Satz: "Ehrlich, ich war ziemlich nervös – ich kannte hier niemanden."
+14–22s — Bild: B-Roll einblenden (Ankommen an der Tür), Stimme läuft weiter · Anker-Satz: "Aber gleich an der Tür hat mich jemand angelächelt."
+22–32s — Bild: B-Roll Kaffee-Moment · Anker-Satz: "Beim Kaffee danach kam ich ins Gespräch – plötzlich war ich nicht mehr allein."
+32–37s — Bild: zurück zur Person · Anker-Satz: "Deshalb bin ich wiedergekommen."
+37–40s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr leise, warm, darf fast verschwinden, damit die Stimme trägt · 💡 Tipp: Nicht auswendig lernen lassen – 3–4 Minuten frei erzählen lassen und danach die ehrlichsten 40 Sekunden herausschneiden.</t>
+        </is>
+      </c>
       <c r="M162" s="2" t="inlineStr"/>
-      <c r="N162" s="3" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr"/>
+      <c r="O162" s="3" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
@@ -9942,9 +11544,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – ohne Anmeldung</t>
         </is>
       </c>
-      <c r="L163" s="4" t="inlineStr"/>
+      <c r="L163" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~14s
+0–3s — Bild: Textkarte in Aubergine · Text: "Muss ich mich anmelden?"
+3–6s — Bild: Cut auf eine Person, die die Kirchentür öffnet · Sprich: "Nein."
+6–11s — Bild: Person hält die Tür auf, drei kurze Text-Stempel blitzen auf · Text: "keine Anmeldung" → "keine Liste" → "keine Registrierung"
+11–14s — Bild: Person winkt herein und lächelt · Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: locker, freundlich, kurz und knackig · 💡 Tipp: Die drei Text-Stempel je ~1 Sekunde einblenden und leicht "reinploppen" lassen – das gibt dem kurzen Reel Tempo.</t>
+        </is>
+      </c>
       <c r="M163" s="4" t="inlineStr"/>
-      <c r="N163" s="5" t="inlineStr"/>
+      <c r="N163" s="4" t="inlineStr"/>
+      <c r="O163" s="5" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -10000,9 +11612,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – auch allein</t>
         </is>
       </c>
-      <c r="L164" s="2" t="inlineStr"/>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Person schaut warm in die Kamera · Text: "Kommst du allein?"
+3–8s — Bild: gleiche Einstellung · Sprich: "Du bist nicht der Einzige. Viele hier kamen beim ersten Mal allein."
+8–14s — Bild: B-Roll – jemand kommt allein zur Tür, wird begrüßt, kommt ins Gespräch · Text: "Nach 10 Minuten kennst du ein Gesicht"
+14–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" + kleine Zeile "Trau dich – auch allein"
+🎵 Musik: warm, ermutigend, leise · 💡 Tipp: Für die B-Roll reicht eine Person, die von hinten zur Tür geht und begrüßt wird – Gesicht muss nicht erkennbar sein, das schützt und wirkt trotzdem echt.</t>
+        </is>
+      </c>
       <c r="M164" s="2" t="inlineStr"/>
-      <c r="N164" s="3" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="3" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
@@ -10058,9 +11680,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L165" s="4" t="inlineStr"/>
+      <c r="L165" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–5s — Bild: draußen – polnische Straßenschilder, Warschauer Stadtbild, ruhiger Handy-Schwenk · Text: "Draußen: Warschau"
+5–6s — Bild: harter Cut (kurze Schwarzblende möglich)
+6–13s — Bild: drinnen – Menschen singen ein deutsches Lied, Originalton läuft mit · Text: "Drinnen: Deutsch"
+13–16s — Bild: ruhiges Bild vom Raum · Text: "Dein Glaube in deiner Sprache"
+16–18s — Endcard: Lutherrose + "Auf Deutsch. Mitten in Warschau." + "So 09:30 · Miodowa 21"
+🎵 Musik: draußen dezenter Stadtklang/O-Ton, drinnen trägt der echte Gesang – dann keine Extra-Musik nötig · 💡 Tipp: Den harten Cut genau auf den ersten gesungenen Ton legen – der Sprung von Straßenlärm zu deutschem Lied ist der ganze Effekt.</t>
+        </is>
+      </c>
       <c r="M165" s="4" t="inlineStr"/>
-      <c r="N165" s="5" t="inlineStr"/>
+      <c r="N165" s="4" t="inlineStr"/>
+      <c r="O165" s="5" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -10116,9 +11749,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L166" s="2" t="inlineStr"/>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Der echte Eingang an der ul. Miodowa 21, frontal, die Tür klar im Zentrum. · Bildaufbau/Licht: Tageslicht, am besten leicht bewölkt oder Vormittag, damit keine harten Schatten die Tür verdecken; frontal und gerade fotografieren, etwas Umgebung mit drauf (Fassade, Straße), damit man sich orientieren kann; ein deutlicher Pfeil/Kreis auf die richtige Tür setzen. · ggf. Text im Bild: oben "Hier geht's rein", auf dem Pfeil "ul. Miodowa 21", unten "So 09:30"
+💡 Tipp: Ein zweites Foto aus der Fußgänger-Perspektive von der Straße aus mitliefern (als 2. Bild im Post) – so erkennt man den Weg, nicht nur die Tür.</t>
+        </is>
+      </c>
       <c r="M166" s="2" t="inlineStr"/>
-      <c r="N166" s="3" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr"/>
+      <c r="O166" s="3" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
@@ -10174,9 +11813,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – auch mit Zweifeln</t>
         </is>
       </c>
-      <c r="L167" s="4" t="inlineStr"/>
+      <c r="L167" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–4s — Bild: Person ruhig vor der Kamera, warmer, offener Ton · Text: "Ich glaube nicht so richtig – darf ich trotzdem?"
+4–10s — Bild: gleiche Einstellung · Sprich: "Zweifel gehören dazu. Du musst nicht überzeugt sein, um willkommen zu sein."
+10–13s — Bild: kurze Pause, ehrlicher Blick, leichtes Nicken · Text: "Kein Bekehrungsdruck. Versprochen."
+13–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine oder extrem leise – die Stille macht den Satz ehrlich · 💡 Tipp: Nach dem Kernsatz bewusst eine Sekunde stillhalten und nicht wegschneiden – dieser offene Blick ist glaubwürdiger als jede Musik.</t>
+        </is>
+      </c>
       <c r="M167" s="4" t="inlineStr"/>
-      <c r="N167" s="5" t="inlineStr"/>
+      <c r="N167" s="4" t="inlineStr"/>
+      <c r="O167" s="5" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -10232,9 +11881,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L168" s="2" t="inlineStr"/>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s (durchgehend aus der Ich-Perspektive gefilmt)
+0–3s — Bild: POV – von der Straße auf die Tür zu · Text: "Was passiert, wenn du reinkommst?"
+3–8s — Bild: POV – Tür öffnet sich, jemand schaut freundlich und begrüßt · Sprich (aus dem Off, warm): "Schön, dass du da bist." · Text: "Schritt 1: Tür auf, Begrüßung"
+8–14s — Bild: POV – langsam durch den Mittelgang, einen Platz in der Bank finden, hinsetzen · Text: "Schritt 2: Platz finden – such dir einen aus"
+14–19s — Bild: POV – eine Hand reicht ein Liedblatt in die Kamera · Text: "Schritt 3: Liedblatt in die Hand"
+19–22s — Endcard: Lutherrose + "Ganz einfach." + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, sanft · 💡 Tipp: Das Handy auf Augenhöhe halten und langsam laufen, damit es sich wirklich wie "aus deinen Augen" anfühlt – das ist der Kern des POV-Effekts.</t>
+        </is>
+      </c>
       <c r="M168" s="2" t="inlineStr"/>
-      <c r="N168" s="3" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr"/>
+      <c r="O168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
@@ -10290,9 +11950,19 @@
           <t>Kommt Sonntag 09:30, Miodowa 21 – mit Kind</t>
         </is>
       </c>
-      <c r="L169" s="4" t="inlineStr"/>
+      <c r="L169" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–4s — Bild: kurzer Clip von einer Familien-Ecke / spielenden Kindern im Raum, lockere Stimmung · Text: "Nimm dein Kind mit"
+4–10s — Bild: ein Elternteil lächelt entspannt in die Kamera · Sprich: "Kinder dürfen bei uns laut sein und wuseln – niemand verdreht die Augen."
+10–13s — Bild: Kind läuft fröhlich durchs Bild · Text: "Kein Grund, zu Hause zu bleiben"
+13–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" + kleine Zeile "Kommt als Familie"
+🎵 Musik: leicht, fröhlich, warm · 💡 Tipp: Kinder nur so filmen, dass sie nicht klar erkennbar sind (von hinten, unscharf, nur Hände/Füße) oder vorher das Okay der Eltern holen – dann seid ihr auf der sicheren Seite.</t>
+        </is>
+      </c>
       <c r="M169" s="4" t="inlineStr"/>
-      <c r="N169" s="5" t="inlineStr"/>
+      <c r="N169" s="4" t="inlineStr"/>
+      <c r="O169" s="5" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -10348,9 +12018,15 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L170" s="2" t="inlineStr"/>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Eine schlichte Info-Grafik in Aubergine mit den vier Kern-Infos gestapelt: "2× im Monat · Sonntags · 09:30 · ul. Miodowa 21". · Bildaufbau/Licht: Reine Grafik, kein Foto nötig – Aubergine-Hintergrund (#480048), Text in Weiß/Creme, Lutherrose klein und dezent in einer Ecke; großzügiger Rand, große Schrift, mittig ausgerichtet, quadratisch oder hochformat. · ggf. Text im Bild: "Zweimal im Monat" / "Sonntags 09:30" / "ul. Miodowa 21" / unten kleiner "Mehr musst du nicht wissen"
+💡 Tipp: Nur eine Schriftgröße für die Kern-Infos und eine kleinere für den Zusatz – so bleibt es auch als Vorschaubild im Feed sofort lesbar.</t>
+        </is>
+      </c>
       <c r="M170" s="2" t="inlineStr"/>
-      <c r="N170" s="3" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr"/>
+      <c r="O170" s="3" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
@@ -10406,9 +12082,17 @@
           <t>Tippe auf den Sticker und frag uns – anonym</t>
         </is>
       </c>
-      <c r="L171" s="4" t="inlineStr"/>
+      <c r="L171" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~10s (Story-Sequenz, 2 Frames)
+Frame 1 (0–6s) — Bild: ruhiger Aubergine-Hintergrund oder ein warmes Foto vom Raum, leicht abgedunkelt · On-Screen-Text oben: "Frag uns alles – ganz anonym" · darunter der Instagram-Fragen-Sticker mit dem Prompt: "Was wolltest du über einen Gottesdienst schon immer wissen?" · kleiner Pfeil/Hinweis: "👆 hier reintippen"
+Frame 2 (6–10s, optional als zweite Story) — Bild: nahe Aufnahme einer freundlichen Person, die kurz in die Kamera nickt · On-Screen-Text: "Keine Frage ist zu klein. Wir antworten ehrlich."
+🎵 Musik: dezenter Story-Sound oder ganz ohne · 💡 Tipp: Den Sticker mittig und groß platzieren (Daumen-Reichweite) und die Story ein paar Tage später mit den eingegangenen Fragen als Antwort-Serie wiederholen – das hält das Thema am Leben.</t>
+        </is>
+      </c>
       <c r="M171" s="4" t="inlineStr"/>
-      <c r="N171" s="5" t="inlineStr"/>
+      <c r="N171" s="4" t="inlineStr"/>
+      <c r="O171" s="5" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -10464,9 +12148,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – bring nur dich mit</t>
         </is>
       </c>
-      <c r="L172" s="2" t="inlineStr"/>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Titelkarte in Aubergine, Lutherrose dezent · Text groß: "3 Dinge, die du NICHT mitbringen musst" · klein: "→ wisch"
+Slide 2: Große Zahl "1" · darüber "Keine Bibel" · darunter warm: "Die liegt bei uns bereit – du musst nichts mitschleppen."
+Slide 3: Große Zahl "2" · darüber "Kein Vorwissen" · darunter: "Wir erklären, was passiert. Du musst nichts vorher gelernt haben."
+Slide 4: Große Zahl "3" · darüber "Keine besondere Kleidung" · darunter: "Komm, wie du bist. Jeans ist genauso richtig wie Sakko."
+Slide 5: Abschluss in Gemeindefarben · groß: "Nur dich – mehr braucht's nicht." · darunter "So 09:30 · Miodowa 21" + "Bring nur dich mit"
+💡 Tipp: Auf jeder Slide dieselbe Position für Zahl, Überschrift und Fließtext halten – beim Durchwischen entsteht so ein sauberer, ruhiger Rhythmus.</t>
+        </is>
+      </c>
       <c r="M172" s="2" t="inlineStr"/>
-      <c r="N172" s="3" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr"/>
+      <c r="O172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
@@ -10522,9 +12216,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L173" s="4" t="inlineStr"/>
+      <c r="L173" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: warme Clips vom Kaffee-Moment – Tassen, Gespräche, Lachen · Text: "Der Kaffee-Moment"
+4–8s — Bild: weiter B-Roll, jemand schenkt Kaffee ein · Text: "Hier lernst du Leute kennen"
+8–13s — Bild: eine Person schaut in die Kamera und lädt ein · Sprich: "Bleib einfach auf einen Kaffee, dann reden wir."
+13–16s — Bild: Gruppe im lockeren Gespräch · Text: "Anschluss? → WhatsApp-Gruppe, Link in Bio"
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, locker, mittleres Tempo · 💡 Tipp: Den Einladungssatz von einer echten, herzlichen Person sprechen lassen, die wirklich beim Kaffee dabei ist – Authentizität schlägt jede perfekte Formulierung.</t>
+        </is>
+      </c>
       <c r="M173" s="4" t="inlineStr"/>
-      <c r="N173" s="5" t="inlineStr"/>
+      <c r="N173" s="4" t="inlineStr"/>
+      <c r="O173" s="5" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -10580,9 +12285,21 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L174" s="2" t="inlineStr"/>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s (schneller O-Ton-Schnitt, alle im gleichen Setting)
+0–3s — Bild: Titelkarte, dann erste Person · Text: "Was mich überrascht hat, als ich das erste Mal kam"
+3–7s — Bild: Person 1 in die Kamera · Sprich: "Dass es so locker war."
+7–11s — Bild: Person 2, gleicher Look · Sprich: "Dass mich einfach jemand angesprochen hat."
+11–15s — Bild: Person 3 · Sprich: "Dass niemand komisch geschaut hat."
+15–17s — Bild: Person 4 lacht kurz · Sprich: "Dass ich wiederkommen wollte."
+17–20s — Endcard: Lutherrose + "Komm und überrasch dich selbst" + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, lockerer Rhythmus, der die schnellen Cuts trägt · 💡 Tipp: Alle Personen am selben Ort, gleicher Bildausschnitt, gleiche Höhe filmen – dann wirken die schnellen Schnitte wie aus einem Guss statt zusammengestückelt.</t>
+        </is>
+      </c>
       <c r="M174" s="2" t="inlineStr"/>
-      <c r="N174" s="3" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr"/>
+      <c r="O174" s="3" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
@@ -10638,9 +12355,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – oder Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L175" s="4" t="inlineStr"/>
+      <c r="L175" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Person schaut ruhig und warm direkt in die Kamera, naher Ausschnitt · Text: "Deine erste Einladung"
+3–8s — Bild: gleiche Einstellung, direkter Blick · Sprich: "Wenn du das siehst, bist du gemeint. Komm diesen Sonntag vorbei."
+8–12s — Bild: kurze Pause, echtes Lächeln · Sprich: "Ich freu mich auf dich."
+12–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" + kleine Zeile "Fragen? Link in Bio → WhatsApp"
+🎵 Musik: warm, herzlich, sehr leise, damit die direkte Ansprache trägt · 💡 Tipp: Die Person soll direkt ins Objektiv sprechen, nicht auf den Bildschirm schauen – der echte Blickkontakt macht das "du bist gemeint" spürbar.</t>
+        </is>
+      </c>
       <c r="M175" s="4" t="inlineStr"/>
-      <c r="N175" s="5" t="inlineStr"/>
+      <c r="N175" s="4" t="inlineStr"/>
+      <c r="O175" s="5" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -10696,9 +12423,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L176" s="2" t="inlineStr"/>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: Handy gleitet langsam an den leeren Bänken entlang · Text: "Wo darf ich sitzen?"
+3–7s — Bild: Schwenk nach vorne zu den ersten Reihen · Sprich (aus dem Off): "Überall."
+7–12s — Bild: Kamera zeigt hintere Reihen und Randplätze · Text: "Keine reservierten Plätze"
+12–14s — Bild: langsame Fahrt endet an einer einladenden Bank · Text: "Such dir deinen Platz"
+14–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, sanft · 💡 Tipp: Für die gleitende Fahrt das Handy dicht über die Banklehnen führen und ganz langsam gehen – diese ruhige Bewegung wirkt einladend statt leer.</t>
+        </is>
+      </c>
       <c r="M176" s="2" t="inlineStr"/>
-      <c r="N176" s="3" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr"/>
+      <c r="O176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
@@ -10754,9 +12492,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L177" s="4" t="inlineStr"/>
+      <c r="L177" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Nahaufnahme einer Hand mit Streichholz, das die erste Kerze am Adventskranz anzündet · Text: "Advent heißt nicht Stress."
+3–9s — Bild: Die Flamme scharf im Fokus, der Rest weich · Sprich: "Advent kommt von adventus — das heißt: Ankunft."
+9–15s — Bild: Langsamer Schwenk nach oben, weg von der Kerze · Sprich: "Keine vier Wochen Hektik. Vier Wochen Warten — auf jemanden, der kommt."
+15–18s — Bild: Ruhiger Blick auf den ganzen Kranz, eine Kerze brennt · Sprich: "Bei uns brennt schon die erste Kerze."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, eine leise Klavier- oder Streicherfläche · 💡 Tipp: Film die Kerze im abgedunkelten Raum, dann leuchtet die Flamme kräftiger — Handy quer halten oder direkt im 9:16-Hochformat filmen und aufs Feuer scharfstellen.</t>
+        </is>
+      </c>
       <c r="M177" s="4" t="inlineStr"/>
-      <c r="N177" s="5" t="inlineStr"/>
+      <c r="N177" s="4" t="inlineStr"/>
+      <c r="O177" s="5" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -10812,9 +12561,15 @@
           <t>Folg uns für die ganze Serie durch den Advent</t>
         </is>
       </c>
-      <c r="L178" s="2" t="inlineStr"/>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Der Adventskranz frontal, eine brennende Kerze (in Woche 1) — schlicht, kein weiterer Deko-Schnickschnack im Bild. · Bildaufbau/Licht: Kranz an einer festen Stelle platzieren, Kamera auf gleicher Höhe und gleichem Abstand (markier dir die Stelle für alle vier Wochen). Warmes, weiches Seitenlicht, Raum leicht abdunkeln, damit die Flamme trägt. Kerze links oder mittig, rechts etwas Luft für die Textzeile. · ggf. Text im Bild: "1. Advent — eine Kerze mehr, ein Sonntag näher."
+💡 Tipp: Fotografier alle vier Wochen exakt gleich (gleicher Ausschnitt, gleiche Uhrzeit/gleiches Licht) — nur die Zahl brennender Kerzen ändert sich. So wird die Serie wiedererkennbar. Merk dir die Handy-Position mit einem Klebeband am Boden.</t>
+        </is>
+      </c>
       <c r="M178" s="2" t="inlineStr"/>
-      <c r="N178" s="3" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr"/>
+      <c r="O178" s="3" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
@@ -10870,9 +12625,20 @@
           <t>Weihnachtsgottesdienst-Zeit auf warschau-evangelisch.de</t>
         </is>
       </c>
-      <c r="L179" s="4" t="inlineStr"/>
+      <c r="L179" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~25s
+0–4s — Bild: Langsamer Schwenk über den abendlich dunklen Kirchenraum bei Kerzenschein · Text: "Warum feiern wir schon am 24.?"
+4–11s — Bild: Detail einer brennenden Kerze, dann die Krippe im Halbdunkel · Sprich: "Vier Wochen lang haben wir gewartet. Am Heiligen Abend endet das Warten."
+11–18s — Bild: Weiterer ruhiger Schwenk über Kerzen und Bänke · Sprich: "Deshalb ist dieser Abend für uns der Höhepunkt — er ist da. Ganz nah, bei Kerzenschein."
+18–22s — Bild: Warmes Gesamtbild des Raums · Sprich: "Feier Weihnachten mit uns."
+22–25s — Endcard: Lutherrose + "Heiligabend · Miodowa 21 · Zeit auf warschau-evangelisch.de"
+🎵 Musik: ruhig, festlich-warm, sehr dezent (leises Cello oder Choralfläche) · 💡 Tipp: Film am besten während einer echten Probe oder abends bei bereits brennenden Kerzen. Belichtung am Handy manuell etwas runterziehen (auf Kerze tippen und halten), damit die Flammen nicht ausbrennen und die Stimmung dunkel-warm bleibt.</t>
+        </is>
+      </c>
       <c r="M179" s="4" t="inlineStr"/>
-      <c r="N179" s="5" t="inlineStr"/>
+      <c r="N179" s="4" t="inlineStr"/>
+      <c r="O179" s="5" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -10928,9 +12694,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L180" s="2" t="inlineStr"/>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Ein Kind im Engelskostüm, das seinen Text sucht und in die Kamera lacht · Text: "Krippenspiel-Probe 🕊️"
+3–8s — Bild: Verrutschter Heiligenschein, jemand richtet ihn liebevoll · Text: "Der Text sitzt noch nicht ganz …"
+8–13s — Bild: Kleines Durcheinander, Erwachsene lachen mit den Kindern · Text: "… aber die Freude schon."
+13–16s — Bild: Fröhlicher, schneller Schnitt durch mehrere Probe-Momente · Text: "Hier ist Leben."
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: fröhlich, leicht, verspielt (dezent, damit die echten Lacher hörbar bleiben) · 💡 Tipp: Nichts stellen — einfach mitlaufen lassen und die echten Momente einfangen. Vorher kurz bei den Eltern das Okay fürs Filmen der Kinder holen; im Zweifel Gesichter nur kurz oder von hinten zeigen.</t>
+        </is>
+      </c>
       <c r="M180" s="2" t="inlineStr"/>
-      <c r="N180" s="3" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr"/>
+      <c r="O180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n">
@@ -10986,9 +12763,20 @@
           <t>Komm zum Weihnachtsgottesdienst, Miodowa 21</t>
         </is>
       </c>
-      <c r="L181" s="4" t="inlineStr"/>
+      <c r="L181" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Der leere Stall, nur Stroh und Holz. Text: "Erst ist der Stall noch leer."
+Slide 2: Maria steht jetzt da. Text: "Maria macht sich auf den Weg."
+Slide 3: Josef kommt dazu. Text: "Josef an ihrer Seite."
+Slide 4: Ochs und Esel dazugestellt. Text: "Die Tiere machen Platz."
+Slide 5: Das Kind liegt in der Krippe. Text: "Und dann — das Kind."
+Slide 6: Die volle Krippe, warm ausgeleuchtet. Text: "Feier die Geschichte mit uns — Weihnachtsgottesdienst, Miodowa 21."
+💡 Tipp: Alle sechs Bilder aus exakt derselben Kameraposition und mit gleichem Licht aufnehmen (Handy auf ein Stativ oder eine Bücherstapel-Halterung), nur die Figuren wandern ins Bild. Beim Durchwischen entsteht so ein sanfter Stop-Motion-Effekt.</t>
+        </is>
+      </c>
       <c r="M181" s="4" t="inlineStr"/>
-      <c r="N181" s="5" t="inlineStr"/>
+      <c r="N181" s="4" t="inlineStr"/>
+      <c r="O181" s="5" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -11044,9 +12832,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L182" s="2" t="inlineStr"/>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Blick aus dem Fenster auf das nächtliche Warschau, ferne Silvesterlichter · Text: "Ein Segen fürs neue Jahr"
+4–10s — Bild: Ruhige, fast stille Kamera auf die Lichter · Sprich: "Während draußen die Raketen steigen, lesen wir leise die Jahreslosung."
+10–16s — Bild: Der Vers wird sanft als Text eingeblendet · Sprich: "Ein Vers, der uns durch alle zwölf Monate begleitet — und der bleibt."
+16–18s — Bild: Ruhiger Blick, Lichter am Horizont · Sprich: "Nimm ihn mit ins neue Jahr."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr ruhig, warm, fast still (leises Piano) · 💡 Tipp: Vom dunklen Zimmer aus nach draußen filmen, damit der Kontrast zwischen warmem Innen und kaltem Stadtlicht wirkt. Die konkrete Jahreslosung vorher heraussuchen und wörtlich einblenden — nichts Erfundenes.</t>
+        </is>
+      </c>
       <c r="M182" s="2" t="inlineStr"/>
-      <c r="N182" s="3" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr"/>
+      <c r="O182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n">
@@ -11102,9 +12901,15 @@
           <t>Schreib in die Kommentare: Was nimmst du mit ins neue Jahr?</t>
         </is>
       </c>
-      <c r="L183" s="4" t="inlineStr"/>
+      <c r="L183" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Zwei Kalenderblätter nebeneinander — links Dezember (leicht abgegriffen, ein paar Notizen), rechts ein blanker Januar. · Bildaufbau/Licht: Flatlay von oben, beide Blätter auf einem schlichten Holztisch oder hellen Untergrund, gleichmäßig weiches Tageslicht ohne harte Schatten. In der Mitte eine klare senkrechte Trennlinie (Kante an Kante legen). Etwas freie Fläche oben lassen für die Textzeile. · ggf. Text im Bild: "Was bleibt — was kommt?"
+💡 Tipp: Fotografier bei Tageslicht am Fenster und leg beide Blätter exakt parallel, damit die Symmetrik ruhig wirkt. Die Community-Frage bewusst offen halten — sie ist der Grund, warum Leute kommentieren.</t>
+        </is>
+      </c>
       <c r="M183" s="4" t="inlineStr"/>
-      <c r="N183" s="5" t="inlineStr"/>
+      <c r="N183" s="4" t="inlineStr"/>
+      <c r="O183" s="5" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -11160,9 +12965,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L184" s="2" t="inlineStr"/>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Nahaufnahme, ein Daumen zeichnet ein kleines Aschekreuz auf eine Stirn oder Handrücken · Text: "Warum fangen wir mit Asche an?"
+3–9s — Bild: Detail der Asche auf der Haut · Sprich: "Ein kleines Aschekreuz — und die Passionszeit beginnt. Sieben Wochen bis Ostern."
+9–15s — Bild: Weicher Übergang, ruhiger Blick · Sprich: "Das ist kein Trübsal. Es ist eine Einladung zum Innehalten — Raum schaffen für das Wesentliche."
+15–16s — Bild: Ruhiges Schlussbild · Sprich: "Geh die Wochen mit uns."
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, gedämpft, nachdenklich · 💡 Tipp: Für die Asche etwas kalte Holzasche oder verriebene Kohle nehmen und im Makro-Modus ganz nah rangehen — die Struktur auf der Haut macht das Bild. Neutraler Hintergrund, damit der Fokus auf dem Kreuz bleibt.</t>
+        </is>
+      </c>
       <c r="M184" s="2" t="inlineStr"/>
-      <c r="N184" s="3" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr"/>
+      <c r="O184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n">
@@ -11218,9 +13034,19 @@
           <t>Stimm in der Story ab und mach mit</t>
         </is>
       </c>
-      <c r="L185" s="4" t="inlineStr"/>
+      <c r="L185" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~10s pro Story-Slide (wöchentlich, 7 Wochen)
+0–2s — Bild: Schlichte violette Farbfläche (liturgische Farbe der Passionszeit), oben klein die Wochenzahl · Text: "7 Wochen ohne · Woche 1"
+2–7s — Bild: Gleiche Fläche, in der Mitte die Frage der Woche · Text: "Worauf könntest du diese Woche verzichten?" · Sprich (optional, warm): "Kein erhobener Zeigefinger — nur eine kleine Frage an dich."
+7–9s — Bild: Umfrage- oder Fragen-Sticker gut sichtbar platziert · Text: "Stimm ab 👇"
+9–10s — Endcard: Lutherrose + "Nächste Woche geht's weiter · Miodowa 21"
+🎵 Musik: ruhig, dezent, optional stumm mit Umfrage-Sticker im Fokus · 💡 Tipp: Für jede der sieben Wochen dasselbe Layout und dieselbe Farbe verwenden — nur Wochenzahl und Frage tauschen. So wird die Serie wiedererkennbar. Die Community-Antworten in einer Folge-Story reposten, das hält die Interaktion am Laufen.</t>
+        </is>
+      </c>
       <c r="M185" s="4" t="inlineStr"/>
-      <c r="N185" s="5" t="inlineStr"/>
+      <c r="N185" s="4" t="inlineStr"/>
+      <c r="O185" s="5" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -11276,9 +13102,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L186" s="2" t="inlineStr"/>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–4s — Bild: Jemand geht durch eine grüne Warschauer Allee, Kamera folgt ruhig von hinten · Text: "Palmsonntag — der Weg beginnt."
+4–11s — Bild: Blätter und Licht über dem Weg, Schritte im Takt · Sprich: "An Palmsonntag zog Jesus in Jerusalem ein. Die Menschen legten ihm Palmzweige auf den Weg."
+11–18s — Bild: Weiter dem Weg folgen, Sonne blitzt durch die Bäume · Sprich: "Wir übersetzen das in einen Spaziergang — mitten in Warschau. Von hier beginnt der Weg der Karwoche."
+18–20s — Bild: Der Weg führt weiter, Person geht ins Licht · Sprich: "Auf nach Ostern. Geh ihn mit uns."
+20–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, hoffnungsvoll, in Bewegung · 💡 Tipp: Beim Mitlaufen das Handy mit beiden Händen dicht am Körper halten und langsam gehen — das gibt einen ruhigen, fast schwebenden Look ohne Gimbal. Am späten Nachmittag filmen, wenn das Licht golden durch die Blätter fällt.</t>
+        </is>
+      </c>
       <c r="M186" s="2" t="inlineStr"/>
-      <c r="N186" s="3" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
@@ -11334,9 +13171,20 @@
           <t>Komm zu unseren Gottesdiensten in der Karwoche, Miodowa 21</t>
         </is>
       </c>
-      <c r="L187" s="4" t="inlineStr"/>
+      <c r="L187" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Titelbild, dunkler Hintergrund. Text: "Die Karwoche in einem Faden — Karfreitag kennt fast jeder. Aber was liegt dazwischen?"
+Slide 2: Ein Tisch mit Brot und Kelch, warm beleuchtet. Text: "Gründonnerstag — das letzte Mahl mit den Freunden."
+Slide 3: Ein schlichtes Kreuz oder ein dunkler Raum. Text: "Karfreitag — der stille Tag. Er stirbt."
+Slide 4: Eine geschlossene Tür, gedämpftes Licht. Text: "Karsamstag — Stille. Das Warten dazwischen."
+Slide 5: Ein heller, offener Raum, Licht fällt herein. Text: "Ostersonntag — das Licht. Er lebt."
+Slide 6: Einladung. Text: "Geh die Woche mit uns — Gottesdienste in der Karwoche, Miodowa 21."
+💡 Tipp: Lass die Bilder eine Lichtreise erzählen — von warm (Gründonnerstag) über dunkel (Karfreitag/Karsamstag) zu hell (Ostern). Diese Helligkeits-Dramaturgie trägt die Geschichte auch ohne viele Worte.</t>
+        </is>
+      </c>
       <c r="M187" s="4" t="inlineStr"/>
-      <c r="N187" s="5" t="inlineStr"/>
+      <c r="N187" s="4" t="inlineStr"/>
+      <c r="O187" s="5" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -11392,9 +13240,19 @@
           <t>Halt heute kurz inne</t>
         </is>
       </c>
-      <c r="L188" s="2" t="inlineStr"/>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–4s — Bild: Eine einzelne Kerze im dunklen Raum, ruhig brennend · Text: "Karfreitag."
+4–9s — Bild: Die Kerze wird langsam ausgeblasen · Text: "Der Tag, an dem selbst die Glocken schweigen."
+9–13s — Bild: Rauch steigt langsam auf, dann dunkel · Text: "Ein Moment der Stille."
+13–15s — Bild: Dunkles, stilles Bild, kein Text, nur ein feiner Lichtschimmer · Text: "—"
+🎵 Musik: keine oder nur ein einzelner, sehr leiser Nachhall-Ton; bewusst viel Stille · 💡 Tipp: Dieses Reel bewusst OHNE CTA und ohne Endcard lassen — die Stille ist die Botschaft. Im ganz dunklen Raum filmen, nur die Kerze als Lichtquelle, und den Rauch nach dem Auspusten noch 2–3 Sekunden laufen lassen.</t>
+        </is>
+      </c>
       <c r="M188" s="2" t="inlineStr"/>
-      <c r="N188" s="3" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr"/>
+      <c r="O188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n">
@@ -11450,9 +13308,20 @@
           <t>Komm zum Ostergottesdienst, Miodowa 21</t>
         </is>
       </c>
-      <c r="L189" s="4" t="inlineStr"/>
+      <c r="L189" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Noch dunkle Warschauer Dächer, erster Himmelsschimmer (Zeitraffer beginnt) · Text: "Ostermorgen."
+4–10s — Bild: Der Zeitraffer läuft, der Himmel färbt sich, erster Lichtstrahl über der Skyline · Text: "Von Dunkel zu Licht."
+10–15s — Bild: Die Sonne bricht durch, Licht flutet die Stadt · Sprich: "Der Herr ist auferstanden."
+15–17s — Bild: Volles Morgenlicht über Warschau · Sprich: "Er ist wahrhaftig auferstanden."
+17–18s — Endcard: Lutherrose + "Ostergottesdienst · Miodowa 21"
+🎵 Musik: ruhig, aufsteigend, hell werdend (crescendo passend zum Lichtwechsel) · 💡 Tipp: Den Zeitraffer am Handy schon vor Sonnenaufgang starten (Kamera-App → Zeitraffer/Timelapse), Handy fest auf die Fensterbank oder ein Mini-Stativ. Kurz vor Ostern die genaue Sonnenaufgangszeit für Warschau checken und pünktlich am Ostermorgen posten.</t>
+        </is>
+      </c>
       <c r="M189" s="4" t="inlineStr"/>
-      <c r="N189" s="5" t="inlineStr"/>
+      <c r="N189" s="4" t="inlineStr"/>
+      <c r="O189" s="5" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -11508,9 +13377,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L190" s="2" t="inlineStr"/>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Leerer Gottesdienstraum, Stühle noch frei, ruhiges Morgenlicht (Timelapse-Start) · Text: "Erst ist der Raum noch leer."
+4–12s — Bild: Zeitraffer — Blumen werden gestellt, Kerzen angezündet, erste Menschen kommen herein · Text: "Dann kommen Blumen, Licht … und Menschen."
+12–17s — Bild: Der Raum füllt sich, festliche Stimmung · Sprich: "Ostern ist kein leerer Feiertag. Ostern ist Gemeinschaft, die zusammenkommt."
+17–18s — Bild: Voller, festlicher Raum · Sprich: "Komm dazu."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig beginnend, dann wärmer und voller werdend (baut sich auf wie der Raum) · 💡 Tipp: Handy vor dem Aufbau fest positionieren (Stativ oder festgeklemmt) und den Timelapse-Modus über die ganze Vorbereitungszeit durchlaufen lassen — nicht zwischendurch bewegen. Vorher die Ankommenden kurz informieren, dass gefilmt wird.</t>
+        </is>
+      </c>
       <c r="M190" s="2" t="inlineStr"/>
-      <c r="N190" s="3" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr"/>
+      <c r="O190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
@@ -11566,9 +13446,21 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L191" s="4" t="inlineStr"/>
+      <c r="L191" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–3s — Bild: Frage groß im Bild, dazu ein Schoko-Osterhase auf dem Tisch · Text: "Was hat der Osterhase mit Ostern zu tun?"
+3–8s — Bild: Jemand schaut in die Kamera und zuckt schmunzelnd mit den Schultern · Sprich: "Ganz ehrlich? Nicht so viel."
+8–14s — Bild: Kurzer Cut auf bunte Eier und den Hasen · Sprich: "Eier und Hasen sind schön, gehören dazu — aber sie sind nicht der Kern."
+14–19s — Bild: Sanfter Schnitt von den Eiern zu einer brennenden Kerze oder einem Kreuz · Sprich: "Worum es wirklich geht: dass das Leben stärker ist als der Tod."
+19–20s — Bild: Warmes, ruhiges Schlussbild · Sprich: "Willst du mehr wissen? Komm vorbei."
+20–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: leicht, freundlich, augenzwinkernd — beim Wechsel zur Kerze etwas wärmer werden lassen · 💡 Tipp: Den Ton locker und selbstironisch halten, nicht belehrend. Der Cut vom Hasen zur Kerze ist der Wendepunkt — plan da eine kleine Pause im Sprechen ein, damit das Bild wirken kann.</t>
+        </is>
+      </c>
       <c r="M191" s="4" t="inlineStr"/>
-      <c r="N191" s="5" t="inlineStr"/>
+      <c r="N191" s="4" t="inlineStr"/>
+      <c r="O191" s="5" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -11624,9 +13516,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L192" s="2" t="inlineStr"/>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Wind bewegt einen Vorhang oder Blätter am Fenster, Licht flackert durch · Text: "50 Tage nach Ostern."
+4–10s — Bild: Spiel von Licht und Bewegung, vielleicht eine flackernde Kerzenflamme · Sprich: "Pfingsten — das Fest, das kaum einer kennt. Dabei ist es der Geburtstag der Kirche."
+10–16s — Bild: Wind und Flamme im Wechsel · Sprich: "Wind und Feuer sind das Bild für den Heiligen Geist — für das, was Menschen bewegt."
+16–18s — Bild: Ruhiger Blick, Vorhang weht aus · Sprich: "Feier mit uns, was da begann."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: leicht, luftig, in Bewegung · 💡 Tipp: Für den Wind-Effekt ein Fenster öffnen und einen leichten Vorhang filmen — oder mit einem Ventilator nachhelfen. Im Zeitlupen-Modus des Handys wirkt die Stoffbewegung noch ruhiger und poetischer.</t>
+        </is>
+      </c>
       <c r="M192" s="2" t="inlineStr"/>
-      <c r="N192" s="3" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr"/>
+      <c r="O192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n">
@@ -11682,9 +13585,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L193" s="4" t="inlineStr"/>
+      <c r="L193" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Titel auf ruhiger Fläche · Text: "An Pfingsten verstanden sich plötzlich alle."
+3–13s — Bild: Schnelle, warme Schnittfolge einzelner Gemeindeglieder, je frontal ins Handy — jede Person sagt ein Wort: · Sprich (Person 1, deutsch): "Frieden." · Sprich (Person 2, polnisch): "Pokój." · Sprich (Person 3, englisch): "Peace." · Sprich (Person 4, weitere Sprache): "…"
+13–17s — Bild: Alle Gesichter kurz als Montage, dann alle Wörter als Text übereinander · Text: "So viele Sprachen — eine Gemeinde."
+17–18s — Bild: Warmes Gruppenbild oder letztes Gesicht, das lächelt · Sprich: "Egal welche du sprichst — du gehörst dazu."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, verbindend, leicht rhythmisch (trägt die schnellen Cuts) · 💡 Tipp: Alle Personen im gleichen Bildausschnitt und Abstand filmen (frontal, Kopf mittig), dann wirkt die Schnittfolge wie aus einem Guss. Jede Person nur das eine Wort sagen lassen — mehrere Takes machen, dann den lebendigsten nehmen.</t>
+        </is>
+      </c>
       <c r="M193" s="4" t="inlineStr"/>
-      <c r="N193" s="5" t="inlineStr"/>
+      <c r="N193" s="4" t="inlineStr"/>
+      <c r="O193" s="5" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -11740,9 +13654,15 @@
           <t>Schreib in die Kommentare: Wofür bist du dankbar?</t>
         </is>
       </c>
-      <c r="L194" s="2" t="inlineStr"/>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Der geschmückte Erntedank-Altar — Brot, Äpfel, Trauben, Getreideähren, ein Kürbis, alles dicht und üppig arrangiert. · Bildaufbau/Licht: Leicht schräg von oben oder auf Augenhöhe der Gaben fotografieren, sodass Tiefe entsteht. Warmes, natürliches Seitenlicht vom Fenster (goldene Nachmittagsstunde), keine harten Blitze. Das Brot als Blickfang nach vorne, Ähren als Rahmen an den Rändern. · ggf. Text im Bild: "Danke für das, was wächst."
+💡 Tipp: Geh für ein zweites Detailbild ganz nah an eine Ähre oder das Brot ran (Makro) — die Textur macht Dankbarkeit fühlbar. Poste das üppige Gesamtbild als Hauptbild, das Detail als zweites.</t>
+        </is>
+      </c>
       <c r="M194" s="2" t="inlineStr"/>
-      <c r="N194" s="3" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr"/>
+      <c r="O194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
@@ -11798,9 +13718,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L195" s="4" t="inlineStr"/>
+      <c r="L195" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Jemand geht mit einer Stofftüte über den Warschauer Wochenmarkt · Text: "Kein Feld, kein Garten?"
+4–10s — Bild: Details — frisches Gemüse, ein Brotstand, Hände, die einen Apfel aussuchen · Sprich: "Erntedank geht auch in der Stadt. Ohne Acker, ohne Ernte."
+10–16s — Bild: Kurzer Cut nach Hause — das gekaufte Brot liegt auf dem Küchentisch · Sprich: "Danke für den Markt um die Ecke. Für das Brot. Für die Menschen um uns."
+16–18s — Bild: Ruhiger Blick auf den gedeckten Tisch · Sprich: "Erntedank für Stadtmenschen. Feier mit uns."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, alltäglich, leicht (nichts Pathetisches) · 💡 Tipp: Auf dem Markt beiläufig aus der Hüfte filmen, damit es echt und ungestellt wirkt — kurze Clips von 2–3 Sekunden reichen. Für die konkrete Marktnennung einen realen Warschauer Wochenmarkt wählen, den ihr wirklich besucht.</t>
+        </is>
+      </c>
       <c r="M195" s="4" t="inlineStr"/>
-      <c r="N195" s="5" t="inlineStr"/>
+      <c r="N195" s="4" t="inlineStr"/>
+      <c r="O195" s="5" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -11856,9 +13787,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L196" s="2" t="inlineStr"/>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–4s — Bild: Jemand steht vor einer alten Holztür, hebt die Hand · Text: "31. Oktober — Reformationstag."
+4–10s — Bild: Nahaufnahme der Hand, die an die Tür klopft · Sprich: "Vor über 500 Jahren schlug Martin Luther seine Thesen an eine Kirchentür."
+10–17s — Bild: Ruhiger Blick auf Tür und Hand, dann in die Kamera · Sprich: "Er stellte Fragen, die viel ins Rollen brachten. Sein Satz: Hier stehe ich."
+17–20s — Bild: Person schaut selbstbewusst, aber freundlich in die Kamera · Sprich: "Das prägt uns bis heute. Neugierig, was evangelisch heute heißt?"
+20–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, würdevoll, mit leichtem Selbstbewusstsein · 💡 Tipp: Eine schöne alte Holztür in Warschau als Kulisse suchen — das echte Material trägt die Geschichte. Beim Klopfen den Ton mit aufnehmen; das kurze Klopfgeräusch ist ein starker Hook in den ersten Sekunden.</t>
+        </is>
+      </c>
       <c r="M196" s="2" t="inlineStr"/>
-      <c r="N196" s="3" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr"/>
+      <c r="O196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n">
@@ -11914,9 +13856,20 @@
           <t>Link in Bio → mehr über uns</t>
         </is>
       </c>
-      <c r="L197" s="4" t="inlineStr"/>
+      <c r="L197" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Die ganze Lutherrose, zentriert auf ruhigem Grund. Text: "Die Lutherrose entschlüsselt — jedes Element hat eine Bedeutung."
+Slide 2: Ausschnitt auf das schwarze Kreuz im Zentrum. Text: "Das Kreuz — der Glaube mitten im Herzen."
+Slide 3: Ausschnitt auf das rote Herz. Text: "Das Herz — der Glaube schenkt Freude und Leben."
+Slide 4: Ausschnitt auf die weiße Blüte. Text: "Die weiße Rose — Freude, Trost und Frieden."
+Slide 5: Ausschnitt auf den goldenen Ring. Text: "Der goldene Ring — ohne Anfang, ohne Ende. Ewigkeit."
+Slide 6: Wieder die ganze Rose, warm. Text: "Das ist unser Symbol. Mehr über uns — Link in Bio."
+💡 Tipp: Nimm die offizielle Lutherrose als Grafik und zoome für jede Slide sauber auf das jeweilige Element (gleicher Bildstil durchziehen). Wenn ihr eine Lutherrose in der Kirche habt — Glasfenster, Wandbild —, fotografier die echte, das ist persönlicher als eine reine Grafik.</t>
+        </is>
+      </c>
       <c r="M197" s="4" t="inlineStr"/>
-      <c r="N197" s="5" t="inlineStr"/>
+      <c r="N197" s="4" t="inlineStr"/>
+      <c r="O197" s="5" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -11972,9 +13925,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L198" s="2" t="inlineStr"/>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Hände falten sich langsam, gedämpftes Novemberlicht · Text: "Buß- und Bettag."
+4–10s — Bild: Nahaufnahme der ruhenden Hände, oder eine Uhr, deren Zeiger stillzustehen scheint · Sprich: "Ein leiser Feiertag im November. Ein Tag zum Innehalten."
+10–15s — Bild: Ruhiger Blick, weiches Fensterlicht · Sprich: "Er meint nicht Schuld — sondern ehrliches Nachdenken über das eigene Leben."
+15–16s — Bild: Hände lösen sich, ruhiger Atemzug · Sprich: "Gönn dir die Pause."
+16–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr ruhig, warm, minimal · 💡 Tipp: Am Fenster bei trübem Novemberlicht filmen — genau dieses graue, weiche Licht passt zur Stimmung, kein künstliches Aufhellen. Die Hände langsam bewegen; alles darf hier bewusst entschleunigt sein.</t>
+        </is>
+      </c>
       <c r="M198" s="2" t="inlineStr"/>
-      <c r="N198" s="3" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr"/>
+      <c r="O198" s="3" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n">
@@ -12030,9 +13994,20 @@
           <t>Komm zum Ewigkeitssonntag-Gottesdienst, Miodowa 21</t>
         </is>
       </c>
-      <c r="L199" s="4" t="inlineStr"/>
+      <c r="L199" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–4s — Bild: Dunkler Raum, eine erste Kerze wird behutsam angezündet · Text: "Ewigkeitssonntag."
+4–11s — Bild: Nacheinander werden weitere Kerzen entzündet, das Licht wächst · Sprich (leise): "Für jeden, an den wir denken, zünden wir ein Licht an."
+11–17s — Bild: Immer mehr Kerzen, ein Meer aus kleinen Lichtern (keine Namen im Bild) · Sprich: "Sie fehlen — und sie bleiben. Kein Name geht verloren."
+17–20s — Bild: Ruhige, weite Aufnahme über die vielen Lichter · Sprich: "Wenn du jemanden vermisst, fern der Heimat — du bist mit deiner Trauer nicht allein."
+20–22s — Endcard: Lutherrose + "Ewigkeitssonntag · Miodowa 21"
+🎵 Musik: sehr ruhig, tröstend, getragen (leises Streicher- oder Orgelpad) · 💡 Tipp: Ganz im Dunkeln filmen, nur die Kerzen als Licht — die wachsende Helligkeit erzählt die Geschichte von allein. Keine echten Namen zeigen; wenn Namen vorgelesen werden, nur als Ton, nie im Bild. Würde vor Reichweite.</t>
+        </is>
+      </c>
       <c r="M199" s="4" t="inlineStr"/>
-      <c r="N199" s="5" t="inlineStr"/>
+      <c r="N199" s="4" t="inlineStr"/>
+      <c r="O199" s="5" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -12088,9 +14063,15 @@
           <t>Unsere Tür steht offen — komm vorbei, Miodowa 21</t>
         </is>
       </c>
-      <c r="L200" s="2" t="inlineStr"/>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Eine einzelne Kerze auf einem Fensterbrett, dahinter der graue, verregnete Warschauer November, unscharf im Hintergrund. · Bildaufbau/Licht: Kerze im vorderen Drittel, seitlich platziert (nicht mittig), das Fenster füllt den Rest. Auf die warme Flamme scharfstellen, die Stadt draußen bewusst weichzeichnen. Warmes Kerzenlicht gegen kaltes Grau — dieser Kontrast ist das ganze Bild. Kein weiterer Deko-Schnickschnack. · ggf. Text im Bild: "Fern der Heimat trauern. Du bist nicht allein."
+💡 Tipp: Bei echtem trübem Wetter fotografieren, damit das Grau draußen ehrlich wirkt. Belichtung leicht runterziehen (auf die Flamme tippen), dann leuchtet die Kerze warm und der Hintergrund bleibt gedämpft. Ein stilles Bild — Ruhe zulassen, nichts überladen.</t>
+        </is>
+      </c>
       <c r="M200" s="2" t="inlineStr"/>
-      <c r="N200" s="3" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr"/>
+      <c r="O200" s="3" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n">
@@ -12146,9 +14127,22 @@
           <t>Speicher dir das Reel und komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L201" s="4" t="inlineStr"/>
+      <c r="L201" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~55s
+0–4s — Bild: Titel auf ruhigem Grund, dann erste Adventskerze · Sprich: "Das ganze Kirchenjahr — in unter einer Minute."
+4–14s — Bild: Schnelle Clips Advent → Weihnachten (Kerze, dann Krippe) · Sprich: "Es beginnt im Advent: warten auf jemanden, der kommt. Weihnachten — er ist da."
+14–26s — Bild: Aschekreuz → schlichtes Kreuz → Sonnenaufgang · Sprich: "Aschermittwoch startet die Passionszeit. Karfreitag — der stille Tag. Ostern — von Dunkel zu Licht."
+26–38s — Bild: Wehender Vorhang (Pfingsten) → Erntegaben (Erntedank) → Lutherrose (Reformation) · Sprich: "Pfingsten, der Geburtstag der Kirche. Erntedank. Reformationstag."
+38–48s — Bild: Viele kleine Kerzen (Ewigkeitssonntag), dann zurück zur ersten Adventskerze · Sprich: "Und am Ewigkeitssonntag ein Licht für jeden, an den wir denken. Dann beginnt alles von vorn."
+48–52s — Bild: Kurze Montage aller Feste im Schnelldurchlauf · Sprich: "Von Anfang bis Ewigkeit — das trägt uns durchs Jahr."
+52–55s — Endcard: Lutherrose + "Speicher dir das Reel · So 09:30 · Miodowa 21"
+🎵 Musik: warm, durchgehend, mit klarem Rhythmus für die Schnitte (baut sich übers Jahr auf) · 💡 Tipp: Sammel übers ganze Jahr je einen 2–3-Sekunden-Clip pro Fest, dann hast du am 1. Advent das Material beisammen. Jeden Clip auf denselben Beat schneiden, damit das Tempo rund läuft. Als Pin-Post oben im Profil festhalten.</t>
+        </is>
+      </c>
       <c r="M201" s="4" t="inlineStr"/>
-      <c r="N201" s="5" t="inlineStr"/>
+      <c r="N201" s="4" t="inlineStr"/>
+      <c r="O201" s="5" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -12204,9 +14198,20 @@
           <t>Entdeck die Farben live — Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L202" s="2" t="inlineStr"/>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Titel auf einem Farbstreifen aus Violett, Weiß, Rot, Grün. Text: "Die Farben des Kirchenjahres — warum wechselt der Altarschmuck die Farbe?"
+Slide 2: Vollflächig Violett. Text: "Violett — Advent und Passionszeit. Farbe des Wartens und der Umkehr."
+Slide 3: Vollflächig Weiß. Text: "Weiß — Weihnachten und Ostern. Farbe des Festes und des Lichts."
+Slide 4: Vollflächig Rot. Text: "Rot — Pfingsten. Farbe des Heiligen Geistes, Feuer und Leben."
+Slide 5: Vollflächig Grün. Text: "Grün — die Zeit dazwischen. Farbe des Wachsens im Alltag."
+Slide 6: Wieder der Farbstreifen. Text: "Entdeck die Farben live bei uns — So 09:30, Miodowa 21."
+💡 Tipp: Nutze satte, ruhige Farbflächen mit viel Weißraum für den Text — das wirkt edel und ist in fünf Minuten in jeder App gebaut. Wenn ihr echte Paramente (Altartücher) in diesen Farben habt, fotografier sie statt reiner Farbflächen: das verbindet die Erklärung mit eurem echten Kirchenraum.</t>
+        </is>
+      </c>
       <c r="M202" s="2" t="inlineStr"/>
-      <c r="N202" s="3" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr"/>
+      <c r="O202" s="3" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n">
@@ -12262,9 +14267,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L203" s="4" t="inlineStr"/>
+      <c r="L203" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Schwarzbild bzw. ganz dunkler Anfang, Kamera ruhig · Text on screen: "Hör mal, wie es hier klingt" · Ton: die Orgel setzt ein (nur Klang, kein Sprechen)
+3–11s — Bild: Kamera fährt langsam vom Fuß der Orgelpfeifen nach oben · Text on screen: "Orgel, live vor dem Gottesdienst"
+11–17s — Bild: oben angekommen, das Licht über den Pfeifen, Kamera hält still · Ton: die Orgel klingt weiter
+17–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · Ton: der Orgelklang klingt langsam aus
+🎵 Musik: keine – der Orgelton IST die Musik, dezent und ruhig · 💡 Tipp: Handy hochkant an die Orgel legen und den Ton nah aufnehmen; nichts drüberlegen, nur den Originalklang.</t>
+        </is>
+      </c>
       <c r="M203" s="4" t="inlineStr"/>
-      <c r="N203" s="5" t="inlineStr"/>
+      <c r="N203" s="4" t="inlineStr"/>
+      <c r="O203" s="5" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -12320,9 +14335,14 @@
           <t>Speichern und folgen für den Vers der Woche</t>
         </is>
       </c>
-      <c r="L204" s="2" t="inlineStr"/>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Bibelvers-Karte im Markendesign – Aubergine-Hintergrund (#480048), Vers in Goldschrift, mittig groß. · Bildaufbau/Licht: quadratisch (1080×1080), viel Ruhe um den Text, Vers klar zentriert, darunter klein die Quelle. · Text im Bild: groß mittig "Der Herr ist mein Hirte, mir wird nichts mangeln.", darunter klein "Psalm 23,1", ganz unten dezent "Speicher ihn dir für Montag". · 💡 Tipp: Genug Rand lassen, damit die Karte auch als kleine Vorschau im Feed noch lesbar ist – lieber ein kurzer Vers groß als ein langer klein.</t>
+        </is>
+      </c>
       <c r="M204" s="2" t="inlineStr"/>
-      <c r="N204" s="3" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr"/>
+      <c r="O204" s="3" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n">
@@ -12378,9 +14398,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L205" s="4" t="inlineStr"/>
+      <c r="L205" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: weite, ruhige Aufnahme des leeren Raums, Kamera steht still · Text on screen: "Der Moment, bevor alles beginnt" · Ton: nur Raumatmosphäre
+4–10s — Bild: Nahaufnahme einer Hand, die die Kerzen entzündet, Streichholz trifft den Docht · Text on screen: "Kerzen an. Stille. Warschau draußen."
+10–16s — Bild: Fenster, dahinter gedämpft die Stadt · Ton: leise, ferne Straßengeräusche · Text on screen: "In ein paar Minuten füllt sich der Raum"
+16–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine – nur Originalton (Kerze, Raum, ferne Stadt) · 💡 Tipp: Handy auflegen oder abstützen für ruhige Bilder; langsame, wenige Schnitte, nichts hektisch.</t>
+        </is>
+      </c>
       <c r="M205" s="4" t="inlineStr"/>
-      <c r="N205" s="5" t="inlineStr"/>
+      <c r="N205" s="4" t="inlineStr"/>
+      <c r="O205" s="5" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -12436,9 +14466,19 @@
           <t>Komm vorbei – Miodowa 21</t>
         </is>
       </c>
-      <c r="L206" s="2" t="inlineStr"/>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Kamera nach oben gerichtet, Kirchturm oder Himmel mit ziehenden Wolken · Text on screen: "Glocken über Warschau" · Ton: die Glocken setzen ein
+4–11s — Bild: weiter der Himmel, Wolken ziehen (gern leichter Zeitraffer) · Text on screen: "Zeit für einen Moment Ruhe" · Ton: die Glocken läuten voll
+11–15s — Bild: der Turm/Himmel, ruhig gehalten · Text on screen: "Zweimal im Monat läuten sie für dich"
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine – nur der Glockenklang · 💡 Tipp: Wenn die Glocken vor Ort nicht hörbar sind, ruhigen Turmblick filmen und ein dezentes, echtes Glocken-Audio dezent unterlegen; Kamera an eine Wand lehnen, damit das Bild nicht wackelt.</t>
+        </is>
+      </c>
       <c r="M206" s="2" t="inlineStr"/>
-      <c r="N206" s="3" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr"/>
+      <c r="O206" s="3" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n">
@@ -12494,9 +14534,19 @@
           <t>Mehr Ruhe? Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L207" s="4" t="inlineStr"/>
+      <c r="L207" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–3s — Bild: Sonnenlicht fällt durchs Fenster auf Holz oder Stein, weicher Anfang · Text on screen: "15 Sekunden Stille für dich" · Ton: nur leise Raumatmosphäre
+3–8s — Bild: Kamera ganz langsam am Lichtstrahl entlanggeführt · Text on screen: "Atme einmal tief durch"
+8–13s — Bild: das Licht ruhig gehalten, Staub tanzt vielleicht darin · Text on screen: "Licht durchs Fenster, mehr braucht es nicht"
+13–15s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine, bewusst ohne – nur Raumton · 💡 Tipp: Handy auflegen und die Kamerabewegung SEHR langsam machen (oder gar nicht bewegen); der Reiz liegt in der Ruhe, nicht im Schwenk.</t>
+        </is>
+      </c>
       <c r="M207" s="4" t="inlineStr"/>
-      <c r="N207" s="5" t="inlineStr"/>
+      <c r="N207" s="4" t="inlineStr"/>
+      <c r="O207" s="5" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -12552,9 +14602,14 @@
           <t>Folgen und jeden Monat sammeln</t>
         </is>
       </c>
-      <c r="L208" s="2" t="inlineStr"/>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Vers-Karte im festen Serien-Template – Aubergine/Gold, immer gleiche Schrift und Anordnung, nur der Vers wechselt. · Bildaufbau/Licht: quadratisch, Vers groß und mittig, oben klein die feste Zeile "Vers-Karte des Monats", in einer Ecke dezent der Monat (z.B. "Juli"). · Text im Bild: "Vers-Karte des Monats" (klein, oben), der Vers (groß, Mitte), "Juli" (klein, Ecke), unten dezent "Ein Vers, den ganzen Monat lang". · 💡 Tipp: Template EINMAL sauber bauen und als Kopiervorlage speichern – so bleibt die Reihe über Monate identisch und wird sofort wiedererkannt.</t>
+        </is>
+      </c>
       <c r="M208" s="2" t="inlineStr"/>
-      <c r="N208" s="3" t="inlineStr"/>
+      <c r="N208" s="2" t="inlineStr"/>
+      <c r="O208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n">
@@ -12610,9 +14665,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L209" s="4" t="inlineStr"/>
+      <c r="L209" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Nahaufnahme des Streichholzes, das sich der Kerze nähert · Sprich (ruhig, warm): "Bevor wir feiern, zünden wir jedes Mal eine Kerze an." · Ton: das Zischen des Streichholzes
+4–9s — Bild: die Flamme fängt, Fokus auf dem wachsenden Licht · Text on screen: "Licht heißt: Du bist nicht allein"
+9–15s — Bild: die ruhig brennende Kerze, weiches Licht · Sprich: "Ein kleines Zeichen dafür, dass du gesehen bist."
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr dezent, warm im Hintergrund – oder ganz weglassen und nur den Flammen-Ton · 💡 Tipp: Kein Gesicht nötig, nur die Hand; nah rangehen und auf weiches, warmes Licht achten – Deckenlicht aus, Kerze wirken lassen.</t>
+        </is>
+      </c>
       <c r="M209" s="4" t="inlineStr"/>
-      <c r="N209" s="5" t="inlineStr"/>
+      <c r="N209" s="4" t="inlineStr"/>
+      <c r="O209" s="5" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -12668,9 +14733,19 @@
           <t>Schreib dein Lieblingslied in die Kommentare</t>
         </is>
       </c>
-      <c r="L210" s="2" t="inlineStr"/>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: Ausschnitt des singenden Raums aus mittlerer Distanz (nur eingewilligte Personen im Bild) · Text on screen: "Unser Lied gerade" · Ton: der Gemeindegesang setzt ein
+3–12s — Bild: der Gesang läuft weiter, ruhig gehalten · Text on screen: "'Von guten Mächten' – EG 65" · Ton: voller Originalgesang
+12–17s — Bild: der ausklingende Gesang, vielleicht die Gesangbücher · Text on screen: "Wie klingt's bei dir? Schreib's uns"
+17–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine zusätzliche – der Gemeindegesang ist der Ton, echt und ungeschönt · 💡 Tipp: WICHTIG vorher das Einverständnis aller sichtbaren Personen einholen; im Zweifel von hinten oder seitlich filmen, sodass niemand erkennbar ist.</t>
+        </is>
+      </c>
       <c r="M210" s="2" t="inlineStr"/>
-      <c r="N210" s="3" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr"/>
+      <c r="O210" s="3" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n">
@@ -12726,9 +14801,21 @@
           <t>Durchwischen, speichern – und sonntags vorbeikommen</t>
         </is>
       </c>
-      <c r="L211" s="4" t="inlineStr"/>
+      <c r="L211" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1 (Titel): Aubergine/Gold, groß "5 Verse für schwere Tage", darunter klein "Zum Speichern – für den Moment, in dem die Worte fehlen".
+Slide 2 (Bei Angst): Überschrift "Bei Angst" + ein tröstender Vers dazu, z.B. "Fürchte dich nicht, denn ich bin bei dir." – Jesaja 41,10.
+Slide 3 (Bei Einsamkeit): Überschrift "Bei Einsamkeit" + Vers, z.B. "Ich bin bei euch alle Tage." – Matthäus 28,20.
+Slide 4 (Zum Danken): Überschrift "Zum Danken" + Vers, z.B. "Danket dem Herrn, denn er ist freundlich." – Psalm 118,1.
+Slide 5 (Für den Neuanfang): Überschrift "Für den Neuanfang" + Vers, z.B. "Siehe, ich mache alles neu." – Offenbarung 21,5.
+Slide 6 (Zur Ruhe): Überschrift "Zur Ruhe" + Vers, z.B. "Bei Gott allein kommt meine Seele zur Ruhe." – Psalm 62,2.
+Slide 7 (Einladung): "Wir sind sonntags für dich da." + "So 09:30 · Miodowa 21" + Lutherrose.
+💡 Tipp: Alle Karten im identischen Layout halten, nur Überschrift und Vers wechseln – so wirkt die Reihe wie aus einem Guss und lädt zum Speichern ein.</t>
+        </is>
+      </c>
       <c r="M211" s="4" t="inlineStr"/>
-      <c r="N211" s="5" t="inlineStr"/>
+      <c r="N211" s="4" t="inlineStr"/>
+      <c r="O211" s="5" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -12784,9 +14871,19 @@
           <t>Komm rein – Miodowa 21, Sonntag 09:30</t>
         </is>
       </c>
-      <c r="L212" s="2" t="inlineStr"/>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–5s — Bild: Regen auf Kopfsteinpflaster, nah, Tropfen springen · Text on screen: "Der Weg zu uns, wenn's regnet" · Ton: Regen, nah aufgenommen
+5–11s — Bild: Schirm von oben oder seitlich, Schritte übers nasse Pflaster · Text on screen: "Nur Regen, Schritte, eine offene Tür" · Ton: Schritte und Regen
+11–17s — Bild: Ankunft an der Kirchentür, die Tür öffnet sich · Text on screen: "Komm rein" · Ton: das Öffnen der Tür, Regen wird leiser
+17–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine – reiner Originalton, das ist der ASMR-Reiz · 💡 Tipp: Ton entscheidet – Handy-Mikro nah an den Regen halten und Wind vermeiden; ruhiges, langsames Tempo, keine schnellen Schnitte.</t>
+        </is>
+      </c>
       <c r="M212" s="2" t="inlineStr"/>
-      <c r="N212" s="3" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr"/>
+      <c r="O212" s="3" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n">
@@ -12842,9 +14939,20 @@
           <t>Tipp auf den Sticker und stimm ab</t>
         </is>
       </c>
-      <c r="L213" s="4" t="inlineStr"/>
+      <c r="L213" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s (hochkant, Story)
+0–2s — Bild: der Raum, Orgel im Blick · Text on screen: "Orgel oder Stille?" · Ton: Orgel setzt ein
+2–10s — Bild: Orgelspiel, ruhig gehalten · Text on screen: "Erst 10 Sekunden Klang" · Ton: voller Orgelklang
+10–12s — Bild: harter Schnitt in denselben Raum, jetzt still · Text on screen: "Dann 10 Sekunden Stille" · Ton: nichts
+12–18s — Bild: der stille Raum, kaum Bewegung · Ton: völlige Stille, nur ganz leise Raumatmosphäre
+18–20s — Bild: Frage-/Umfrage-Sticker groß platzieren · Text on screen: "Was tut dir gerade gut?"
+🎵 Musik: keine – erst Orgel, dann bewusst Stille · 💡 Tipp: Hochkant filmen und den Umfrage-Sticker (Orgel / Stille) so setzen, dass er nichts Wichtiges verdeckt; den Stille-Teil wirklich still lassen, nicht nachvertonen.</t>
+        </is>
+      </c>
       <c r="M213" s="4" t="inlineStr"/>
-      <c r="N213" s="5" t="inlineStr"/>
+      <c r="N213" s="4" t="inlineStr"/>
+      <c r="O213" s="5" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -12900,9 +15008,14 @@
           <t>Original ansehen – komm vorbei, Miodowa 21</t>
         </is>
       </c>
-      <c r="L214" s="2" t="inlineStr"/>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: das echte Foto vom Vers/Spruch an der Gemeindewand, kombiniert mit der nachgebauten Marken-Karte desselben Verses (Aubergine/Gold). · Bildaufbau/Licht: als Doppelbild (oben echtes Foto, unten die Karte) oder zwei Slides; das reale Foto gut ausleuchten, gerade fotografieren, sodass der Wandtext lesbar ist. · Text im Bild: oben klein "Dieser Vers hängt bei uns an der Wand", am echten Foto "Von echt …", an der Karte "… zu unserer Karte für dich". · 💡 Tipp: Beim Wandfoto seitliches Licht vermeiden, das Reflexe/Schatten wirft – lieber frontal und gerade, damit der Original-Charakter klar bleibt.</t>
+        </is>
+      </c>
       <c r="M214" s="2" t="inlineStr"/>
-      <c r="N214" s="3" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr"/>
+      <c r="O214" s="3" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
@@ -12958,9 +15071,19 @@
           <t>Bis nächsten Sonntag – 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L215" s="4" t="inlineStr"/>
+      <c r="L215" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: die brennenden Kerzen nah, ruhig, warmes Licht · Text on screen: "Kurz bevor das Licht ausgeht" · Ton: leise Raumatmosphäre
+4–11s — Bild: das Löschen, Rauchfäden steigen im Gegenlicht auf · Text on screen: "Der Rauch steigt, der Sonntag klingt aus" · Ton: original, ganz leise
+11–15s — Bild: der letzte Rauch verweht, das Bild wird ruhig · Text on screen: "Bis nächsten Sonntag"
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr dezent und warm – oder ganz still lassen · 💡 Tipp: Gegen eine Lichtquelle filmen (Fenster im Rücken der Kerze), dann werden die Rauchfäden erst richtig sichtbar; dunkler Hintergrund hilft.</t>
+        </is>
+      </c>
       <c r="M215" s="4" t="inlineStr"/>
-      <c r="N215" s="5" t="inlineStr"/>
+      <c r="N215" s="4" t="inlineStr"/>
+      <c r="O215" s="5" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -13016,9 +15139,19 @@
           <t>Speichern – oder Sonntag 09:30 live erleben</t>
         </is>
       </c>
-      <c r="L216" s="2" t="inlineStr"/>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–3s — Bild: ruhige Kerze oder Licht am Fenster · Text on screen: "Ein Segen zum Mitnehmen" · Sprich (ruhig, warm): "Ein alter Segen – für dich."
+3–16s — Bild: dasselbe ruhige Lichtbild, kaum Bewegung, Untertitel mitlaufen lassen · Sprich langsam: "Der Herr segne dich und behüte dich. Der Herr lasse sein Angesicht leuchten über dir und sei dir gnädig. Der Herr hebe sein Angesicht über dich und gebe dir Frieden."
+16–19s — Bild: die Kerze, ruhig · Text on screen: "Speicher ihn dir für später"
+19–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine oder sehr leise – die Stimme muss klar tragen · 💡 Tipp: Voiceover in einem ruhigen Raum getrennt aufnehmen (nah ans Mikro, weich sprechen) und erst danach unter das Bild legen; Untertitel setzen, viele hören ohne Ton.</t>
+        </is>
+      </c>
       <c r="M216" s="2" t="inlineStr"/>
-      <c r="N216" s="3" t="inlineStr"/>
+      <c r="N216" s="2" t="inlineStr"/>
+      <c r="O216" s="3" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n">
@@ -13074,9 +15207,14 @@
           <t>Speichern und folgen für mehr</t>
         </is>
       </c>
-      <c r="L217" s="4" t="inlineStr"/>
+      <c r="L217" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Vers-Karte im Marken-Layout (Aubergine/Gold), darunter abgesetzt eine kurze, offene Gebetszeile in schlichter Schrift. · Bildaufbau/Licht: quadratisch, viel Ruhe und Weißraum; oben der Vers, darunter ein feiner Trenner, dann der Gebetssatz – klar getrennt, damit man beides erfasst. · Text im Bild: oben klein "Für heute Abend", der Vers (Mitte), darunter eine ehrliche Ein-Satz-Gebetszeile, z.B. "Gott, danke für heute. Das, was mir schwer ist, lege ich hin. Bleib bei mir. Amen.", ganz unten dezent "Kein perfektes Gebet nötig". · 💡 Tipp: Bewusst kein Kirchendeutsch – der Gebetssatz soll klingen, wie man wirklich denkt; lieber schlicht und ehrlich als fromm formuliert.</t>
+        </is>
+      </c>
       <c r="M217" s="4" t="inlineStr"/>
-      <c r="N217" s="5" t="inlineStr"/>
+      <c r="N217" s="4" t="inlineStr"/>
+      <c r="O217" s="5" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -13132,9 +15270,19 @@
           <t>Live erleben – Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L218" s="2" t="inlineStr"/>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~16s
+0–3s — Bild: ruhiges Bild des Raums · Text on screen: "Hör mit Kopfhörern 🎧" · Ton: noch still
+3–5s — Bild: der Raum, kaum Bewegung · Text on screen: "Kopfhörer rein, Augen zu" · Ton: ein einzelner Ton wird gesungen/gespielt
+5–13s — Bild: der weite Raum, ganz ruhig · Text on screen: "Ein Ton, der im Raum nachhallt" · Ton: der Nachhall läuft voll aus, langsam verklingend
+13–16s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine – nur der eine Ton und sein Nachhall · 💡 Tipp: Handy möglichst nah an die Klangquelle und den Raum vorher wirklich still machen; der ganze Effekt hängt am sauber eingefangenen Nachhall.</t>
+        </is>
+      </c>
       <c r="M218" s="2" t="inlineStr"/>
-      <c r="N218" s="3" t="inlineStr"/>
+      <c r="N218" s="2" t="inlineStr"/>
+      <c r="O218" s="3" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n">
@@ -13190,9 +15338,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L219" s="4" t="inlineStr"/>
+      <c r="L219" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: das Fenster im Sommerlicht, warm · Text on screen: "Ein Fenster, vier Jahreszeiten" + "Sommer"
+3–8s — Bild: dasselbe Fenster im Herbst, goldene Töne (weiche Überblendung) · Text on screen: "Herbst"
+8–13s — Bild: dasselbe Fenster im Winter, Schnee draußen · Text on screen: "Winter"
+13–17s — Bild: dasselbe Fenster im Frühling, erstes Grün · Text on screen: "Frühling"
+17–20s — Endcard: Text "Manches bleibt, während alles sich ändert" + Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig und warm, ein durchgehender leiser Ton, der die vier Bilder verbindet · 💡 Tipp: Die Handy-Position exakt markieren (Klebeband am Boden/Fensterbrett), damit der Ausschnitt über das Jahr identisch bleibt – nur so wirkt der Vergleich.</t>
+        </is>
+      </c>
       <c r="M219" s="4" t="inlineStr"/>
-      <c r="N219" s="5" t="inlineStr"/>
+      <c r="N219" s="4" t="inlineStr"/>
+      <c r="O219" s="5" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -13248,9 +15407,18 @@
           <t>Tipp deinen Vers an und folg uns</t>
         </is>
       </c>
-      <c r="L220" s="2" t="inlineStr"/>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s (hochkant, Story, statisch mit Sticker)
+0–3s — Bild: hochkant, oben groß die Frage · Text on screen: "Welcher Vers passt gerade zu dir?"
+3–12s — Bild: drei Vers-Karten untereinander/nebeneinander im Marken-Layout, klar mit 1, 2, 3 nummeriert (drei thematisch unterschiedliche Verse) · Text on screen: "1, 2 oder 3?"
+12–15s — Bild: Umfrage-/Tap-Sticker über die Karten gelegt · Text on screen: "Tipp deinen an"
+🎵 Musik: ruhig und dezent, gern ein sanfter Loop · 💡 Tipp: Die drei Karten groß genug und gut nummeriert setzen, den Tap-/Umfrage-Sticker so platzieren, dass er keine Verse verdeckt – hochkant im echten Story-Format (9:16) bauen.</t>
+        </is>
+      </c>
       <c r="M220" s="2" t="inlineStr"/>
-      <c r="N220" s="3" t="inlineStr"/>
+      <c r="N220" s="2" t="inlineStr"/>
+      <c r="O220" s="3" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="n">
@@ -13306,9 +15474,19 @@
           <t>Sei dabei – Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L221" s="4" t="inlineStr"/>
+      <c r="L221" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: vom hinteren Rand des Raums, Menschen im Vordergrund unscharf/von hinten · Text on screen: "So fängt unser Sonntag an" · Ton: das Orgel-Vorspiel setzt ein
+3–11s — Bild: der Raum füllt sich langsam, ruhige Bewegung · Text on screen: "Das erste Orgel-Vorspiel" · Ton: volles Vorspiel
+11–15s — Bild: der fast gefüllte Raum, es wird ruhig · Text on screen: "Der Raum füllt sich, es wird ruhig"
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine – das Orgel-Vorspiel trägt · 💡 Tipp: Auf den hinteren Reihen bleiben und niemanden erkennbar ins Bild nehmen; leichte Unschärfe im Vordergrund schützt die Privatsphäre und sieht gleichzeitig atmosphärisch aus.</t>
+        </is>
+      </c>
       <c r="M221" s="4" t="inlineStr"/>
-      <c r="N221" s="5" t="inlineStr"/>
+      <c r="N221" s="4" t="inlineStr"/>
+      <c r="O221" s="5" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -13364,9 +15542,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L222" s="2" t="inlineStr"/>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–5s — Bild: lauter Warschauer Stadtverkehr, Straße, Menschen, Hektik · Text on screen: "Wenn dir Warschau zu laut wird" · Ton: laut, voll, Stadtlärm
+5–6s — Bild: HARTER Schnitt in den stillen Gemeinderaum · Ton: schlagartig still
+6–12s — Bild: der ruhige, leise Raum, Kerze oder Fenster · Text on screen: "… dann gibt es hier einen leisen Ort" · Ton: fast Stille
+12–16s — Bild: eine deutsche Vers-Karte im Marken-Layout · Text on screen: "Und ein Wort auf Deutsch"
+16–18s — Endcard: Lutherrose + "Miodowa 21" + "Link in Bio → WhatsApp-Gruppe"
+🎵 Musik: keine im ersten Teil (Stadtlärm), dann bewusst Stille – der Lautstärke-Sprung ist der Effekt · 💡 Tipp: Den Lautstärke-Kontrast NICHT normalisieren/angleichen; genau der harte Sprung von laut zu leise macht das Reel.</t>
+        </is>
+      </c>
       <c r="M222" s="2" t="inlineStr"/>
-      <c r="N222" s="3" t="inlineStr"/>
+      <c r="N222" s="2" t="inlineStr"/>
+      <c r="O222" s="3" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="n">
@@ -13422,9 +15611,20 @@
           <t>Speichern – und in Warschau vorbeikommen</t>
         </is>
       </c>
-      <c r="L223" s="4" t="inlineStr"/>
+      <c r="L223" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1 (Titel): Reise-Sub-Layout (Aubergine/Gold + kleines Koffer-/Wege-Motiv in der Ecke), groß "Verse fürs Handgepäck", darunter klein "Zum Speichern – für alle, die unterwegs sind".
+Slide 2 (Für die neue Stadt): Überschrift "Für die neue Stadt" + Vers, z.B. "Ich bin bei dir und will dich behüten, wohin du auch gehst." – 1. Mose 28,15.
+Slide 3 (Fürs Fernweh): Überschrift "Fürs Fernweh" + Vers, z.B. "Von allen Seiten umgibst du mich." – Psalm 139,5.
+Slide 4 (Fürs Ankommen): Überschrift "Fürs Ankommen" + Vers, z.B. "Kommt her zu mir … ich will euch erquicken." – Matthäus 11,28.
+Slide 5 (Für den Abschied): Überschrift "Für den Abschied" + Vers, z.B. "Der Herr behüte deinen Ausgang und Eingang." – Psalm 121,8.
+Slide 6 (Einladung): "In Warschau findest du ein Stück Zuhause." + "So 09:30 · Miodowa 21" + Lutherrose.
+💡 Tipp: Das Koffer-/Wege-Detail auf JEDER Karte an derselben Stelle wiederholen – dieses kleine Motiv macht die Reise-Reihe sofort als eigene Serie erkennbar.</t>
+        </is>
+      </c>
       <c r="M223" s="4" t="inlineStr"/>
-      <c r="N223" s="5" t="inlineStr"/>
+      <c r="N223" s="4" t="inlineStr"/>
+      <c r="O223" s="5" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -13480,9 +15680,20 @@
           <t>Live hören – Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L224" s="2" t="inlineStr"/>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~30s
+0–4s — Bild: Nahaufnahme der Hände auf den Orgeltasten, ruhig · Text on screen: "Hör 30 Sekunden lang nur zu" · Ton: die Improvisation setzt ein
+4–8s — Bild: die Hände spielen weiter, ruhig gehalten · Text on screen: "Kurz durchatmen" · Ton: voller Orgelklang
+8–14s — Bild: dieselbe Nahaufnahme · Text on screen: "Orgel-Improvisation, live" (danach kein Text mehr) · Ton: nur der Klang
+14–27s — Bild: ruhige Hände/Tasten, langsame kleine Bewegung, keine Einblendung · Ton: nur die Improvisation
+27–30s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine zusätzliche – die Orgel-Improvisation IST die Musik · 💡 Tipp: Text bewusst nur am Anfang; danach das Bild und den Klang ganz für sich stehen lassen – Handy nah an die Pfeifen/Tasten für satten Ton.</t>
+        </is>
+      </c>
       <c r="M224" s="2" t="inlineStr"/>
-      <c r="N224" s="3" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr"/>
+      <c r="O224" s="3" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="n">
@@ -13538,9 +15749,19 @@
           <t>Komm vorbei – Miodowa 21, Sonntag 09:30</t>
         </is>
       </c>
-      <c r="L225" s="4" t="inlineStr"/>
+      <c r="L225" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: das tiefe, warme Winterlicht fällt in den Raum, goldene Töne · Text on screen: "Das schönste Licht ist im Winter um 15 Uhr" · Ton: leise Raumatmosphäre
+4–10s — Bild: Kerzen ins Bild geholt, sie ergänzen das warme Licht · Text on screen: "Gegen die Novemberschwere"
+10–15s — Bild: langsame, ruhige Kamerabewegung durch den warmen Raum · Text on screen: "Ein warmer Ort, wenn's früh dunkel wird"
+15–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig und warm, sehr dezent · 💡 Tipp: Die goldene Stunde (kurz vor Dämmerung) nutzen und die warmen Farben in der Nachbearbeitung NICHT neutralisieren – genau die Wärme ist die Botschaft.</t>
+        </is>
+      </c>
       <c r="M225" s="4" t="inlineStr"/>
-      <c r="N225" s="5" t="inlineStr"/>
+      <c r="N225" s="4" t="inlineStr"/>
+      <c r="O225" s="5" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -13596,9 +15817,14 @@
           <t>Speichern und vorbeikommen – Miodowa 21</t>
         </is>
       </c>
-      <c r="L226" s="2" t="inlineStr"/>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: reales Foto von ul. Miodowa 21 (Eingang/Fassade), darüber sanft die Vers-Karte im Marken-Layout eingeblendet. · Bildaufbau/Licht: das Ortsfoto gerade und bei gutem Tageslicht aufnehmen; die Karte halbtransparent oder als klar abgesetzter Block darüberlegen, mit dunklem Verlauf hinter dem Text für Lesbarkeit. · Text im Bild: der Vers (groß, aus der Karte), darunter "ul. Miodowa 21, Warschau", dezent "Schön gedacht, echt zu finden". · 💡 Tipp: Genug Kontrast zwischen Karte und Ortsfoto sicherstellen – lieber einen ruhigen Bildausschnitt der Fassade wählen, damit der Vers klar lesbar bleibt.</t>
+        </is>
+      </c>
       <c r="M226" s="2" t="inlineStr"/>
-      <c r="N226" s="3" t="inlineStr"/>
+      <c r="N226" s="2" t="inlineStr"/>
+      <c r="O226" s="3" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n">
@@ -13654,9 +15880,20 @@
           <t>Bleib kurz – und komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L227" s="4" t="inlineStr"/>
+      <c r="L227" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: ein ruhiges Standbild – Kerze, Fenster oder Kreuz, Kamera steht still · Text on screen: "Stille ist auch Gebet" · Ton: fast nichts, nur ganz leise Raumatmosphäre
+4–9s — Bild: dasselbe Motiv, kaum Bewegung · Text on screen: "Einatmen" (langsam eingeblendet)
+9–14s — Bild: unverändert ruhig · Text on screen: "Ausatmen"
+14–17s — Bild: das stille Motiv · Text on screen: "Da sein, mehr nicht"
+17–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine – bewusst fast tonlos, das ist der Gegenpol zum lauten Feed · 💡 Tipp: Die Untertitel im echten Atem-Tempo einblenden (Einatmen ~4s halten, Ausatmen ~5s), damit die Betrachter wirklich mitatmen; Handy auflegen für ein absolut ruhiges Bild.</t>
+        </is>
+      </c>
       <c r="M227" s="4" t="inlineStr"/>
-      <c r="N227" s="5" t="inlineStr"/>
+      <c r="N227" s="4" t="inlineStr"/>
+      <c r="O227" s="5" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -13712,9 +15949,19 @@
           <t>Frag anonym über den Sticker in der Story</t>
         </is>
       </c>
-      <c r="L228" s="2" t="inlineStr"/>
+      <c r="L228" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~40s (ein Antwort-Clip, pro Frage wiederholen)
+0–4s — Bild: Pfarrer sitzt ruhig, Frontkamera, warmes Fensterlicht von der Seite · On-Screen (oben): "Warum lässt Gott Leid zu?" · Sprich: "Das ist die Frage, die mir am häufigsten gestellt wird — und die ehrlichste Antwort ist: Ich weiß es auch nicht ganz."
+4–18s — Bild: näher ran, Pfarrer schaut direkt in die Linse · Sprich: "Ich glaube nicht, dass Gott Leid schickt. Aber ich glaube, dass er mitten drin bei uns ist — auch dann, wenn wir ihn gerade nicht spüren."
+18–34s — Bild: gleiche Einstellung, ruhig · Sprich: "Du musst diese Frage nicht auflösen, um glauben zu dürfen. Zweifeln und glauben schließen sich nicht aus. Du darfst beides mitbringen."
+34–40s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · On-Screen: "Deine Frage ist willkommen"
+🎵 Musik: ruhig/warm/dezent, sehr leise · 💡 Tipp: Nicht auswendig aufsagen — lieber einmal frei sprechen, kleine Pausen und ein ehrliches "hm" wirken echter als der perfekte Take.</t>
+        </is>
+      </c>
       <c r="M228" s="2" t="inlineStr"/>
-      <c r="N228" s="3" t="inlineStr"/>
+      <c r="N228" s="2" t="inlineStr"/>
+      <c r="O228" s="3" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n">
@@ -13770,9 +16017,17 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L229" s="4" t="inlineStr"/>
+      <c r="L229" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Eine einzelne brennende Altarkerze im halbdunklen Synodalsaal, im Hintergrund weich verschwommen die Stuhlreihen. Alternativ das aufgeschlagene Gesangbuch mit der Kerze daneben.
+Bildaufbau/Licht: Spätnachmittags-Fenster­licht oder nur das Kerzenlicht selbst — warm, keine Deckenlampe. Kamera leicht von schräg oben, Kerze aus der Bildmitte nach links, damit rechts Platz für Text bleibt. Hochformat 9:16.
+Text im Bild: "Morgen früh sehen wir uns" (oben), darunter Countdown-Sticker auf So 09:30, unten Orts-Sticker "Miodowa 21".
+💡 Tipp: In den flackernden Momenten der Kerze auslösen (Serienbild) und das wärmste Einzelbild wählen — Kerzenlicht sieht auf Fotos lebendiger aus als bei Deckenlicht.</t>
+        </is>
+      </c>
       <c r="M229" s="4" t="inlineStr"/>
-      <c r="N229" s="5" t="inlineStr"/>
+      <c r="N229" s="4" t="inlineStr"/>
+      <c r="O229" s="5" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -13828,9 +16083,17 @@
           <t>Schick deinen Vers über den Sticker</t>
         </is>
       </c>
-      <c r="L230" s="2" t="inlineStr"/>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Zwei Storys nacheinander. (A) Aufruf-Story: schlichter Aubergine-Hintergrund (#480048) mit Fragen-Sticker "Welcher Bibelvers trägt dich gerade?". (B) Vorlage für die Einsendungen: derselbe Aubergine-Hintergrund, ein eingesandter Vers zentriert.
+Bildaufbau/Licht: Rein digital gebaut, kein Foto nötig. Heller, warmweißer Serifentext (creme, nicht reinweiß) mittig, viel Luft rundherum. Quelle klein und dezent darunter, z. B. "Psalm 23". Bei Einsendungen unten klein "— aus unserer Gemeinde" oder "anonym".
+Text im Bild: "Welcher Vers trägt dich?" / bzw. der Vers selbst, groß und ruhig gesetzt.
+💡 Tipp: Einen festen Look definieren (gleicher Hintergrund, gleiche Schrift, gleiche Position) und alle Wochen-Storys damit bauen — so wird die Reihe sofort wiedererkennbar.</t>
+        </is>
+      </c>
       <c r="M230" s="2" t="inlineStr"/>
-      <c r="N230" s="3" t="inlineStr"/>
+      <c r="N230" s="2" t="inlineStr"/>
+      <c r="O230" s="3" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="n">
@@ -13886,9 +16149,17 @@
           <t>Stimm im Sticker ab</t>
         </is>
       </c>
-      <c r="L231" s="4" t="inlineStr"/>
+      <c r="L231" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Warmes Alltagsfoto vom Kaffeetisch nach dem Gottesdienst — eine Kaffeekanne neben einer Teekanne, zwei Tassen. Alternativ schlichter Aubergine-Hintergrund.
+Bildaufbau/Licht: Von leicht oben auf den Tisch, Tageslicht vom Fenster, warm. Kanne/Tassen aus der Mitte nach unten setzen, oben Platz für Frage und Sticker. Hochformat.
+Text im Bild: "Diese oder jene?" (oben), darunter Umfrage-Sticker mit zwei Optionen "Kaffee ☕ / Tee 🫖". Folge-Story: Ergebnis-Screenshot + "Ihr habt entschieden 💛".
+💡 Tipp: Mach daraus eine feste Wochenserie mit immer gleicher Optik ("Diese oder jene?") — wiederkehrende Formate bauen Gewohnheit auf und die Leute warten drauf.</t>
+        </is>
+      </c>
       <c r="M231" s="4" t="inlineStr"/>
-      <c r="N231" s="5" t="inlineStr"/>
+      <c r="N231" s="4" t="inlineStr"/>
+      <c r="O231" s="5" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -13944,9 +16215,17 @@
           <t>Teile dein Anliegen anonym im Sticker</t>
         </is>
       </c>
-      <c r="L232" s="2" t="inlineStr"/>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Ruhige Altarkerze in weichem, gedämpftem Licht — oder gefaltete Hände auf dunklem Tisch, nur angeschnitten, nicht das Gesicht.
+Bildaufbau/Licht: Sehr ruhig, dunkler und stiller als sonst. Warmes Kerzen- oder Seitenlicht, viel Schatten, keine grellen Stellen. Motiv unten/seitlich, oben Raum für Frage und den Vertraulichkeits-Hinweis.
+Text im Bild: "Wofür sollen wir am Sonntag beten?" (oben), klein und klar darunter: "anonym · vertraulich · wird nicht öffentlich gezeigt", dann der Fragen-Sticker. Folge-Story schlicht: "Wir haben für euch gebetet."
+💡 Tipp: Den Vertraulichkeits-Satz wirklich sichtbar setzen — bei diesem sensiblen Thema entscheidet das Gefühl von Sicherheit darüber, ob jemand sich traut zu schreiben.</t>
+        </is>
+      </c>
       <c r="M232" s="2" t="inlineStr"/>
-      <c r="N232" s="3" t="inlineStr"/>
+      <c r="N232" s="2" t="inlineStr"/>
+      <c r="O232" s="3" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n">
@@ -14002,9 +16281,17 @@
           <t>Rate im Sticker — Auflösung in der nächsten Story</t>
         </is>
       </c>
-      <c r="L233" s="4" t="inlineStr"/>
+      <c r="L233" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Extreme Nahaufnahme eines einzelnen Details — Fensterkreuz mit einfallendem Licht, ein alter Kerzenständer, der Rücken eines abgegriffenen Gesangbuchs, eine geschnitzte Ecke.
+Bildaufbau/Licht: Ganz nah ran, sodass man erst mal rätselt, was es ist. Weiches Seitenlicht, das Struktur zeigt (Holzmaserung, Metallglanz). Motiv füllt den Rahmen, ein Fleck freier Fläche oben für Frage + Sticker.
+Text im Bild: "Wo ist das? 🔍" (oben), Quiz-/Umfrage-Sticker darunter. Folge-Story: dasselbe Detail aus mehr Distanz + eine warme Zeile Geschichte dazu.
+💡 Tipp: Handy dicht ans Motiv, dann zum Fokussieren einmal auf den Bildschirm tippen und leicht zurückweichen — so wird die Nahaufnahme scharf statt matschig.</t>
+        </is>
+      </c>
       <c r="M233" s="4" t="inlineStr"/>
-      <c r="N233" s="5" t="inlineStr"/>
+      <c r="N233" s="4" t="inlineStr"/>
+      <c r="O233" s="5" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -14060,9 +16347,17 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L234" s="2" t="inlineStr"/>
+      <c r="L234" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Warmes Warschau-Foto mit Wiedererkennung, aber nicht Postkarte — eine Straße in der Altstadt im Abendlicht, ein Café-Fenster, oder der einladende Gemeinderaum mit offener Tür.
+Bildaufbau/Licht: Goldene Stunde oder warmes Innenlicht, einladend statt kühl. Etwas Tiefe im Bild (Gasse, Fluchtlinie), oben und mittig Raum für Frage und Sticker.
+Text im Bild: "Neu in Warschau? 👋" (oben), darunter Fragen-Sticker "Seit wann bist du hier — und was fehlt dir am meisten?". Folge-Story auf eine Antwort: herzliche Reaktion + Link-Sticker zur WhatsApp-Gruppe.
+💡 Tipp: In Antwort-Storys nie belehren, sondern spiegeln — "Deutsches Brot fehlt dir? Kennen wir. Komm in die Gruppe, da hat jemand einen Tipp." Nähe entsteht durchs Eingehen, nicht durchs Einladen.</t>
+        </is>
+      </c>
       <c r="M234" s="2" t="inlineStr"/>
-      <c r="N234" s="3" t="inlineStr"/>
+      <c r="N234" s="2" t="inlineStr"/>
+      <c r="O234" s="3" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n">
@@ -14118,9 +16413,17 @@
           <t>Schieb den Regler im Sticker</t>
         </is>
       </c>
-      <c r="L235" s="4" t="inlineStr"/>
+      <c r="L235" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Sehr ruhiger, weicher Hintergrund — Aubergine-Fläche (#480048) oder ein unscharfes warmes Foto (Kerze, Fenster mit weichem Licht, verschwommene Herbstblätter).
+Bildaufbau/Licht: Bewusst reduziert und still, damit der Regler-Sticker im Mittelpunkt steht. Motiv unscharf/dezent, mittig viel Ruhe. Hochformat.
+Text im Bild: "Wie geht's dir diese Woche — wirklich?" (oben), Emoji-Schieberegler-Sticker mittig, z. B. 😴 → 🙏. Darunter klein: "ohne Wertung · du darfst ehrlich sein".
+💡 Tipp: Kein Foto von lachenden Menschen dahinter — das erzeugt Druck, gut drauf sein zu müssen. Ein ruhiger, offener Hintergrund lädt eher zur ehrlichen Antwort ein.</t>
+        </is>
+      </c>
       <c r="M235" s="4" t="inlineStr"/>
-      <c r="N235" s="5" t="inlineStr"/>
+      <c r="N235" s="4" t="inlineStr"/>
+      <c r="O235" s="5" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -14176,9 +16479,17 @@
           <t>Stell deine Frage im Sticker</t>
         </is>
       </c>
-      <c r="L236" s="2" t="inlineStr"/>
+      <c r="L236" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Freundlicher, heller Blick in den Gemeinderaum — offene Tür, Stuhlreihen, Tageslicht. Einladend, aufgeräumt, nicht leer-kühl.
+Bildaufbau/Licht: Frontal oder leicht schräg in den Raum hinein, Tageslicht vom Fenster. Der Raum unten, oben Platz für Q&amp;A-Sticker.
+Text im Bild: "Frag uns alles über die Gemeinde 💬" (oben), Q&amp;A-Sticker darunter. Antwort-Storys je Frage schlicht auf Aubergine, z. B. Frage "Muss ich Mitglied sein?" → Antwort groß: "Nein. Komm einfach."
+💡 Tipp: Die drei häufigsten Hemmschwellen-Fragen ruhig selbst vorformulieren und beantworten — das nimmt Schweigenden die Angst und zeigt: solche Fragen sind hier normal. Als Highlight "Erste Fragen" dauerhaft sichern.</t>
+        </is>
+      </c>
       <c r="M236" s="2" t="inlineStr"/>
-      <c r="N236" s="3" t="inlineStr"/>
+      <c r="N236" s="2" t="inlineStr"/>
+      <c r="O236" s="3" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="n">
@@ -14234,9 +16545,20 @@
           <t>Schreib dein Wort in die Kommentare</t>
         </is>
       </c>
-      <c r="L237" s="4" t="inlineStr"/>
+      <c r="L237" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1 (Titel): Aubergine-Hintergrund (#480048), heller Serifentext mittig — "Eure Worte fürs Jahr", klein darunter "— aus unserer Gemeinde".
+Slide 2: Ein Wort groß und zentriert, z. B. "Mut", darunter dezent eine kurze Einsendung dazu (falls vorhanden): "weil ich dieses Jahr springen will".
+Slide 3: Nächstes Wort groß — "Vertrauen".
+Slide 4: Nächstes Wort groß — "Ruhe".
+Slide 5: Nächstes Wort groß — "Neuanfang".
+Slide 6 (Abschluss/CTA): Alle Wörter klein zusammen als Wortfeld/Word-Cloud auf Aubergine, darüber "So klingt unsere Gemeinde", unten "Welches fehlt? Schreib's in die Kommentare 💬".
+💡 Tipp: Ein einziges Design-Raster (gleiche Schrift, gleiche Position, gleicher Hintergrund) für alle Wort-Slides nutzen — dann wirkt das Carousel wie aus einem Guss und ist in Canva in 10 Minuten dupliziert.</t>
+        </is>
+      </c>
       <c r="M237" s="4" t="inlineStr"/>
-      <c r="N237" s="5" t="inlineStr"/>
+      <c r="N237" s="4" t="inlineStr"/>
+      <c r="O237" s="5" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -14292,9 +16614,17 @@
           <t>Stimm im Umfrage-Sticker ab</t>
         </is>
       </c>
-      <c r="L238" s="2" t="inlineStr"/>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Kanzel oder aufgeschlagene Bibel im Seitenlicht — oder schlichter Aubergine-Hintergrund, wenn kein Foto verfügbar.
+Bildaufbau/Licht: Ruhig, warm, leicht von der Seite. Motiv nach unten/seitlich, oben viel Raum für Frage und Umfrage-Sticker (die drei Optionen brauchen Platz).
+Text im Bild: "Worüber sollen wir als Nächstes sprechen?" (oben), darunter Umfrage-Sticker mit "Vergebung / Angst / Dankbarkeit". Folge-Story: Ergebnis + "Am [Datum] ist es so weit 🗓️".
+💡 Tipp: Das Versprechen auch einlösen und in ein paar Wochen zurückverweisen ("Ihr habt 'Angst' gewählt — heute im Gottesdienst"). Wenn Beteiligung sichtbar Folgen hat, machen beim nächsten Mal mehr mit.</t>
+        </is>
+      </c>
       <c r="M238" s="2" t="inlineStr"/>
-      <c r="N238" s="3" t="inlineStr"/>
+      <c r="N238" s="2" t="inlineStr"/>
+      <c r="O238" s="3" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="n">
@@ -14350,9 +16680,19 @@
           <t>Reagier mit einem Herz, wenn du es brauchst</t>
         </is>
       </c>
-      <c r="L239" s="4" t="inlineStr"/>
+      <c r="L239" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–4s — Bild: Person aus dem Team, ruhig, warmes Fensterlicht, Handy auf Stativ/gestützt · On-Screen: "Ein Segen — für dich" · Sprich (langsam): "Ich möchte dir kurz etwas zusprechen. Egal, wo du gerade bist."
+4–14s — Bild: etwas näher ran, direkter Blick in die Linse · Sprich (ruhig, mit Pausen): "Der Herr segne dich und behüte dich. Er lasse sein Angesicht leuchten über dir und sei dir gnädig."
+14–18s — Bild: gleiche Einstellung, leichtes Lächeln · Sprich: "Wenn du das gerade brauchst, reagier mit einem Herz. Dann beten wir still für dich mit."
+18–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · On-Screen: "Du bist nicht allein"
+🎵 Musik: sehr ruhig/warm, kaum hörbar unter der Stimme · 💡 Tipp: Langsamer sprechen, als sich richtig anfühlt, und am Ende zwei Sekunden einfach still in die Kamera schauen — die Pause macht den Segen spürbar.</t>
+        </is>
+      </c>
       <c r="M239" s="4" t="inlineStr"/>
-      <c r="N239" s="5" t="inlineStr"/>
+      <c r="N239" s="4" t="inlineStr"/>
+      <c r="O239" s="5" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -14408,9 +16748,20 @@
           <t>Schreib deinen Wunsch in den Sticker</t>
         </is>
       </c>
-      <c r="L240" s="2" t="inlineStr"/>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~24s (Beispiel: Wunsch "Orgel")
+0–3s — Bild: Screenshot der Einsendung / Frage groß auf Aubergine · On-Screen: "Ihr wolltet die Orgel sehen" · Sprich: "Ihr habt gefragt — hier ist sie."
+3–9s — Bild: langsamer Schwenk die Orgelpfeifen hoch, dann auf die Tasten · Sprich: "Über hundert Jahre alt, und jeden Sonntag im Einsatz."
+9–17s — Bild: Nahaufnahme von Händen auf den Tasten, ein paar echte Töne als Ton · Sprich: "So klingt sie, wenn ihr sonntags reinkommt."
+17–21s — Bild: Blick vom Orgelplatz in den Kirchraum runter · Sprich: "Was sollen wir als Nächstes zeigen?"
+21–24s — Endcard: Lutherrose + "So 09:30 · Miodowa 21" · On-Screen: "Sag's uns im Sticker"
+🎵 Musik: dezent/warm — oder ganz weglassen und den echten Orgelton wirken lassen · 💡 Tipp: Bewegungen langsam führen (Schwenk über 4–5 Sek) und Handy mit beiden Händen an den Körper stützen — langsame, ruhige Kamera sieht auf dem Handy sofort hochwertiger aus.</t>
+        </is>
+      </c>
       <c r="M240" s="2" t="inlineStr"/>
-      <c r="N240" s="3" t="inlineStr"/>
+      <c r="N240" s="2" t="inlineStr"/>
+      <c r="O240" s="3" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="n">
@@ -14466,9 +16817,18 @@
           <t>Vervollständige den Satz im Sticker</t>
         </is>
       </c>
-      <c r="L241" s="4" t="inlineStr"/>
+      <c r="L241" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Schlichter Aubergine-Hintergrund (#480048), kein Foto — die Reduktion macht die offene Frage stark.
+Bildaufbau/Licht: Rein digital. Heller Serifentext, oben angesetzt "Kirche ist für mich …" mit sichtbarem Leerraum/Linie, darunter der Fragen-Sticker zum Vervollständigen. Viel Ruhe.
+Text im Bild: "Kirche ist für mich …" (offen gelassen), klein darunter "ehrlich — auch kritisch. Hier darfst du das."
+Zitat-Storys (Auflösung): dasselbe Aubergine-Layout, die eingesandte Antwort groß in Anführungszeichen, unten dezent "— anonym". Kommentarlos stehen lassen.
+💡 Tipp: Auch eine kritische Antwort ungeschönt teilen ("Kirche ist für mich oft zu laut über Sünde, zu leise über Liebe") — das signalisiert echte Offenheit und ist der glaubwürdigste Vertrauensbeweis, den ihr posten könnt.</t>
+        </is>
+      </c>
       <c r="M241" s="4" t="inlineStr"/>
-      <c r="N241" s="5" t="inlineStr"/>
+      <c r="N241" s="4" t="inlineStr"/>
+      <c r="O241" s="5" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -14524,9 +16884,20 @@
           <t>Wähl das nächste Lied im Umfrage-Sticker</t>
         </is>
       </c>
-      <c r="L242" s="2" t="inlineStr"/>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–3s — Bild: kurzer Rückblick — Screenshot des Umfrage-Stickers mit den zwei Liedern · On-Screen: "Ihr habt gewählt" · Text (kein Sprechen nötig): "Ihr habt entschieden …"
+3–7s — Bild: Aufgeschlagenes Gesangbuch auf der Liednummer, Hand blättert · On-Screen: der Liedtitel groß
+7–15s — Bild: Weiter Schwenk über die singende Gemeinde von hinten (keine erkennbaren Gesichter nötig), Orgel im Originalton · Text: —
+15–18s — Bild: die letzte Note klingt aus, ruhiger Kirchraum · On-Screen: "So klang's bei uns 💛"
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: KEIN Musikoverlay — der echte Gemeindegesang IST die Musik · 💡 Tipp: Von hinten oder seitlich filmen, damit keine Gesichter frontal erkennbar sind — so brauchst du niemanden vorher um Erlaubnis zu fragen und der Klang bleibt echt.</t>
+        </is>
+      </c>
       <c r="M242" s="2" t="inlineStr"/>
-      <c r="N242" s="3" t="inlineStr"/>
+      <c r="N242" s="2" t="inlineStr"/>
+      <c r="O242" s="3" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="n">
@@ -14582,9 +16953,17 @@
           <t>Grüß jemanden über den Sticker</t>
         </is>
       </c>
-      <c r="L243" s="4" t="inlineStr"/>
+      <c r="L243" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Warmes, verbindendes Bild — ein leerer Stuhl mit Licht drauf, zwei Kaffeetassen nebeneinander, oder Aubergine-Hintergrund. Etwas, das sanft an jemanden erinnert, der fehlt.
+Bildaufbau/Licht: Weich und warm, leicht wehmütig, nicht traurig. Motiv seitlich/unten, oben Platz für Frage und Sticker.
+Text im Bild: "Wen aus der Gemeinde vermisst du gerade? 💛" (oben), Fragen-Sticker darunter. Weitergabe-Story schlicht auf Aubergine: "Jemand aus der Gemeinde denkt gerade an dich."
+💡 Tipp: Grüße nur ohne Namen weitergeben ("jemand denkt an dich"), außer der Absender wünscht ausdrücklich einen Namen — so bleibt es diskret und niemand fühlt sich bloßgestellt.</t>
+        </is>
+      </c>
       <c r="M243" s="4" t="inlineStr"/>
-      <c r="N243" s="5" t="inlineStr"/>
+      <c r="N243" s="4" t="inlineStr"/>
+      <c r="O243" s="5" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -14640,9 +17019,19 @@
           <t>Komm jetzt vorbei — 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L244" s="2" t="inlineStr"/>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Nahaufnahme, ein Streichholz zündet die Altarkerze an · Text: —  · Sprich (aus dem Off, warm): "Guten Morgen — wir richten gerade her."
+4–9s — Bild: kurzer Schwenk über die Stuhlreihen, jemand legt Gesangbücher aus · On-Screen: "Gleich geht's los"
+9–14s — Bild: Kaffee wird aufgesetzt, Tassen kommen auf den Tisch · Sprich: "In 20 Minuten fangen wir an."
+14–18s — Bild: Person schaut in die Kamera, offene Tür im Rücken · Sprich: "Wenn du noch überlegst — komm einfach vorbei." · On-Screen: "09:30 · Miodowa 21" + Orts-Sticker
+🎵 Musik: keine oder nur Originalton (Kerze, Schritte, Tassen) — Live-Charakter wirkt echter · 💡 Tipp: Nicht schneiden-müssen wollen — roh und ungeschliffen ist bei diesem Format genau richtig, es soll wie ein spontaner Blick durch die Tür wirken, nicht wie Werbung.</t>
+        </is>
+      </c>
       <c r="M244" s="2" t="inlineStr"/>
-      <c r="N244" s="3" t="inlineStr"/>
+      <c r="N244" s="2" t="inlineStr"/>
+      <c r="O244" s="3" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="n">
@@ -14698,9 +17087,17 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L245" s="4" t="inlineStr"/>
+      <c r="L245" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Freundliches Foto einer Hand mit Smartphone (auf dem WhatsApp erkennbar geöffnet ist) im warmen Café-/Gemeinderaum-Licht. Alternativ Aubergine-Hintergrund.
+Bildaufbau/Licht: Warm, alltagsnah, das Handy leicht schräg gehalten. Motiv unten, oben Platz für Frage und Ja/Nein-Sticker.
+Text im Bild: "Kennst du schon unsere WhatsApp-Gruppe?" (oben), Ja/Nein-Umfrage-Sticker darunter. Folge-Story: "Noch nicht dabei? 👇" + Link-Sticker + eine Zeile "Infos, Grüße, spontane Treffen — kein Spam, versprochen."
+💡 Tipp: Immer erst die Umfrage, dann in der zweiten Story den Link — die kleine Ja/Nein-Interaktion erhöht die Reichweite, sodass der Link-Sticker danach mehr Leute erreicht.</t>
+        </is>
+      </c>
       <c r="M245" s="4" t="inlineStr"/>
-      <c r="N245" s="5" t="inlineStr"/>
+      <c r="N245" s="4" t="inlineStr"/>
+      <c r="O245" s="5" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -14756,9 +17153,20 @@
           <t>Teil deinen Dank in den Kommentaren</t>
         </is>
       </c>
-      <c r="L246" s="2" t="inlineStr"/>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1 (Titel): Aubergine-Hintergrund (#480048), heller Serifentext mittig — "Dankbarkeit der Gemeinde", klein darunter "was ihr uns diese Woche geschrieben habt".
+Slide 2: Ein Dank groß und zentriert — "Für einen Anruf, mit dem ich nicht gerechnet habe."
+Slide 3: Nächster Dank — "Dass mein Kind wieder gesund ist."
+Slide 4: Nächster Dank — "Für einen ganz gewöhnlichen, ruhigen Tag."
+Slide 5: Nächster Dank — "Dass ich hier nicht mehr fremd bin."
+Slide 6 (Abschluss/CTA): Aubergine, mittig "Wofür bist du diese Woche dankbar?", unten "Schreib's in die Kommentare 💛".
+💡 Tipp: Die Einsendungen wörtlich und ungeglättet übernehmen (kleine Alltagssätze wirken stärker als polierte) und anonym halten — ein festes Slide-Template macht den wöchentlichen Aufbau zur Routine.</t>
+        </is>
+      </c>
       <c r="M246" s="2" t="inlineStr"/>
-      <c r="N246" s="3" t="inlineStr"/>
+      <c r="N246" s="2" t="inlineStr"/>
+      <c r="O246" s="3" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n">
@@ -14814,9 +17222,17 @@
           <t>Rate im Quiz-Sticker mit</t>
         </is>
       </c>
-      <c r="L247" s="4" t="inlineStr"/>
+      <c r="L247" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Jahreszeitliches Stillleben — ein kleiner Erntekorb mit Äpfeln und Ähren, oder eine Kerze mit Herbstzweig, auf einem Holztisch.
+Bildaufbau/Licht: Warmes Tageslicht von der Seite, natürlicher Look. Motiv nach unten, oben Raum für Quiz-Sticker mit Antwortoptionen.
+Text im Bild: "Wie gut kennst du das Kirchenjahr? 🌾" (oben), Quiz-Sticker "Was feiern wir an Erntedank?" mit 3 Optionen. Folge-Story: richtige Antwort markiert + 2 warme Sätze Erklärung: "Erntedank heißt Danke sagen für das, was gewachsen ist — auch für das, was in uns gewachsen ist."
+💡 Tipp: Die Erklärung als Geschichte erzählen, nie als Belehrung — ein Bild oder ein Danke-Gedanke bleibt hängen, eine Definition scrollt man weg.</t>
+        </is>
+      </c>
       <c r="M247" s="4" t="inlineStr"/>
-      <c r="N247" s="5" t="inlineStr"/>
+      <c r="N247" s="4" t="inlineStr"/>
+      <c r="O247" s="5" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -14872,9 +17288,17 @@
           <t>Frag oder empfiehl über den Sticker</t>
         </is>
       </c>
-      <c r="L248" s="2" t="inlineStr"/>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Alltagsnahes Warschau-Foto — ein Bäckerei-Schaufenster, ein Marktstand, eine belebte Straße. Warm und konkret, nicht abstrakt.
+Bildaufbau/Licht: Tageslicht, lebendig, etwas Straßenatmosphäre. Motiv über die untere Bildhälfte, oben Platz für Frage und Fragen-Sticker.
+Text im Bild: "Frag die Gemeinde 🤝" (oben), Fragen-Sticker "Guter Arzt? Bäcker? Deutschkurs? Wer kennt was?". Folge-Storys: hilfreiche Empfehlungen weitergeben (mit Einverständnis) + "Wir sind nicht nur sonntags füreinander da."
+💡 Tipp: Empfehlungen kurz bündeln und als Highlight "Tipps für Warschau" speichern — daraus wird eine dauerhaft nützliche Ressource, die auch neue Follower anzieht.</t>
+        </is>
+      </c>
       <c r="M248" s="2" t="inlineStr"/>
-      <c r="N248" s="3" t="inlineStr"/>
+      <c r="N248" s="2" t="inlineStr"/>
+      <c r="O248" s="3" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n">
@@ -14930,9 +17354,17 @@
           <t>Schreib deine zwei Worte in den Sticker</t>
         </is>
       </c>
-      <c r="L249" s="4" t="inlineStr"/>
+      <c r="L249" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Ruhiger Kirchraum kurz nach dem Gottesdienst — die leere Kanzel, das Rednerpult, das Licht, das durch die Fenster fällt. Nachklang-Stimmung.
+Bildaufbau/Licht: Weiches Vormittagslicht, ruhig, ein bisschen "gerade ist etwas vorbei". Kanzel seitlich, oben Raum für Frage und Sticker.
+Text im Bild: "Beschreib die Predigt in zwei Worten" (oben), Fragen-Sticker darunter. Folge-Storys: einzelne Zwei-Wort-Antworten groß auf Aubergine ("nachdenklich · dankbar"). Optional kurzer Clip (~8s): Pfarrer liest eine Rückmeldung vom Handy ab und lächelt in die Kamera.
+💡 Tipp: Das Format sonntags direkt nach dem Segen posten, solange die Predigt noch frisch ist — die zwei-Wort-Beschränkung senkt die Hürde und bringt mehr Antworten als eine offene Frage.</t>
+        </is>
+      </c>
       <c r="M249" s="4" t="inlineStr"/>
-      <c r="N249" s="5" t="inlineStr"/>
+      <c r="N249" s="4" t="inlineStr"/>
+      <c r="O249" s="5" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -14988,9 +17420,17 @@
           <t>Zähl mit uns — schau täglich in die Story</t>
         </is>
       </c>
-      <c r="L250" s="2" t="inlineStr"/>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv (Serie, täglich gleiche Bildsprache): Tag für Tag eine brennende Kerze in warmem Dunkel — Tag 1 eine Kerze, dann wachsend Richtung Fest. Wechselnd daneben mal ein aufgeschlagener Vers, mal ein Gesangbuch.
+Bildaufbau/Licht: Immer dieselbe Ecke, dasselbe warme Kerzenlicht, hochformatiges Nah-Stillleben. Der wiederkehrende Look macht die Serie erkennbar. Countdown-Sticker konstant an gleicher Stelle.
+Text im Bild: Tag-Story oben "Tag für Tag zum Fest", darunter ein kurzer Gedanke/Vers, z. B. "Fürchtet euch nicht." + Countdown-Sticker. Festtags-Abschluss: besonderer Post "Heute ist es so weit 🕯️".
+💡 Tipp: Alle Bilder an EINEM Nachmittag vorproduzieren (eine Kerzenreihe abfotografieren) und dann täglich terminiert posten — so hält die Serie durch, ohne dass jeden Tag jemand ran muss.</t>
+        </is>
+      </c>
       <c r="M250" s="2" t="inlineStr"/>
-      <c r="N250" s="3" t="inlineStr"/>
+      <c r="N250" s="2" t="inlineStr"/>
+      <c r="O250" s="3" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="n">
@@ -15046,9 +17486,17 @@
           <t>Stimm ab — und bleib Sonntag auf einen Kaffee</t>
         </is>
       </c>
-      <c r="L251" s="4" t="inlineStr"/>
+      <c r="L251" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Gedeckter Kaffeetisch nach dem Gottesdienst — Tassen, eine Kanne, ein aufgeschnittener Kuchen, vielleicht eine Hand, die eine Tasse reicht.
+Bildaufbau/Licht: Leicht von oben auf den Tisch, warmes Fensterlicht, gemütlich und einladend. Fülle im Bild (mehrere Tassen) signalisiert Gemeinschaft. Oben Platz für Frage und Umfrage-Sticker.
+Text im Bild: "Nach dem Gottesdienst — Kaffee oder gleich weiter? ☕" (oben), Umfrage-Sticker darunter. Folge-Story: Ergebnis + "Egal wie du gestimmt hast: Der Tisch ist gedeckt, komm dazu." + dezent "So 09:30 · Miodowa 21".
+💡 Tipp: Auf Wärme statt Perfektion filmen — ein leicht unaufgeräumter, echter Tisch (Krümel, halbvolle Tassen) wirkt einladender als ein gestyltes Foto und senkt die Hemmschwelle zu bleiben.</t>
+        </is>
+      </c>
       <c r="M251" s="4" t="inlineStr"/>
-      <c r="N251" s="5" t="inlineStr"/>
+      <c r="N251" s="4" t="inlineStr"/>
+      <c r="O251" s="5" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -15104,9 +17552,17 @@
           <t>Stell deine Frage im Sticker</t>
         </is>
       </c>
-      <c r="L252" s="2" t="inlineStr"/>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Ehrenamtliche Person mitten in ihrer Aufgabe — Kaffee kochen, Gesangbücher auslegen, Kerzen anzünden. Wer scheu ist: von der Seite oder nur die Hände beim Tun.
+Bildaufbau/Licht: Warmes Innenlicht, natürlicher "mitten drin"-Moment statt gestelltes Porträt. Person/Hände im unteren Bilddrittel, oben Platz für Q&amp;A-Sticker.
+Text im Bild: "Frag unsere Ehrenamtlichen 🤍" (oben), Q&amp;A-Sticker "Warum machst du das eigentlich?". Antwort-Storys: kurze Selfie- oder Text-Story der Person, ehrlich, z. B. "Weil ich sonntags einen Ort gebraucht hab, an dem ich gebraucht werde."
+💡 Tipp: Nie zum Gesicht-Zeigen drängen — Hände beim Kerzenanzünden plus eine ehrliche Stimme wirken oft persönlicher als ein Porträt und die scheue Person macht eher mit.</t>
+        </is>
+      </c>
       <c r="M252" s="2" t="inlineStr"/>
-      <c r="N252" s="3" t="inlineStr"/>
+      <c r="N252" s="2" t="inlineStr"/>
+      <c r="O252" s="3" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="n">
@@ -15162,9 +17618,17 @@
           <t>Wähl deine Reaktion im Sticker</t>
         </is>
       </c>
-      <c r="L253" s="4" t="inlineStr"/>
+      <c r="L253" s="5" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Schlicht gestalteter Bibelvers auf Aubergine-Hintergrund (#480048), heller Serifentext, Vers zentriert — kein Foto, die Ruhe ist das Design.
+Bildaufbau/Licht: Rein digital. Vers groß und mittig mit viel Luft, Quelle klein darunter (z. B. "Matthäus 11,28"). Oben etwas Rand frei für die Frage, unten für den Sticker.
+Text im Bild: Der Vers selbst, darüber klein "Ein Vers — drei Reaktionen". Umfrage-/Emoji-Sticker mit drei Optionen: "tröstlich 🕊️ / herausfordernd 🔥 / rätselhaft 🌫️". Folge-Story: Ergebnis + je ein warmer Satz zu allen drei Deutungen.
+💡 Tipp: In der Auflösung wirklich alle drei Reaktionen würdigen ("auch 'rätselhaft' ist eine ehrliche Antwort auf Gott") — das hält die Einladung offen und niemand fühlt sich mit seiner Wahl falsch.</t>
+        </is>
+      </c>
       <c r="M253" s="4" t="inlineStr"/>
-      <c r="N253" s="5" t="inlineStr"/>
+      <c r="N253" s="4" t="inlineStr"/>
+      <c r="O253" s="5" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -15220,9 +17684,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L254" s="2" t="inlineStr"/>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s
+0–3s — Bild: Nahaufnahme, eine Hand zündet mit einem Streichholz eine Kerze an, warmes Licht · Text: "Es ist 09:30 — wir sind da."
+3–7s — Bild: Ruhiger Schwenk auf den vorbereiteten Raum, Wochenspruch auf einem Blatt · Sprich: "Der Wochenspruch begleitet uns diese Woche — und dich auch."
+7–12s — Bild: Person schaut warm in die Kamera · Sprich: "Ob du kommst oder nur kurz reinschaust: schön, dass du da bist."
+12–15s — Bild: Kurzes freundliches Winken, dann Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: Immer denselben Bildausschnitt und dieselbe Kerzenstelle nutzen — die Wiedererkennung entsteht durch Gleichheit, nicht durch Abwechslung.</t>
+        </is>
+      </c>
       <c r="M254" s="2" t="inlineStr"/>
-      <c r="N254" s="3" t="inlineStr"/>
+      <c r="N254" s="2" t="inlineStr"/>
+      <c r="O254" s="3" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n">
@@ -15278,9 +17752,19 @@
           <t>Schreib uns in den Kommentaren, was dich diese Woche beschäftigt</t>
         </is>
       </c>
-      <c r="L255" s="4" t="inlineStr"/>
+      <c r="L255" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Handgeschriebener Vers auf Papier wird langsam vor Fenster/Kerze ins Bild gehalten · Text: "Wort für die Woche"
+4–9s — Bild: Nahaufnahme der Schrift, Kamera hält ruhig, damit man mitlesen kann · Sprich: "Ein Vers, ein ehrlicher Gedanke — mehr braucht ein Montag manchmal nicht."
+9–16s — Bild: Person hält das Papier, schaut ruhig in die Kamera · Sprich: "Vielleicht triffst du diesen Satz gerade da, wo du heute stehst. Nimm ihn einfach mit in die Woche."
+16–20s — Bild: Papier sinkt langsam ab, letztes Wort bleibt stehen · Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: Schreib den Vers mit dickem Stift und großen Buchstaben — kleine Handschrift ist auf dem Handy nicht lesbar.</t>
+        </is>
+      </c>
       <c r="M255" s="4" t="inlineStr"/>
-      <c r="N255" s="5" t="inlineStr"/>
+      <c r="N255" s="4" t="inlineStr"/>
+      <c r="O255" s="5" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -15336,9 +17820,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 — jetzt kennst du schon den Weg</t>
         </is>
       </c>
-      <c r="L256" s="2" t="inlineStr"/>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Die geschlossene Eingangstür in ruhiger Totale, warmes Tageslicht · Text: "Hinter dieser Tür passiert sonntags etwas."
+3–9s — Bild: Langsamer Zoom auf ein Detail der Tür (Griff, Holz, Hausnummer) · Sprich: "Das ist Miodowa 21 — mitten in der Altstadt, und hier feiern wir sonntags Gottesdienst."
+9–15s — Bild: Kamera geht näher an die Tür heran, als würde man gleich eintreten · Sprich: "In dieser Reihe zeigen wir dir diesen Ort Stück für Stück — damit er dir vertraut wird, bevor du zum ersten Mal kommst."
+15–18s — Bild: Endcard: Lutherrose + "Kapitel 1: Die Tür · So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: In jeder Folge genau EIN Detail zeigen — nicht das ganze Haus. Die Reihe lebt von der Neugier auf das nächste Kapitel.</t>
+        </is>
+      </c>
       <c r="M256" s="2" t="inlineStr"/>
-      <c r="N256" s="3" t="inlineStr"/>
+      <c r="N256" s="2" t="inlineStr"/>
+      <c r="O256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
@@ -15394,9 +17888,19 @@
           <t>Link in Bio → WhatsApp-Gruppe für Deutschsprachige in Warschau</t>
         </is>
       </c>
-      <c r="L257" s="4" t="inlineStr"/>
+      <c r="L257" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1 (Titel): "Neu in Warschau? Gerade angekommen und keiner spricht deine Sprache?" — darunter klein: Thema des Monats, z.B. "Deutschsprachige Ärzte finden"
+Slide 2 (Warum): "Am Anfang ist alles fremd — Behörden, Ärzte, Einkaufen. Wir sammeln, was wirklich hilft."
+Slide 3 (Tipp 1): Konkreter Tipp mit Handy-Foto vom Ort, ein Satz Erklärung — z.B. "Praxis X spricht Deutsch, Anmeldung geht online."
+Slide 4 (Tipp 2): Zweiter konkreter Tipp, gleiche Machart — ein Ort, ein klarer Hinweis.
+Slide 5 (Abschluss): "Und sonntags bist du bei uns nicht allein." — darunter: Miodowa 21 · WhatsApp-Gruppe (Link in Bio)
+💡 Tipp: Pro Slide nur eine Kernaussage und maximal drei Zeilen Text — im Feed liest niemand vollgeschriebene Kacheln.</t>
+        </is>
+      </c>
       <c r="M257" s="4" t="inlineStr"/>
-      <c r="N257" s="5" t="inlineStr"/>
+      <c r="N257" s="4" t="inlineStr"/>
+      <c r="O257" s="5" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -15452,9 +17956,19 @@
           <t>Stell deine Frage in den Stories → wir antworten im nächsten Reel</t>
         </is>
       </c>
-      <c r="L258" s="2" t="inlineStr"/>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~30s
+0–4s — Bild: Pfarrer sitzt auf einem Stuhl, natürliches Licht, Frage groß eingeblendet · Sprich: "Frage der Woche: Muss ich eigentlich getauft sein, um zu euch zu kommen?"
+4–22s — Bild: Pfarrer schaut ruhig in die Kamera, antwortet in einem Take · Sprich: "Nein, musst du nicht. Zu unserem Gottesdienst ist jeder willkommen — getauft oder nicht, gläubig oder noch auf der Suche. Du musst nichts vorweisen, nichts können, nichts mitbringen außer dir selbst."
+22–27s — Bild: Ruhiges Schlussbild des Pfarrers · Text: "Keine Frage ist zu klein."
+27–30s — Bild: Endcard: Lutherrose + "Stell deine Frage in den Stories · So 09:30 · Miodowa 21"
+🎵 Musik: sehr leise oder keine — die Stimme trägt · 💡 Tipp: Handy auf Augenhöhe stellen und in einem Take sprechen — kleine Versprecher wirken echt und nahbar, nicht störend.</t>
+        </is>
+      </c>
       <c r="M258" s="2" t="inlineStr"/>
-      <c r="N258" s="3" t="inlineStr"/>
+      <c r="N258" s="2" t="inlineStr"/>
+      <c r="O258" s="3" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n">
@@ -15510,9 +18024,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21 — alles ist für dich bereit</t>
         </is>
       </c>
-      <c r="L259" s="4" t="inlineStr"/>
+      <c r="L259" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Leerer Saal am frühen Morgen, ruhige Totale, weiches Licht · Text: "Bevor ihr kommt, sieht das so aus."
+4–10s — Bild: Nahaufnahmen der Handgriffe — Stühle rücken, Gesangbücher auslegen · Sprich (leise, fast wie zu sich selbst): "Bevor sonntags jemand kommt, machen wir alles bereit."
+10–16s — Bild: Kleine warme Details — eine Kerze wird angezündet, ein Blumenstrauß gerichtet · Text: "Das Unspektakuläre, das ein Zuhause macht."
+16–20s — Bild: Der fertig vorbereitete Raum in ruhiger Totale · Endcard: Lutherrose + "Alles ist für dich bereit · So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent (trägt fast den ganzen Clip) · 💡 Tipp: Wenig oder gar nicht sprechen — dieser Clip lebt von Bildern und Ruhe. Handbewegungen langsam und bewusst ausführen.</t>
+        </is>
+      </c>
       <c r="M259" s="4" t="inlineStr"/>
-      <c r="N259" s="5" t="inlineStr"/>
+      <c r="N259" s="4" t="inlineStr"/>
+      <c r="O259" s="5" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -15568,9 +18092,20 @@
           <t>Sing mit uns Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L260" s="2" t="inlineStr"/>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~25s
+0–4s — Bild: Weite Aufnahme des leeren Saals mit Klavier, warmes Licht · Text: "Lied der Woche — hör mal rein."
+4–8s — Bild: Nahaufnahme der Hände am Klavier / des Gesichts der singenden Person · Sprich: "Das singen wir diesen Sonntag."
+8–20s — Bild: Eine Strophe wird gesungen oder gespielt, Handy nah dran für guten Ton · (kein Sprechen — nur der Choral)
+20–22s — Bild: Ruhiges Schlussbild · Text: "[Choral-Titel], [Jahr] — trägt bis heute."
+22–25s — Bild: Endcard: Lutherrose + "Sing mit uns · So 09:30 · Miodowa 21"
+🎵 Musik: keine zusätzliche — der Live-Ton IST die Musik · 💡 Tipp: Handy nah an Klavier oder Stimme stellen und den Raum vorher ruhig halten. Guter Ton schlägt hier jedes schöne Bild.</t>
+        </is>
+      </c>
       <c r="M260" s="2" t="inlineStr"/>
-      <c r="N260" s="3" t="inlineStr"/>
+      <c r="N260" s="2" t="inlineStr"/>
+      <c r="O260" s="3" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n">
@@ -15626,9 +18161,19 @@
           <t>Feier das nächste Fest mit uns — Termine in Bio</t>
         </is>
       </c>
-      <c r="L261" s="4" t="inlineStr"/>
+      <c r="L261" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1 (Titel): "Was ist eigentlich Epiphanias?" — darunter klein: "Kirchenjahr erklärt, ohne Fachjargon"
+Slide 2 (Was): "Was wird gefeiert? Die Erscheinung Gottes in der Welt — der Moment, in dem das Licht sichtbar wird."
+Slide 3 (Warum): "Warum? Weil auch die von weit her — die Weisen aus dem Morgenland — den Weg gefunden haben. Ein Fest für alle, die von irgendwoher kommen."
+Slide 4 (Wie): "Wie feiern wir es? Mit Handy-Foto aus der Gemeinde und einem Satz, was bei uns an dem Tag passiert."
+Slide 5 (Abschluss): "Feier mit uns." — darunter: passender Gottesdiensttermin · So 09:30 · Miodowa 21
+💡 Tipp: Ein klares Icon oder Symbol pro Slide (Stern, Kerze, Kreuz) macht die Reihe wiedererkennbar und die Kacheln ruhig.</t>
+        </is>
+      </c>
       <c r="M261" s="4" t="inlineStr"/>
-      <c r="N261" s="5" t="inlineStr"/>
+      <c r="N261" s="4" t="inlineStr"/>
+      <c r="O261" s="5" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -15684,9 +18229,19 @@
           <t>Erzähl uns deine Geschichte — komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L262" s="2" t="inlineStr"/>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~30s
+0–4s — Bild: Person sitzt entspannt im Gemeinderaum, natürliches Licht, schaut leicht neben die Kamera · Text: "Warum kommst du eigentlich?"
+4–24s — Bild: Person antwortet ehrlich in einem Take, Handkamera-Nähe · Sprich (Beispiel-Antwort der Person): "Ehrlich? Am Anfang wegen der Sprache — ich wollte einmal die Woche einfach Deutsch reden. Geblieben bin ich, weil hier keiner fragt, ob ich oft genug komme. Man ist einfach willkommen."
+24–27s — Bild: Ruhiges Schlussbild der Person · Text: "— Vorname (oder anonym)"
+27–30s — Bild: Endcard: Lutherrose + "Hier ist Platz für jede Geschichte · So 09:30 · Miodowa 21"
+🎵 Musik: sehr leise, warm · 💡 Tipp: Die Frage vorher locker stellen und die Person einfach reden lassen — die beste Antwort kommt meist nach dem zweiten Satz, nicht im ersten.</t>
+        </is>
+      </c>
       <c r="M262" s="2" t="inlineStr"/>
-      <c r="N262" s="3" t="inlineStr"/>
+      <c r="N262" s="2" t="inlineStr"/>
+      <c r="O262" s="3" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n">
@@ -15742,9 +18297,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21 — du findest uns</t>
         </is>
       </c>
-      <c r="L263" s="4" t="inlineStr"/>
+      <c r="L263" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~25s
+0–4s — Bild: Der Ausgang der Metrostation, Schild im Bild · Sprich: "Du startest hier — an der Metro Ratusz-Arsenał. Von hier sind es nur ein paar Minuten."
+4–12s — Bild: Gehsequenz aus der Ich-Perspektive, Handy in der Hand, natürliches Tempo · Text: "Rechts halten, Richtung Altstadt"
+12–19s — Bild: Markante Punkte am Weg (eine Ecke, ein Schild, ein Gebäude) · Sprich: "An dieser Ecke einfach weiter geradeaus — du kannst dich kaum verlaufen."
+19–22s — Bild: Ankunft an der Tür, Blick auf den Eingang · Sprich: "Und da sind wir schon: Miodowa 21."
+22–25s — Bild: Endcard: Lutherrose + "Du findest uns · So 09:30 · Miodowa 21"
+🎵 Musik: leicht, freundlich, dezent · 💡 Tipp: Beim Gehen das Handy mit beiden Händen ruhig halten oder gegen den Körper stützen — sonst wackelt die Ich-Perspektive zu stark.</t>
+        </is>
+      </c>
       <c r="M263" s="4" t="inlineStr"/>
-      <c r="N263" s="5" t="inlineStr"/>
+      <c r="N263" s="4" t="inlineStr"/>
+      <c r="O263" s="5" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -15800,9 +18366,19 @@
           <t>Sing die alten Worte mit uns — Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L264" s="2" t="inlineStr"/>
+      <c r="L264" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1 (Motiv): Nahaufnahme des aufgeschlagenen Gesangbuchs, die Liedzeile im Fokus — darüber klein: "Aus dem Gesangbuch"
+Slide 2 (Zeile groß): Die Liedzeile typografisch groß auf ruhigem Hintergrund (Aubergine-Ton) — darunter: "über 300 Jahre alt"
+Slide 3 (Geschichte 1): "Geschrieben wurde sie von [Name], in einer Zeit, in der [kurzer Umstand — Krieg, Verlust, Neuanfang]."
+Slide 4 (Geschichte 2): "Und doch klingt die Zeile, als wäre sie für heute geschrieben."
+Slide 5 (Abschluss): "Trifft das heute noch? Welche Zeile begleitet dich?" — darunter: So 09:30 · Miodowa 21
+💡 Tipp: Die Liedzeile auf Slide 2 wirklich groß setzen — sie ist das Herz des Posts. Warmes, ruhiges Licht bei der Buch-Aufnahme.</t>
+        </is>
+      </c>
       <c r="M264" s="2" t="inlineStr"/>
-      <c r="N264" s="3" t="inlineStr"/>
+      <c r="N264" s="2" t="inlineStr"/>
+      <c r="O264" s="3" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n">
@@ -15858,9 +18434,19 @@
           <t>Bleib auf einen Kaffee — Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L265" s="4" t="inlineStr"/>
+      <c r="L265" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–4s — Bild: Kaffee wird eingeschenkt, dampfende Tasse in Nahaufnahme · Text: "Der wichtigste Teil kommt nach dem Amen."
+4–10s — Bild: Gruppen im Gespräch, warme unscharfe Hintergründe (nur mit Einverständnis gefilmt) · Sprich: "Nach dem Amen ist noch lange nicht Schluss."
+10–15s — Bild: Lachen, Hände, ein Stück Kuchen — kleine Momente · Sprich: "Für viele beginnt der schönste Teil erst hier — beim Kaffee danach."
+15–18s — Bild: Zwei Tassen stoßen sanft aneinander · Endcard: Lutherrose + "Bleib auf einen Kaffee · So 09:30 · Miodowa 21"
+🎵 Musik: warm, leicht, fröhlich-dezent · 💡 Tipp: Gesichter nur mit Einverständnis zeigen — im Zweifel Hände, Tassen und unscharfe Hintergründe filmen, das wirkt oft sogar herzlicher.</t>
+        </is>
+      </c>
       <c r="M265" s="4" t="inlineStr"/>
-      <c r="N265" s="5" t="inlineStr"/>
+      <c r="N265" s="4" t="inlineStr"/>
+      <c r="O265" s="5" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -15916,9 +18502,20 @@
           <t>Folg uns für deinen wöchentlichen Moment der Stille</t>
         </is>
       </c>
-      <c r="L266" s="2" t="inlineStr"/>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~40s
+0–6s — Bild: Ruhige Totale des leeren Saals, Kerzenlicht, kaum Bewegung · Text: "Nimm dir kurz Zeit — nur atmen."
+6–16s — Bild: Langsame Nahaufnahme der Kerzenflamme · Sprich (sehr leise, langsam): "Was auch immer dein Tag bisher war — leg es für einen Moment ab."
+16–32s — Bild: Kaum bewegte Bilder, Flamme, weiches Licht · Sprich: "Atme ein. Und wieder aus. Du musst gerade nichts leisten, nichts schaffen, nichts sein. Du darfst einfach hier sein."
+32–36s — Bild: Kerze, sanftes Licht · Text: "Atme durch."
+36–40s — Bild: Sanftes Ausblenden · Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr leise, fast nur Raumton · 💡 Tipp: Bewusst langsam schneiden und lange Einstellungen stehen lassen — die Ruhe ist der Inhalt. Kein Text-Overload, höchstens ein Wort pro Einblendung.</t>
+        </is>
+      </c>
       <c r="M266" s="2" t="inlineStr"/>
-      <c r="N266" s="3" t="inlineStr"/>
+      <c r="N266" s="2" t="inlineStr"/>
+      <c r="O266" s="3" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n">
@@ -15974,9 +18571,19 @@
           <t>Frag uns in den Kommentaren, welchen Begriff wir als Nächstes erklären sollen</t>
         </is>
       </c>
-      <c r="L267" s="4" t="inlineStr"/>
+      <c r="L267" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1 (Titel): "Was heißt eigentlich Gnade?" — darunter klein: "Erklärt ohne Fachjargon, wie einem Freund"
+Slide 2 (Alltagsbild): "Stell dir vor, jemand schenkt dir etwas, obwohl du es dir nicht verdient hast — und erwartet nichts zurück. So ungefähr."
+Slide 3 (Für dich): "Für dein Leben heißt das: Du musst dich nicht erst gut genug machen. Du bist schon gemeint, so wie du bist."
+Slide 4 (Bei uns): "Wie wir das leben? Bei uns musst du nichts vorweisen, um dazuzugehören — komm einfach, wie du bist."
+Slide 5 (Abschluss): "Frag ruhig nach." — darunter: Welchen Begriff sollen wir als Nächstes erklären? · So 09:30 · Miodowa 21
+💡 Tipp: Sprache bewusst so wählen, wie du es einem Freund am Küchentisch erzählen würdest — kein einziges Kirchenwort, das man nachschlagen müsste.</t>
+        </is>
+      </c>
       <c r="M267" s="4" t="inlineStr"/>
-      <c r="N267" s="5" t="inlineStr"/>
+      <c r="N267" s="4" t="inlineStr"/>
+      <c r="O267" s="5" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -16032,9 +18639,19 @@
           <t>Teil unsere Geschichte weiter — und komm dazu, Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L268" s="2" t="inlineStr"/>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1 (Titel): "Heute vor einigen Jahren in unserer Gemeinde" — darüber klein: "Fenster zum Kirchenjahr"
+Slide 2 (Altes Foto): Das abfotografierte Archivfoto groß, warmes nostalgisches Licht — darunter: "So sah es damals bei uns aus."
+Slide 3 (Geschichte): "Was war das? Wer war dabei? — Ein, zwei Sätze zur Erinnerung hinter dem Foto."
+Slide 4 (Damals &amp; heute): Aktuelles Foto vom selben Ort daneben — "Und so sieht derselbe Ort heute aus."
+Slide 5 (Abschluss): "Unsere Geschichte trägt weiter — und du gehörst dazu." — darunter: So 09:30 · Miodowa 21
+💡 Tipp: Altes Foto bei Tageslicht am Fenster abfotografieren, nicht mit Blitz — so bleibt der warme, nostalgische Charakter erhalten und es spiegelt nicht.</t>
+        </is>
+      </c>
       <c r="M268" s="2" t="inlineStr"/>
-      <c r="N268" s="3" t="inlineStr"/>
+      <c r="N268" s="2" t="inlineStr"/>
+      <c r="O268" s="3" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="n">
@@ -16090,9 +18707,18 @@
           <t>Tipp auf den Countdown-Sticker → dann sehen wir uns Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L269" s="4" t="inlineStr"/>
+      <c r="L269" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~8s (Story)
+0–3s — Bild: Wiedererkennbares Intro — die Kerze oder die Tür in Nahaufnahme · Text: "Noch 3 Tage."
+3–6s — Bild: Datum und Uhrzeit groß, immer gleiches Layout · Sprich/Text: "Dann sehen wir uns — Sonntag 09:30, Miodowa 21."
+6–8s — Bild: Countdown-Sticker + Standort-Sticker zu Miodowa 21 platzieren · Text: "Tipp auf den Countdown!"
+🎵 Musik: kurz, freundlich, wiedererkennbar (immer derselbe Sound) · 💡 Tipp: Layout, Sound und Bildaufbau bei JEDER Folge identisch lassen — nur Datum und Zahl ändern. So wird der Reminder zur verlässlichen Gewohnheit.</t>
+        </is>
+      </c>
       <c r="M269" s="4" t="inlineStr"/>
-      <c r="N269" s="5" t="inlineStr"/>
+      <c r="N269" s="4" t="inlineStr"/>
+      <c r="O269" s="5" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -16148,9 +18774,19 @@
           <t>Verrate uns deinen stillen Ort in den Kommentaren</t>
         </is>
       </c>
-      <c r="L270" s="2" t="inlineStr"/>
+      <c r="L270" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–5s — Bild: Ruhige Aufnahme eines stillen Ortes, z.B. Weichselufer im Morgenlicht · Text: "Wo findest du hier Ruhe?"
+5–11s — Bild: Kleine Details — Wasser, Blätter, eine leere Bank · Sprich (leise): "Warschau kann laut sein. Aber es gibt diese Ecken, an denen man kurz durchatmen kann."
+11–17s — Bild: Weiter Blick über den Ort, alles darf atmen · Sprich: "Halt hier einfach mal kurz inne — dieser Moment gehört dir."
+17–20s — Bild: Weite Abschlussaufnahme · Endcard: Lutherrose + "Wo ist dein stiller Ort? · So 09:30 · Miodowa 21"
+🎵 Musik: sehr ruhig, atmosphärisch · 💡 Tipp: Früh morgens filmen, wenn wenig los ist — das Morgenlicht und die Leere machen die Ruhe glaubwürdig. Lange Einstellungen, kein hektischer Schnitt.</t>
+        </is>
+      </c>
       <c r="M270" s="2" t="inlineStr"/>
-      <c r="N270" s="3" t="inlineStr"/>
+      <c r="N270" s="2" t="inlineStr"/>
+      <c r="O270" s="3" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n">
@@ -16206,9 +18842,19 @@
           <t>Lust mitzumachen? Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L271" s="4" t="inlineStr"/>
+      <c r="L271" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~25s
+0–4s — Bild: Hände beim Tun in Nahaufnahme — z.B. am Klavier, an der Kaffeekanne, beim Stühlerücken · Text: "Ohne diese Hände läuft hier nichts."
+4–18s — Bild: Person schaut in die Kamera, kurzes Statement · Sprich (Beispiel): "Ich mach hier den Kaffee für nach dem Gottesdienst. Klingt klein — aber genau da kommen die Leute ins Reden. Und das mach ich einfach gern."
+18–22s — Bild: Ein Moment, in dem man die Freude sieht — ein Lächeln, eine eingeschenkte Tasse · Text: "Danke, dass es dich gibt."
+22–25s — Bild: Endcard: Lutherrose + "— Vorname, [Rolle] · Auch du kannst mitmachen → Link in Bio"
+🎵 Musik: warm, wertschätzend, dezent · 💡 Tipp: Erst die Hände bei der Aufgabe filmen, dann das Statement — so hat man immer Bild zum Drüberlegen, falls die Person beim Reden verlegen wird.</t>
+        </is>
+      </c>
       <c r="M271" s="4" t="inlineStr"/>
-      <c r="N271" s="5" t="inlineStr"/>
+      <c r="N271" s="4" t="inlineStr"/>
+      <c r="O271" s="5" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -16264,9 +18910,18 @@
           <t>Speicher dir den Segen und folg uns für jeden Freitag</t>
         </is>
       </c>
-      <c r="L272" s="2" t="inlineStr"/>
+      <c r="L272" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Person schaut ruhig und freundlich direkt in die Kamera, warmes Licht, nahes Bild · Text: "Ein Segen für deinen Weg — nimm ihn mit."
+3–15s — Bild: Person spricht langsam und persönlich · Sprich: "Egal, wie deine Woche war: Du bist gemeint. Du bist gehalten. Geh behütet ins Wochenende — und weißt du was? Du bist nicht allein unterwegs."
+15–18s — Bild: Kurzes Nicken und ein Lächeln · Endcard: Lutherrose + "Geh behütet · So 09:30 · Miodowa 21"
+🎵 Musik: sehr leise oder keine — die Stimme trägt · 💡 Tipp: Direkt in die Linse schauen, nicht auf den Bildschirm — nur so entsteht das Gefühl, dass der Segen wirklich der Person am anderen Ende gilt.</t>
+        </is>
+      </c>
       <c r="M272" s="2" t="inlineStr"/>
-      <c r="N272" s="3" t="inlineStr"/>
+      <c r="N272" s="2" t="inlineStr"/>
+      <c r="O272" s="3" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="n">
@@ -16322,9 +18977,19 @@
           <t>Schreib uns, welches Symbol du erklärt haben willst</t>
         </is>
       </c>
-      <c r="L273" s="4" t="inlineStr"/>
+      <c r="L273" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~30s
+0–4s — Bild: Die Lutherrose in schöner Nahaufnahme, langsamer Zoom · Text: "Warum steht da eine Rose?"
+4–24s — Bild: Objekt bleibt im Fokus, langsame Kamerabewegung · Sprich: "Das ist die Lutherrose — ein Herz mit einem Kreuz darin, umgeben von einer weißen Rose. Das Kreuz erinnert an das, was uns trägt. Die Rose zeigt: Der Glaube schenkt Freude und Frieden, nicht nur Ernst. Ein kleines Bild mit einer ganzen Botschaft."
+24–27s — Bild: Ruhiges Abschlussbild des Symbols · Text: "Jetzt weißt du's."
+27–30s — Bild: Endcard: Lutherrose + "Welches Symbol als Nächstes? · So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: Nur EIN Objekt und EIN Gedanke pro Folge — der Reiz der Reihe liegt in der Kürze. Unter 40 Sekunden bleiben.</t>
+        </is>
+      </c>
       <c r="M273" s="4" t="inlineStr"/>
-      <c r="N273" s="5" t="inlineStr"/>
+      <c r="N273" s="4" t="inlineStr"/>
+      <c r="O273" s="5" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -16380,9 +19045,19 @@
           <t>Link in Bio → WhatsApp-Gruppe für deutschsprachige Familien</t>
         </is>
       </c>
-      <c r="L274" s="2" t="inlineStr"/>
+      <c r="L274" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–5s — Bild: Kleiner Alltagsmoment — z.B. ein Kind wechselt mitten im Satz von Deutsch zu Polnisch, oder ein Zettel mit beiden Sprachen · Text: "Zuhause Deutsch, draußen Polnisch — kennst du das?"
+5–12s — Bild: Warme Familienszene (mit Einverständnis) oder symbolisches Bild · Sprich: "Für viele Familien hier ist genau das der Alltag — zwischen zwei Sprachen, zwischen zwei Welten."
+12–17s — Bild: Ruhiges, herzliches Bild · Text/Sprich: "Bei uns musst du dich nicht entscheiden. Du darfst beides sein."
+17–20s — Bild: Endcard: Lutherrose + "Willkommen, so wie du bist · Link in Bio → WhatsApp"
+🎵 Musik: warm, familiär, leicht · 💡 Tipp: Wenn Kinder zu sehen sind, unbedingt vorher das Einverständnis der Eltern einholen — im Zweifel nur von hinten oder symbolisch (Hände, Zettel) filmen.</t>
+        </is>
+      </c>
       <c r="M274" s="2" t="inlineStr"/>
-      <c r="N274" s="3" t="inlineStr"/>
+      <c r="N274" s="2" t="inlineStr"/>
+      <c r="O274" s="3" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="n">
@@ -16438,9 +19113,21 @@
           <t>Schreib deine 3 Worte in die Kommentare</t>
         </is>
       </c>
-      <c r="L275" s="4" t="inlineStr"/>
+      <c r="L275" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–2s — Bild: Titelkarte · Text: "Beschreib die Gemeinde in drei Worten."
+2–6s — Bild: Person A schaut in die Kamera · Sprich: "Warm. Ehrlich. Zuhause."
+6–10s — Bild: Harter Schnitt zu Person B · Sprich: "Unkompliziert, herzlich, deutsch."
+10–14s — Bild: Harter Schnitt zu Person C · Sprich: "Klein, aber familiär."
+14–17s — Bild: Schneller Wechsel weiterer Gesichter, je drei Worte · Text: "Ehrlich &amp; ungefiltert"
+17–20s — Bild: Alle Worte kurz als Liste/Wortwolke · Endcard: Lutherrose + "Und deine 3 Worte? · So 09:30 · Miodowa 21"
+🎵 Musik: rhythmisch, aber warm — treibt den schnellen Schnitt · 💡 Tipp: Alle Personen im selben Bildausschnitt und Abstand filmen — dann wirken die harten Schnitte sauber und der Rhythmus stimmt.</t>
+        </is>
+      </c>
       <c r="M275" s="4" t="inlineStr"/>
-      <c r="N275" s="5" t="inlineStr"/>
+      <c r="N275" s="4" t="inlineStr"/>
+      <c r="O275" s="5" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -16496,9 +19183,15 @@
           <t>Verpass keinen Gedanken mehr — komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L276" s="2" t="inlineStr"/>
+      <c r="L276" s="3" t="inlineStr">
+        <is>
+          <t>📸 Motiv: Der prägnanteste Satz der Sonntagspredigt, typografisch groß und schlicht auf ruhigem Aubergine-Hintergrund (#480048). · Bildaufbau/Licht: Viel Weißraum um das Zitat, Text zentriert oder linksbündig, gut lesbar auch im kleinen Feed-Vorschaubild; klein und dezent unten Datum + Anlass des Gottesdienstes. · Text im Bild: "[prägnantester Predigtsatz]" — darunter klein: "Aus der Predigt · [Datum]"
+💡 Tipp: Nur EIN Satz aufs Bild — je kürzer und klarer das Zitat, desto eher wird es gespeichert und geteilt. Im Zweifel den Satz noch straffen, nicht den zweiten dazunehmen.</t>
+        </is>
+      </c>
       <c r="M276" s="2" t="inlineStr"/>
-      <c r="N276" s="3" t="inlineStr"/>
+      <c r="N276" s="2" t="inlineStr"/>
+      <c r="O276" s="3" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="n">
@@ -16554,9 +19247,20 @@
           <t>Trau dich — komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L277" s="4" t="inlineStr"/>
+      <c r="L277" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~30s
+0–4s — Bild: Blick auf die geöffnete Tür, jemand macht eine einladende Geste · Sprich: "Komm rein — ich zeig dir alles, ganz in Ruhe."
+4–12s — Bild: Rundgang aus der Ich-Perspektive, Kamera geht in den Raum · Sprich: "Hier kommst du an, hängst deine Jacke auf — und setzen kannst du dich einfach dahin, wo du magst."
+12–22s — Bild: Schwenk über Bänke, Gesangbuch, den Ablauf zeigen · Sprich: "Wir singen, wir hören zu, wir beten — aber keine Sorge: Du musst nichts mitsingen und nichts können. Zuschauen ist völlig okay."
+22–26s — Bild: Kamera hält an einem freien Platz an · Sprich: "Und dieser Platz hier? Der ist auch für dich."
+26–30s — Bild: Endcard: Lutherrose + "Trau dich · So 09:30 · Miodowa 21"
+🎵 Musik: freundlich, einladend, dezent · 💡 Tipp: In einem durchgehenden Gang filmen (ein Take), als würdest du eine Freundin persönlich herumführen — das nimmt mehr Angst als perfekt geschnittene Einzelbilder.</t>
+        </is>
+      </c>
       <c r="M277" s="4" t="inlineStr"/>
-      <c r="N277" s="5" t="inlineStr"/>
+      <c r="N277" s="4" t="inlineStr"/>
+      <c r="O277" s="5" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -16612,9 +19316,18 @@
           <t>Tipp auf die Fragebox und stell deine Frage</t>
         </is>
       </c>
-      <c r="L278" s="2" t="inlineStr"/>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~8s (Story)
+0–3s — Bild: Einladendes ruhiges Bild (Kerze, Tür, warmer Raum), Fragebox-Sticker platziert · Text: "Was wolltest du eine Kirche schon immer mal fragen?"
+3–6s — Bild: Gleiches Bild, Blick auf den Fragebox-Sticker gelenkt · Sprich/Text: "Anonym, ehrlich, ohne dumme Fragen — trau dich einfach."
+6–8s — Bild: Sticker im Fokus · Text: "Die beste Frage kommt ins nächste Reel."
+🎵 Musik: leicht, einladend, dezent · 💡 Tipp: Frage-Sticker groß und mittig platzieren, damit der Daumen ihn sofort trifft — und nach ein paar Tagen die (anonymisierten) Fragen in einer Folge-Story teilen, das hält den Dialog am Laufen.</t>
+        </is>
+      </c>
       <c r="M278" s="2" t="inlineStr"/>
-      <c r="N278" s="3" t="inlineStr"/>
+      <c r="N278" s="2" t="inlineStr"/>
+      <c r="O278" s="3" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="n">
@@ -16670,9 +19383,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L279" s="4" t="inlineStr"/>
+      <c r="L279" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Person frontal, Handy auf Augenhöhe, freundlicher Blick · Sprich: "Ein Wort, und Warschau wird dir gleich freundlicher."
+3–8s — Bild: Nahaufnahme ihres Gesichts, sie spricht langsam · Sprich: "Dziękuję. Das heißt einfach: Danke. Sprich mir nach – dschen-KU-je."
+8–13s — Bild: kurze Alltagsszene beim Bäcker, sie nimmt die Tüte und sagt es · Sprich: "Beim Bäcker, im Bus, beim Nachbarn – ein Danke öffnet Türen."
+13–17s — Bild: sie lacht, sagt es nochmal, Daumen hoch · Sprich: "Trau dich. Auch holprig zählt."
+17–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, warm, dezent · 💡 Tipp: Nimm den Ton nah am Mund auf (Handy in Armlänge, ruhiger Raum), damit das Wort klar verständlich bleibt.</t>
+        </is>
+      </c>
       <c r="M279" s="4" t="inlineStr"/>
-      <c r="N279" s="5" t="inlineStr"/>
+      <c r="N279" s="4" t="inlineStr"/>
+      <c r="O279" s="5" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -16728,9 +19452,20 @@
           <t>Schreib deinen falschen Freund in die Kommentare</t>
         </is>
       </c>
-      <c r="L280" s="2" t="inlineStr"/>
+      <c r="L280" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~17s
+0–3s — Bild: Person hält ein Handschild mit dem Wort hoch, guckt fragend in die Kamera · Sprich: "Falscher Freund der Woche – Achtung, gleich wird's peinlich."
+3–8s — Bild: sie zeigt aufs Schild, ernste Miene · Sprich: "Klingt wie bei uns, heißt aber im Polnischen was ganz anderes."
+8–13s — Bild: kleine Alltagsszene, in der das Missverständnis passieren könnte, sie schaut ertappt · Sprich: "Genau da bin ich schon reingetappt."
+13–16s — Bild: sie lacht, zuckt mit den Schultern · Sprich: "Sprache verbindet – und verwirrt. Welchen kennst du?"
+16–17s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: verspielt, leicht, dezent · 💡 Tipp: Schreib das Wort dick mit Filzstift auf ein Blatt – das liest sich im Reel besser als ein kleines Handydisplay.</t>
+        </is>
+      </c>
       <c r="M280" s="2" t="inlineStr"/>
-      <c r="N280" s="3" t="inlineStr"/>
+      <c r="N280" s="2" t="inlineStr"/>
+      <c r="O280" s="3" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="n">
@@ -16786,9 +19521,19 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L281" s="4" t="inlineStr"/>
+      <c r="L281" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Altes Foto / Stadtansicht Warschau, darüber der Titel "Wie man in Warschau evangelisch wird" – Untertitel: "Eine leise, treue Geschichte."
+Slide 2: Text auf ruhigem Hintergrund: "Seit Jahrhunderten sind Deutschsprachige hier zu Hause – und feiern ihren Glauben mitten in dieser Stadt."
+Slide 3: Alte Kirchen- oder Gemeindeansicht · Text: "Eine Gemeinde, die blieb – durch gute und durch schwere Zeiten."
+Slide 4: Aktuelles Foto vom Gottesdienst an der Miodowa · Text: "Bis heute treffen wir uns – ul. Miodowa 21."
+Slide 5: Warmes Gruppenfoto oder Lutherrose · Text: "Du gehörst dazu. Komm Sonntag 09:30, Miodowa 21."
+💡 Tipp: Halte die Textmenge pro Slide kurz (max. 2 Zeilen) und nutze auf allen Slides dieselbe Schrift und Farbe (Aubergine), damit das Carousel wie aus einem Guss wirkt.</t>
+        </is>
+      </c>
       <c r="M281" s="4" t="inlineStr"/>
-      <c r="N281" s="5" t="inlineStr"/>
+      <c r="N281" s="4" t="inlineStr"/>
+      <c r="O281" s="5" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -16844,9 +19589,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L282" s="2" t="inlineStr"/>
+      <c r="L282" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: langsamer Schwenk über den leeren Synodalsaal, Licht fällt durch die Fenster · Sprich (aus dem Off, ruhig): "Das hier ist unser Sonntagmorgen-Ort."
+4–9s — Bild: Detail von Stühlen, ein aufgeschlagenes Gesangbuch, eine Kerze · Sprich: "Wir haben keine eigene Kirche. Wir feiern als Gäste."
+9–15s — Bild: weiter Blick in den Saal, weiche Kamerabewegung · Sprich: "Zu Gast bei den polnischen Geschwistern – Gastfreundschaft, die trägt."
+15–19s — Bild: die offene Tür, Blick hinein · Sprich: "Die Tür steht offen. Komm vorbei."
+19–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: ruhig, sakral-warm, sehr dezent · 💡 Tipp: Film die Schwenks langsam und stütz das Handy an einer Stuhllehne ab – ruhige Bilder wirken hier würdevoller als jede Bewegung aus der Hand.</t>
+        </is>
+      </c>
       <c r="M282" s="2" t="inlineStr"/>
-      <c r="N282" s="3" t="inlineStr"/>
+      <c r="N282" s="2" t="inlineStr"/>
+      <c r="O282" s="3" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="n">
@@ -16902,9 +19658,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L283" s="4" t="inlineStr"/>
+      <c r="L283" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–3s — Bild: Person auf einer Café-Bank, direkt in die Kamera · Sprich: "Neu in Warschau? Drei Dinge, die mir keiner gesagt hat."
+3–9s — Bild: Einblendung "Tipp 1", sie hält einen Finger hoch · Sprich: "Erstens, die Behörden: Bring Geduld mit – und von jedem Dokument eine Kopie."
+9–15s — Bild: Einblendung "Tipp 2" · Sprich: "Zweitens, die Wohnung: Die besten findest du übers Netzwerk, nicht auf Portalen. Frag Leute."
+15–20s — Bild: Einblendung "Tipp 3", warmer Blick · Sprich: "Und drittens: Anschluss. Du bist nicht allein – wir Deutschsprachigen treffen uns wirklich."
+20–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, leicht optimistisch, dezent · 💡 Tipp: Setz dich seitlich ans Fensterlicht statt mit dem Rücken davor – so ist dein Gesicht schön ausgeleuchtet statt dunkel.</t>
+        </is>
+      </c>
       <c r="M283" s="4" t="inlineStr"/>
-      <c r="N283" s="5" t="inlineStr"/>
+      <c r="N283" s="4" t="inlineStr"/>
+      <c r="O283" s="5" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -16960,9 +19727,19 @@
           <t>Link in Bio → Termine zur Weihnachtszeit</t>
         </is>
       </c>
-      <c r="L284" s="2" t="inlineStr"/>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Kerzenschein und ein Tannenzweig, darüber "Heiligabend – hier vs. daheim".
+Slide 2: Foto eines festlich gedeckten Tisches · Text: "In Polen: Wigilia am 24. – zwölf Gerichte, das Warten aufs erste Sternchen."
+Slide 3: Adventskranz, warmes Licht · Text: "Daheim: Kranz, Kerzen, vertraute Lieder – die Weihnacht, die du kennst."
+Slide 4: Foto vom Gottesdienstraum oder Kerzen im Saal · Text: "Beides darf sein. Bei uns kommt es zusammen."
+Slide 5: Lutherrose · Text: "Feier mit uns – kein Heimweh allein. Termine zur Weihnachtszeit: Link in Bio."
+💡 Tipp: Fotografiere die Kerzenbilder in der Dämmerung ohne Blitz und tippe im Handy einmal aufs Licht zum Scharfstellen – das warme Glühen macht dieses Carousel aus.</t>
+        </is>
+      </c>
       <c r="M284" s="2" t="inlineStr"/>
-      <c r="N284" s="3" t="inlineStr"/>
+      <c r="N284" s="2" t="inlineStr"/>
+      <c r="O284" s="3" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="n">
@@ -17018,9 +19795,20 @@
           <t>Link in Bio → mehr über uns</t>
         </is>
       </c>
-      <c r="L285" s="4" t="inlineStr"/>
+      <c r="L285" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~19s
+0–4s — Bild: ruhige Aufnahme eines Fensters, weiches Licht in einem stillen Zimmer · Sprich (leise): "Wie sagt man Frieden auf Polnisch?"
+4–8s — Bild: Person im weichen Licht, sie spricht das Wort langsam · Sprich: "Pokój."
+8–13s — Bild: Einblendung der doppelten Bedeutung, Kamera ruht · Sprich: "Dasselbe Wort heißt auch: Zimmer. Ein Raum."
+13–18s — Bild: eine Kerze, Stille, sanfter Zoom · Sprich: "Vielleicht kein Zufall. Frieden ist ein Raum, den wir füreinander offen halten."
+18–19s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr ruhig, meditativ, kaum hörbar · 💡 Tipp: Lass zwischen den Sätzen bewusst Stille – bei diesem nachdenklichen Ton wirken Pausen stärker als volle Vertonung.</t>
+        </is>
+      </c>
       <c r="M285" s="4" t="inlineStr"/>
-      <c r="N285" s="5" t="inlineStr"/>
+      <c r="N285" s="4" t="inlineStr"/>
+      <c r="O285" s="5" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -17076,9 +19864,20 @@
           <t>Link in Bio → mehr über uns</t>
         </is>
       </c>
-      <c r="L286" s="2" t="inlineStr"/>
+      <c r="L286" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–5s — Bild: gehende Handyaufnahme durch eine Warschauer Straße, ruhiges Tempo · Sprich (aus dem Off, leise): "Manche Straßen hier tragen mehr als einen Namen."
+5–11s — Bild: Ankunft am Ort – Kirche oder Denkmal, langsamer Schwenk · Sprich: "Dieser Ort erzählt eine deutsch-polnische Geschichte. Eine schwere."
+11–16s — Bild: Detail von Schild, Inschrift oder einem Kranz · Sprich: "Erinnerung, die verpflichtet. Wir gehen achtsam durch diese Stadt."
+16–21s — Bild: weiter Blick, dann Innehalten, Stille · Sprich: "Kein großes Wort. Nur ein Moment des Innehaltens."
+21–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: sehr zurückhaltend, ernst, fast nur Klangfläche · 💡 Tipp: Bei diesem sensiblen Thema keine dramatische Musik und keine schnellen Schnitte – langsam gehen, ruhig atmen, den Ort für sich sprechen lassen.</t>
+        </is>
+      </c>
       <c r="M286" s="2" t="inlineStr"/>
-      <c r="N286" s="3" t="inlineStr"/>
+      <c r="N286" s="2" t="inlineStr"/>
+      <c r="O286" s="3" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="n">
@@ -17134,9 +19933,20 @@
           <t>Link in Bio → Kontakt aufnehmen</t>
         </is>
       </c>
-      <c r="L287" s="4" t="inlineStr"/>
+      <c r="L287" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~19s
+0–3s — Bild: Person ruhig im Bild, warmer Hintergrund · Sprich: "Seelsorge – klingt nach einem großen, alten Wort."
+3–8s — Bild: Nahaufnahme, sie hält kurz inne · Sprich: "Dabei meint es etwas ganz Einfaches: Sorge für die Seele."
+8–14s — Bild: sie spricht ruhig weiter, ehrlicher Blick · Sprich: "Zuhören. Da sein. Jemanden nicht allein lassen."
+14–18s — Bild: warmes Lächeln · Sprich: "Und zwar in der Sprache, in der dir das Herz aufgeht. Wir sind für dich da."
+18–19s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, tröstlich, dezent · 💡 Tipp: Sprich langsamer als du denkst – bei einem so persönlichen Text wirkt Ruhe glaubwürdiger als Tempo.</t>
+        </is>
+      </c>
       <c r="M287" s="4" t="inlineStr"/>
-      <c r="N287" s="5" t="inlineStr"/>
+      <c r="N287" s="4" t="inlineStr"/>
+      <c r="O287" s="5" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -17192,9 +20002,19 @@
           <t>Sticker antippen → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L288" s="2" t="inlineStr"/>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~15s (2 Story-Karten)
+0–3s — Story 1, Bild: Fensterblick am ruhigen Morgen oder ein Kalenderblatt · On-Screen-Text: "Feiertag heute – in welchem Land?"
+3–7s — Story 1 weiter, Bild: gleiche Szene · On-Screen-Text mit Quiz-Sticker: "Deutschland? Polen? Beide?" (Umfrage-Sticker antippbar)
+7–11s — Story 2, Bild: warmes Detail (Kaffeetasse, Kerze) · On-Screen-Text: "Auflösung: heute frei in … · Das wird gefeiert: …"
+11–15s — Story 2 Endkarte, Bild: Lutherrose · On-Screen-Text: "Guten Feiertag dir! · Mehr Alltagshilfe? Sticker antippen → WhatsApp-Gruppe · So 09:30 · Miodowa 21"
+🎵 Musik: leicht, freundlich, dezent · 💡 Tipp: Nutz den Quiz- oder Umfrage-Sticker von Instagram direkt – echte Antippbarkeit bringt mehr Reichweite als ein reines Text-Bild.</t>
+        </is>
+      </c>
       <c r="M288" s="2" t="inlineStr"/>
-      <c r="N288" s="3" t="inlineStr"/>
+      <c r="N288" s="2" t="inlineStr"/>
+      <c r="O288" s="3" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="n">
@@ -17250,9 +20070,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L289" s="4" t="inlineStr"/>
+      <c r="L289" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: Nahaufnahme, Kaffee wird eingeschenkt, Kuchen auf dem Tisch · Sprich (aus dem Off): "Das Schönste kommt nach dem Gottesdienst."
+3–8s — Bild: Gruppe im Gespräch, echtes Gelächter, Sprachwechsel mitten im Satz · Text: "Kaffee auf Deutsch, Kuchen auf Polnisch."
+8–13s — Bild: Detail, Hände reichen einen Teller weiter · Sprich: "Beide Sprachen durcheinander – und keiner schämt sich."
+13–17s — Bild: zwei Leute stoßen mit Kaffeetassen an, lachen · Sprich: "Kein Sprachkurs nötig. Nur Dabeisein."
+17–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: fröhlich, warm, gemütlich · 💡 Tipp: Filme echte Szenen beim nächsten Kirchenkaffee mit kurzen 2–3-Sekunden-Clips – authentisches Gewusel schlägt jede gestellte Aufnahme. Frag die Leute vorher um Erlaubnis.</t>
+        </is>
+      </c>
       <c r="M289" s="4" t="inlineStr"/>
-      <c r="N289" s="5" t="inlineStr"/>
+      <c r="N289" s="4" t="inlineStr"/>
+      <c r="O289" s="5" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -17308,9 +20139,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L290" s="2" t="inlineStr"/>
+      <c r="L290" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~22s
+0–3s — Bild: Nahaufnahme eines aufgeschlagenen Gesangbuchs · Text (kein Sprechen, nur Einblendung): "Ein Lied, zwei Sprachen"
+3–10s — Bild: jemand singt ruhig eine Strophe auf Deutsch · Sing (wörtlich): "Großer Gott, wir loben dich, Herr, wir preisen deine Stärke." · Untertitel: "Deutsch"
+10–17s — Bild: Schnitt auf dieselbe Melodie polnisch, evtl. andere Person · Sing (polnische Strophe desselben Chorals) · Untertitel: "Polnisch"
+17–21s — Bild: kurze Überblendung beider Aufnahmen, letzter Ton klingt aus · Text: "Glaube klingt über Grenzen."
+21–22s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: keine zusätzliche Musik – der Gesang selbst trägt · 💡 Tipp: Nimm den Gesang in einem hallarmen Raum auf und lass die Person nah ans Handy singen; sauberer Ton ist hier wichtiger als das Bild.</t>
+        </is>
+      </c>
       <c r="M290" s="2" t="inlineStr"/>
-      <c r="N290" s="3" t="inlineStr"/>
+      <c r="N290" s="2" t="inlineStr"/>
+      <c r="O290" s="3" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="n">
@@ -17366,9 +20208,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L291" s="4" t="inlineStr"/>
+      <c r="L291" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s (fast wortlos, Bilder tragen)
+0–4s — Bild: ruhige Straße am frühen Sonntagmorgen, kaum Menschen · On-Screen-Text: "Warschau um 9:15"
+4–9s — Bild: weiches Morgenlicht auf Fassaden, leiser Schwenk · On-Screen-Text: "Die Stadt ist noch still."
+9–14s — Bild: Schritte auf dem Weg zur Miodowa, Ich-Perspektive · On-Screen-Text: "Der Weg, den viele sonntags gehen."
+14–18s — Bild: Ankunft, die Tür an der Miodowa 21 · On-Screen-Text: "Ziel: Miodowa 21"
+18–20s — Endcard: Lutherrose + "09:30 – wir warten auf dich · So · Miodowa 21"
+🎵 Musik: ruhig, warm, leicht sehnsüchtig · 💡 Tipp: Halte das Handy beim Gehen mit beiden Händen dicht am Körper (oder nutz den Bildstabilisator) – wackelfreie Schritte machen dieses stille Reel aus.</t>
+        </is>
+      </c>
       <c r="M291" s="4" t="inlineStr"/>
-      <c r="N291" s="5" t="inlineStr"/>
+      <c r="N291" s="4" t="inlineStr"/>
+      <c r="O291" s="5" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -17424,9 +20277,19 @@
           <t>Kommentier deine Heimatstadt</t>
         </is>
       </c>
-      <c r="L292" s="2" t="inlineStr"/>
+      <c r="L292" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Schlichte Landkarte von D/A/CH und Umgebung · Text: "Woher kommst du? – Die Landkarte unserer Gemeinde".
+Slide 2: Dieselbe Karte mit gesetzten Pins auf mehreren Orten · Text: "Aus Deutschland, Österreich, der Schweiz – und weit darüber hinaus."
+Slide 3: Ruhiger Hintergrund mit kurzen Zitaten · Text: "'Ich komme aus Hamburg.' · 'Ich aus Wien.' · 'Und ich aus Bern.'"
+Slide 4: Warmes Foto der Gruppe · Text: "So bunt ist 'deutschsprachig' wirklich."
+Slide 5: Karte mit einem leeren Pin · Text: "Und du? Kommentier deine Heimatstadt. Komm dazu – So 09:30, Miodowa 21."
+💡 Tipp: Du brauchst keine Profi-Grafik – eine schlichte Karte aus einer kostenlosen Vorlage mit ein paar aufgesetzten Pin-Emojis reicht völlig und wirkt nahbar.</t>
+        </is>
+      </c>
       <c r="M292" s="2" t="inlineStr"/>
-      <c r="N292" s="3" t="inlineStr"/>
+      <c r="N292" s="2" t="inlineStr"/>
+      <c r="O292" s="3" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="n">
@@ -17482,9 +20345,21 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L293" s="4" t="inlineStr"/>
+      <c r="L293" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~21s
+0–3s — Bild: Person vor neutralem Hintergrund, hält drei Finger hoch · Sprich: "Der Amtsbesuch ist der Endgegner. Drei Wörter, und du kommst durch."
+3–8s — Bild: Einblendung "1. Dzień dobry" · Sprich: "Erstens, zur Begrüßung: Dzień dobry – guten Tag. Immer freundlich rein."
+8–14s — Bild: Einblendung "2. Poproszę", sie schmunzelt · Sprich: "Zweitens: Poproszę – ich bitte um. Ich hab das mal vergessen und bin ziemlich baff angeschaut worden."
+14–18s — Bild: Einblendung "3. Nie rozumiem" · Sprich: "Und drittens, der Rettungsanker: Nie rozumiem – ich verstehe nicht."
+18–20s — Bild: sie lacht · Sprich: "Du schaffst das."
+20–21s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: leicht, augenzwinkernd, dezent · 💡 Tipp: Blende jedes Wort groß und lang genug ein (mind. 2 Sekunden), damit man die Aussprache mitlesen und pausieren kann.</t>
+        </is>
+      </c>
       <c r="M293" s="4" t="inlineStr"/>
-      <c r="N293" s="5" t="inlineStr"/>
+      <c r="N293" s="4" t="inlineStr"/>
+      <c r="O293" s="5" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -17540,9 +20415,20 @@
           <t>Link in Bio → mehr über uns</t>
         </is>
       </c>
-      <c r="L294" s="2" t="inlineStr"/>
+      <c r="L294" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: ruhige Aufnahme, warmes Licht, Person im Bild · Sprich: "Wie klingt ein Gruß, der ein kleiner Segen ist?"
+3–8s — Bild: Nahaufnahme, sie spricht langsam · Sprich: "Szczęść Boże. Sprich mir nach – shtscheschtsch BO-sche."
+8–13s — Bild: Einblendung der Übersetzung · Sprich: "Das heißt: Gott zum Gruße. Ein Segen mitten im Alltag."
+13–17s — Bild: leises Lächeln, ein Nicken · Sprich: "Uns berührt das jedes Mal – die Frömmigkeit, die uns hier umgibt."
+17–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, ehrfürchtig, sehr dezent · 💡 Tipp: Zeig den Gruß mit echter Wertschätzung, nicht belustigt – ein ruhiger, respektvoller Ton unterscheidet dieses Reel von den Sprachwitz-Clips.</t>
+        </is>
+      </c>
       <c r="M294" s="2" t="inlineStr"/>
-      <c r="N294" s="3" t="inlineStr"/>
+      <c r="N294" s="2" t="inlineStr"/>
+      <c r="O294" s="3" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="n">
@@ -17598,9 +20484,19 @@
           <t>Link in Bio → Reformationsgottesdienst</t>
         </is>
       </c>
-      <c r="L295" s="4" t="inlineStr"/>
+      <c r="L295" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Lutherrose auf ruhigem Grund · Text: "Zwei Reformationstage, ein Glaube · 31. Oktober".
+Slide 2: Foto/Motiv aus Deutschland · Text: "In Deutschland: gemeinsames Gedenken an die Reformation – vielerorts ein Feiertag."
+Slide 3: Foto einer polnisch-evangelischen Gemeinde · Text: "In Polen: die kleine, treue evangelische Minderheit feiert mit."
+Slide 4: Foto unserer Gemeinde / Miodowa · Text: "Als deutschsprachige Lutheraner stehen wir mittendrin."
+Slide 5: Lutherrose · Text: "Feier den Reformationstag mit uns. Reformationsgottesdienst – Link in Bio."
+💡 Tipp: Verwende die Lutherrose auf der ersten und letzten Slide als roten Faden – das gibt dem Carousel sofort einen wiedererkennbaren, würdevollen Rahmen.</t>
+        </is>
+      </c>
       <c r="M295" s="4" t="inlineStr"/>
-      <c r="N295" s="5" t="inlineStr"/>
+      <c r="N295" s="4" t="inlineStr"/>
+      <c r="O295" s="5" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -17656,9 +20552,20 @@
           <t>Kommentier deinen Lieblingsort</t>
         </is>
       </c>
-      <c r="L296" s="2" t="inlineStr"/>
+      <c r="L296" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: gemütliche Außenaufnahme des Cafés oder Buchladens · Sprich (aus dem Off): "Ein Ort, an dem plötzlich Deutsch erklingt – in der Fremde Gold wert."
+3–8s — Bild: Innen, Details von Büchern, Tassen, Atmosphäre · Sprich: "Kein bezahltes Werben. Nur ein ehrlicher Lieblingsort von uns."
+8–14s — Bild: Person am Tisch, erzählt kurz · Sprich: "Hier fühl ich mich ein Stück zu Hause. Genau das braucht man am Anfang."
+14–17s — Bild: Adresse eingeblendet, Kaffee in der Hand, Lächeln · Sprich: "Anschluss findet man Stück für Stück. Kennst du auch so einen Ort?"
+17–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: gemütlich, leicht, dezent · 💡 Tipp: Frag im Laden kurz um Erlaubnis zum Filmen und meide fremde Gesichter im Bild – so bleibt's entspannt und du hast keine Rechteprobleme.</t>
+        </is>
+      </c>
       <c r="M296" s="2" t="inlineStr"/>
-      <c r="N296" s="3" t="inlineStr"/>
+      <c r="N296" s="2" t="inlineStr"/>
+      <c r="O296" s="3" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="n">
@@ -17714,9 +20621,21 @@
           <t>Schreib dein Wort in die Kommentare</t>
         </is>
       </c>
-      <c r="L297" s="4" t="inlineStr"/>
+      <c r="L297" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~19s
+0–3s — Bild: erste Person ruhig in die Kamera · On-Screen-Text: "Heimweh hat keine Grenze. Was fehlt dir am meisten?"
+3–7s — Bild: schneller Schnitt, Person 1 · Sprich: "Das Brot."
+7–10s — Bild: Person 2 · Sprich: "Der Wald zu Hause."
+10–13s — Bild: Person 3 · Sprich: "Meine Sprache. Einfach mal Deutsch reden."
+13–17s — Bild: gemeinsames Bild der Gruppe, warme Blicke · Sprich (eine Stimme): "Hier darfst du es teilen. Hier bist du nicht allein."
+17–19s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: leise, warm, ein wenig wehmütig · 💡 Tipp: Nimm alle Personen im gleichen Bildausschnitt und Abstand auf – gleiche Rahmung macht die schnelle Schnittfolge ruhig statt hektisch.</t>
+        </is>
+      </c>
       <c r="M297" s="4" t="inlineStr"/>
-      <c r="N297" s="5" t="inlineStr"/>
+      <c r="N297" s="4" t="inlineStr"/>
+      <c r="O297" s="5" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -17772,9 +20691,19 @@
           <t>Link in Bio → Termine im Advent</t>
         </is>
       </c>
-      <c r="L298" s="2" t="inlineStr"/>
+      <c r="L298" s="3" t="inlineStr">
+        <is>
+          <t>Slide 1: Adventskranz mit einer brennenden Kerze, warmes Licht · Text: "Advent zwischen zwei Welten".
+Slide 2: Kranz, Adventskalender, Plätzchen · Text: "Unsere Tradition: Kranz, Kalender, vertraute Lieder – aus der Heimat mitgebracht."
+Slide 3: Foto eines polnischen Vorweihnachtsbrauchs · Text: "Polnische Vorweihnacht daneben – wir lernen sie lieben."
+Slide 4: Beides zusammen auf einem Tisch · Text: "Heimat ist etwas, das man mitnimmt und teilt."
+Slide 5: Kerzenlicht / Lutherrose · Text: "Feier den Advent mit uns – nicht allein. Termine im Advent: Link in Bio."
+💡 Tipp: Fotografiere alle fünf Bilder im selben warmen Kerzenlicht und mit ähnlichem Ausschnitt, dann wirkt das Carousel wie eine zusammengehörige kleine Adventsgeschichte.</t>
+        </is>
+      </c>
       <c r="M298" s="2" t="inlineStr"/>
-      <c r="N298" s="3" t="inlineStr"/>
+      <c r="N298" s="2" t="inlineStr"/>
+      <c r="O298" s="3" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="n">
@@ -17830,9 +20759,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L299" s="4" t="inlineStr"/>
+      <c r="L299" s="5" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~18s
+0–3s — Bild: warme Aufnahme einer kleinen Gruppe beim Beisammensein · Sprich (aus dem Off): "Es gibt ein polnisches Wort für Gemeinde, das ich besonders mag."
+3–8s — Bild: Person spricht langsam in die Kamera · Sprich: "Wspólnota. Sprich es ruhig aus – wsPUL-no-ta."
+8–13s — Bild: Einblendung der Bedeutung, Schnitte von Händen und Lachen · Sprich: "Es heißt: Gemeinschaft. Ein Ort, wo du dazugehörst."
+13–17s — Bild: Beieinandersein, warmer Schlussblick · Sprich: "Egal welche Sprache du sprichst. Du gehörst dazu."
+17–18s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: warm, verbindend, dezent · 💡 Tipp: Zeig im Hintergrund echte Gemeinschaft (Kirchenkaffee, kleine Gruppe) statt einer einzelnen Person – das Bild soll das Wort einlösen.</t>
+        </is>
+      </c>
       <c r="M299" s="4" t="inlineStr"/>
-      <c r="N299" s="5" t="inlineStr"/>
+      <c r="N299" s="4" t="inlineStr"/>
+      <c r="O299" s="5" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -17888,9 +20828,20 @@
           <t>Komm Sonntag 09:30, Miodowa 21</t>
         </is>
       </c>
-      <c r="L300" s="2" t="inlineStr"/>
+      <c r="L300" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~20s
+0–4s — Bild: Einstieg an der Tramhaltestelle, Liniennummer eingeblendet · Sprich: "Du weißt nicht, wie du zu uns kommst? Ich zeig's dir – ganz konkret."
+4–9s — Bild: Fahrt aus dem Fenster gefilmt, kurze Schnitte · Sprich: "Mit Tram oder Bus bist du in wenigen Minuten in der Nähe."
+9–14s — Bild: Ausstieg, Weg zu Fuß von der Altstadt · Sprich: "Von der Altstadt sind es nur ein paar Schritte zu Fuß."
+14–18s — Bild: Ankunft an der Miodowa 21, Eingang zeigen · Sprich: "Und da ist es schon – Miodowa 21. Geschafft."
+18–20s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: leicht, bewegt, freundlich · 💡 Tipp: Blende an jeder Station die konkrete Linien-/Haltestellennummer als Text ein – dann funktioniert das Reel auch stumm als echte Wegbeschreibung.</t>
+        </is>
+      </c>
       <c r="M300" s="2" t="inlineStr"/>
-      <c r="N300" s="3" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr"/>
+      <c r="O300" s="3" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="n">
@@ -17946,9 +20897,19 @@
           <t>Link in Bio → mehr über uns</t>
         </is>
       </c>
-      <c r="L301" s="4" t="inlineStr"/>
+      <c r="L301" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Altes Schwarz-Weiß-Foto der Gemeinde oder Kirche · Text: "Als die Deutschen in Warschau beteten".
+Slide 2: Ruhiger Hintergrund mit einem kurzen Absatz · Text: "Deutschsprachige haben hier gebetet, gefeiert und gehofft – in guten und in sehr schweren Zeiten."
+Slide 3: Ausschnitt eines historischen Dokuments oder Details · Text: "Kontinuität und Demut – wir vergessen die schweren Kapitel nicht."
+Slide 4: Aktuelles Foto derselben Gemeinde / Miodowa · Text: "Dieselbe Gemeinde, bis heute lebendig."
+Slide 5: Lutherrose · Text: "Wir stehen in einer langen Linie – und tragen sie weiter. Komm dazu: mehr über uns in der Bio."
+💡 Tipp: Bei historischen Fotos immer die Herkunft/Quelle klären, bevor du postest – und den Ton demütig halten, ohne die schwere gemeinsame Geschichte zu beschönigen.</t>
+        </is>
+      </c>
       <c r="M301" s="4" t="inlineStr"/>
-      <c r="N301" s="5" t="inlineStr"/>
+      <c r="N301" s="4" t="inlineStr"/>
+      <c r="O301" s="5" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -18004,9 +20965,20 @@
           <t>Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L302" s="2" t="inlineStr"/>
+      <c r="L302" s="3" t="inlineStr">
+        <is>
+          <t>🎬 Länge ~19s
+0–3s — Bild: das Wort groß eingeblendet, jemand liest es fassungslos · Sprich: "Angeblich das schwerste polnische Wort. Szczebrzeszyn. Bitte was?"
+3–9s — Bild: schnelle Reihe von Versuchen verschiedener Leute, alle scheitern lustig · Sprich (mehrere Stimmen): "Schtsche… nee. · Szcze-brze… hilfe. · Ich geb auf!"
+9–13s — Bild: Zwischenschnitte, Gelächter, Kopfschütteln · Text: "Wir sind auch nur Zugezogene."
+13–17s — Bild: ein halbwegs gelungener Versuch, alle jubeln · Sprich: "Fast! Siehst du – geht doch. Trau dich, wir üben zusammen."
+17–19s — Endcard: Lutherrose + "So 09:30 · Miodowa 21"
+🎵 Musik: fröhlich, schwungvoll, verspielt · 💡 Tipp: Sammle mehrere kurze Versuchs-Clips vom Handy und schneide sie eng aneinander – je schneller die Abfolge, desto lustiger wirkt das Scheitern.</t>
+        </is>
+      </c>
       <c r="M302" s="2" t="inlineStr"/>
-      <c r="N302" s="3" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr"/>
+      <c r="O302" s="3" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="n">
@@ -18062,12 +21034,22 @@
           <t>Komm Sonntag 09:30, Miodowa 21 – oder Link in Bio → WhatsApp-Gruppe</t>
         </is>
       </c>
-      <c r="L303" s="4" t="inlineStr"/>
+      <c r="L303" s="5" t="inlineStr">
+        <is>
+          <t>Slide 1: Foto vom Eingang Miodowa 21 · Text: "Dein erster Sonntag hier – was dich erwartet".
+Slide 2: Foto von Eingang und Weg hinein · Text: "Wo rein? Einfach durch die Tür an der Miodowa 21 – niemand schaut komisch, versprochen."
+Slide 3: Foto vom Saal · Text: "Wo sitzen? Wohin du magst. Der Ablauf ist ruhig und leicht zu folgen."
+Slide 4: Ruhiger Hintergrund · Text: "Musst du was können? Nein. Und ja – es ist auf Deutsch."
+Slide 5: Warmes Gruppen- oder Türfoto / Lutherrose · Text: "Wir freuen uns auf dich. So 09:30, Miodowa 21 – oder erst mal in die WhatsApp-Gruppe (Link in Bio)."
+💡 Tipp: Nimm echte Fotos vom Eingang und Saal (bei leerem Raum, mit Erlaubnis) statt Symbolbilder – vertraute konkrete Orte nehmen einem Erstbesucher am meisten Angst.</t>
+        </is>
+      </c>
       <c r="M303" s="4" t="inlineStr"/>
-      <c r="N303" s="5" t="inlineStr"/>
+      <c r="N303" s="4" t="inlineStr"/>
+      <c r="O303" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N303"/>
+  <autoFilter ref="A1:O303"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>